--- a/exports/dados_exportados_jira_por_ano.xlsx
+++ b/exports/dados_exportados_jira_por_ano.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC198"/>
+  <dimension ref="A1:BC203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33924,7 +33924,7 @@
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>[ASPLAGMETA-2801] TJMG 129 - Executar 100% (cem por cento) do projeto de Painel de Gestão Automatizada de Receitas Judiciais até dezembro de 2025.</t>
+          <t>[ASPLAGMETA-2871] TJMG 154 – Definir e preparar, até dezembro de 2025, 100% (cem por cento) dos conjuntos de dados do TJMG que serão adequados ao formato aberto, a ser disponibilizado no portal na primeira fase do projeto.</t>
         </is>
       </c>
       <c r="F148" t="inlineStr"/>
@@ -33940,7 +33940,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Diretora de Secretaria</t>
+          <t>Gerente</t>
         </is>
       </c>
       <c r="J148" t="inlineStr"/>
@@ -33963,19 +33963,11 @@
       <c r="O148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Corregedoria</t>
-        </is>
-      </c>
-      <c r="Q148" t="inlineStr">
-        <is>
-          <t>seplan@tjmg.jus.br</t>
-        </is>
-      </c>
-      <c r="R148" t="inlineStr">
-        <is>
-          <t>asplag@tjmg.jus.br</t>
-        </is>
-      </c>
+          <t>Presidência</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr"/>
+      <c r="R148" t="inlineStr"/>
       <c r="S148" t="inlineStr">
         <is>
           <t>Responsável</t>
@@ -33988,36 +33980,28 @@
       </c>
       <c r="U148" t="inlineStr"/>
       <c r="V148" t="inlineStr"/>
-      <c r="W148" t="inlineStr">
-        <is>
-          <t>Cronograma de acompanhamento da Iniciativa 93 - Painel de Gestão Automatizada de Receitas Judiciais</t>
-        </is>
-      </c>
-      <c r="X148" t="inlineStr">
-        <is>
-          <t>Último Valor</t>
-        </is>
-      </c>
+      <c r="W148" t="inlineStr"/>
+      <c r="X148" t="inlineStr"/>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>(atividades concluídas no período / atividades previstas para serem realizadas até dezembro/2025) x 100. Considerando o peso definido para cada uma delas.</t>
+          <t>Conjunto de dados definidos e preparados para disponibilização em formato aberto.</t>
         </is>
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>Sra. Bruna Eduarda Medeiros de Sousa</t>
+          <t>Sra. Ursina Regina Sousa Andrade</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025
-             - 9.29 - Taxa de implantação do Painel de Gestão Automatizada de Receitas Judiciais.</t>
+             - 9.32 - Taxa de conjunto de dados abertos a serem disponibilizados pelo TJMG.</t>
         </is>
       </c>
       <c r="AB148" t="inlineStr"/>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>93 - Painel de gestão Automatizada de Receitas Judiciais.</t>
+          <t>95 - Justiça Sustentável: Implementação da Governança ESG no TJMG.</t>
         </is>
       </c>
       <c r="AD148" t="inlineStr"/>
@@ -34029,11 +34013,7 @@
         </is>
       </c>
       <c r="AH148" t="inlineStr"/>
-      <c r="AI148" t="inlineStr">
-        <is>
-          <t>ASPLAG</t>
-        </is>
-      </c>
+      <c r="AI148" t="inlineStr"/>
       <c r="AJ148" t="inlineStr">
         <is>
           <t>16 - Paz, Justiça e Instituições Eficazes</t>
@@ -34041,22 +34021,22 @@
       </c>
       <c r="AK148" t="inlineStr">
         <is>
-          <t>COAPE , COSIS , DIRFOR , GACOR</t>
+          <t>CECONTI</t>
         </is>
       </c>
       <c r="AL148" t="inlineStr">
         <is>
-          <t>Des. Estevão Lucchesi de Carvalho</t>
+          <t>Dra. Marcela Maria Pereira Amaral Novais.</t>
         </is>
       </c>
       <c r="AM148" t="inlineStr">
         <is>
-          <t>Mensal</t>
+          <t>Anual</t>
         </is>
       </c>
       <c r="AN148" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>PE , PROJEF 5.0</t>
         </is>
       </c>
       <c r="AO148" t="inlineStr">
@@ -34081,19 +34061,15 @@
       </c>
       <c r="AS148" t="inlineStr">
         <is>
-          <t>ASPLAGMETA-2802</t>
+          <t>ASPLAGMETA-2872</t>
         </is>
       </c>
       <c r="AT148" t="inlineStr">
         <is>
-          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2802 Janeiro Apuração Aberto ASPLAGMETA-2803 Fevereiro Apuração Aberto ASPLAGMETA-2804 Março Apuração Aberto ASPLAGMETA-2805 Abril Apuração Aberto ASPLAGMETA-2806 Maio Apuração Aberto ASPLAGMETA-2807 Junho Apuração Aberto ASPLAGMETA-2808 Julho Apuração Aberto ASPLAGMETA-2809 Agosto Apuração Aberto ASPLAGMETA-2810 Setembro Apuração Aberto ASPLAGMETA-2811 Outubro Apuração Aberto ASPLAGMETA-2812 Novembro Apuração Aberto ASPLAGMETA-2813 Dezembro Apuração Aberto ASPLAGMETA-2814 Apurado no período Apuração Aberto</t>
-        </is>
-      </c>
-      <c r="AU148" t="inlineStr">
-        <is>
-          <t>(31) 3237-8229</t>
-        </is>
-      </c>
+          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2872 Janeiro Apuração Aberto ASPLAGMETA-2873 Fevereiro Apuração Aberto ASPLAGMETA-2874 Março Apuração Aberto ASPLAGMETA-2875 Abril Apuração Aberto ASPLAGMETA-2876 Maio Apuração Aberto ASPLAGMETA-2877 Junho Apuração Aberto ASPLAGMETA-2878 Julho Apuração Aberto ASPLAGMETA-2879 Agosto Apuração Aberto ASPLAGMETA-2880 Setembro Apuração Aberto ASPLAGMETA-2881 Outubro Apuração Aberto ASPLAGMETA-2882 Novembro Apuração Aberto ASPLAGMETA-2883 Dezembro Apuração Aberto ASPLAGMETA-2884 Apurado no período Apuração Aberto</t>
+        </is>
+      </c>
+      <c r="AU148" t="inlineStr"/>
       <c r="AV148" t="inlineStr">
         <is>
           <t>Estado</t>
@@ -34106,7 +34082,7 @@
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>SEPLAN</t>
+          <t>SEGOVE</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
@@ -34114,7 +34090,11 @@
           <t>Percentual</t>
         </is>
       </c>
-      <c r="AZ148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="BA148" t="inlineStr">
         <is>
           <t>100</t>
@@ -34146,7 +34126,7 @@
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>[ASPLAGMETA-2787] TJMG 155  – Concluir o estudo Diagnóstico dos 39 cartórios judiciais da Segunda Instância até 19 de dezembro de 2025.</t>
+          <t>[ASPLAGMETA-2857] TJMG 153 - Ofertar pelo menos 04 (quatro) turmas dos cursos voltados para a gestão socioambiental e realizar 05 (cinco) campanhas ou ações de sensibilização sobre a temática até dezembro de 2025.</t>
         </is>
       </c>
       <c r="F149" t="inlineStr"/>
@@ -34160,7 +34140,11 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr"/>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Diretora</t>
+        </is>
+      </c>
       <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr">
         <is>
@@ -34169,19 +34153,15 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>Valéria Areal Guerra Soares</t>
-        </is>
-      </c>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
+          <t>Bárbara Oliveira</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr"/>
       <c r="N149" t="inlineStr"/>
       <c r="O149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>1ª Vice Presidência</t>
+          <t>Presidência</t>
         </is>
       </c>
       <c r="Q149" t="inlineStr"/>
@@ -34198,25 +34178,38 @@
       </c>
       <c r="U149" t="inlineStr"/>
       <c r="V149" t="inlineStr"/>
-      <c r="W149" t="inlineStr">
-        <is>
-          <t>Resultado = Nº de Cartórios Judiciais em que foi realizado o diagnóstico/ 39 cartórios X 100</t>
-        </is>
-      </c>
-      <c r="X149" t="inlineStr">
-        <is>
-          <t>Último Valor</t>
-        </is>
-      </c>
-      <c r="Y149" t="inlineStr"/>
-      <c r="Z149" t="inlineStr"/>
-      <c r="AA149" t="inlineStr"/>
+      <c r="W149" t="inlineStr"/>
+      <c r="X149" t="inlineStr"/>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>Somatório dos cursos e somatório das ações de sensibilização.</t>
+        </is>
+      </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>Sra. Selmara Alves Fernades</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>2025
+             - 9.31 - Quantidade de cursos e ações de sensibilização para a gestão socioambiental.</t>
+        </is>
+      </c>
       <c r="AB149" t="inlineStr"/>
-      <c r="AC149" t="inlineStr"/>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>95 - Justiça Sustentável: Implementação da Governança ESG no TJMG.</t>
+        </is>
+      </c>
       <c r="AD149" t="inlineStr"/>
       <c r="AE149" t="inlineStr"/>
       <c r="AF149" t="inlineStr"/>
-      <c r="AG149" t="inlineStr"/>
+      <c r="AG149" t="inlineStr">
+        <is>
+          <t>9 - Aprimoramento da Gestão Administrativa e da Governança Judiciária</t>
+        </is>
+      </c>
       <c r="AH149" t="inlineStr"/>
       <c r="AI149" t="inlineStr"/>
       <c r="AJ149" t="inlineStr">
@@ -34225,15 +34218,19 @@
         </is>
       </c>
       <c r="AK149" t="inlineStr"/>
-      <c r="AL149" t="inlineStr"/>
+      <c r="AL149" t="inlineStr">
+        <is>
+          <t>Desa. Mônica Libânio Rocha Bretas</t>
+        </is>
+      </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>Mensal</t>
+          <t>Anual</t>
         </is>
       </c>
       <c r="AN149" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>PE , PROJEF 5.0</t>
         </is>
       </c>
       <c r="AO149" t="inlineStr">
@@ -34258,12 +34255,12 @@
       </c>
       <c r="AS149" t="inlineStr">
         <is>
-          <t>ASPLAGMETA-2788</t>
+          <t>ASPLAGMETA-2858</t>
         </is>
       </c>
       <c r="AT149" t="inlineStr">
         <is>
-          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2788 Janeiro Apuração Aberto ASPLAGMETA-2789 Fevereiro Apuração Aberto ASPLAGMETA-2790 Março Apuração Aberto ASPLAGMETA-2791 Abril Apuração Aberto ASPLAGMETA-2792 Maio Apuração Aberto ASPLAGMETA-2793 Junho Apuração Aberto ASPLAGMETA-2794 Julho Apuração Aberto ASPLAGMETA-2795 Agosto Apuração Aberto ASPLAGMETA-2796 Setembro Apuração Aberto ASPLAGMETA-2797 Outubro Apuração Aberto ASPLAGMETA-2798 Novembro Apuração Aberto ASPLAGMETA-2799 Dezembro Apuração Aberto ASPLAGMETA-2800 Apurado no período Apuração Aberto</t>
+          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2858 Janeiro Apuração Aberto ASPLAGMETA-2859 Fevereiro Apuração Aberto ASPLAGMETA-2860 Março Apuração Aberto ASPLAGMETA-2861 Abril Apuração Aberto ASPLAGMETA-2862 Maio Apuração Aberto ASPLAGMETA-2863 Junho Apuração Aberto ASPLAGMETA-2864 Julho Apuração Aberto ASPLAGMETA-2865 Agosto Apuração Aberto ASPLAGMETA-2866 Setembro Apuração Aberto ASPLAGMETA-2867 Outubro Apuração Aberto ASPLAGMETA-2868 Novembro Apuração Aberto ASPLAGMETA-2869 Dezembro Apuração Aberto ASPLAGMETA-2870 Apurado no período Apuração Aberto</t>
         </is>
       </c>
       <c r="AU149" t="inlineStr"/>
@@ -34279,7 +34276,7 @@
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Superintendência Judiciária</t>
+          <t>CESUS</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
@@ -34290,7 +34287,7 @@
       <c r="AZ149" t="inlineStr"/>
       <c r="BA149" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>9</t>
         </is>
       </c>
       <c r="BB149" t="inlineStr">
@@ -34319,7 +34316,7 @@
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>[ASPLAGMETA-2773] TJMG 156 - Implantar o eproc em 84 (oitenta e quatro) comarcas do Interior com competência cível lato sensu, conforme os ciclos previstos na Portaria Conjunta nº 1.681/2025, até dezembro de 2025.</t>
+          <t>[ASPLAGMETA-2843] TJMG 152 - Elaborar, em 2025, o Plano inicial de descarbonização do TJMG (100% cem porcento). (após concepção de relatório de inventário).</t>
         </is>
       </c>
       <c r="F150" t="inlineStr"/>
@@ -34333,16 +34330,20 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="I150" t="inlineStr"/>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Diretora</t>
+        </is>
+      </c>
       <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr">
         <is>
-          <t>Aline , Plano Estratégico 2025</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>ASPLAG/TJMG</t>
+          <t>Bárbara Oliveira</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -34371,32 +34372,28 @@
       </c>
       <c r="U150" t="inlineStr"/>
       <c r="V150" t="inlineStr"/>
-      <c r="W150" t="inlineStr">
-        <is>
-          <t>DIRTEC</t>
-        </is>
-      </c>
-      <c r="X150" t="inlineStr">
-        <is>
-          <t>Soma</t>
-        </is>
-      </c>
+      <c r="W150" t="inlineStr"/>
+      <c r="X150" t="inlineStr"/>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>Σ comarcas com competência cível lato sensu contempladas com a instalação do sistema eproc.</t>
-        </is>
-      </c>
-      <c r="Z150" t="inlineStr"/>
+          <t>Documento elaborado e aprovado contendo o Plano Inicial de descarbonização.</t>
+        </is>
+      </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>Sra. Selmara Alves Fernades</t>
+        </is>
+      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025
-             - 3.69 - Número de comarcas do interior com competência cível lato senso com o eproc implantado.</t>
+             - 9.30 - Taxa de criação do Plano Inicial de Descarbonização do TJMG.</t>
         </is>
       </c>
       <c r="AB150" t="inlineStr"/>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>87 - Programa Estadual de Governança Estratégica de Unidades Judiciárias - Implantação do Sistema Eletrônico para Tramitação de Processos Judiciais Eproc.</t>
+          <t>95 - Justiça Sustentável: Implementação da Governança ESG no TJMG.</t>
         </is>
       </c>
       <c r="AD150" t="inlineStr"/>
@@ -34404,7 +34401,7 @@
       <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="inlineStr">
         <is>
-          <t>3 - Agilidade e Produtividade na Prestação Jurisdicional</t>
+          <t>9 - Aprimoramento da Gestão Administrativa e da Governança Judiciária</t>
         </is>
       </c>
       <c r="AH150" t="inlineStr"/>
@@ -34414,20 +34411,20 @@
           <t>16 - Paz, Justiça e Instituições Eficazes</t>
         </is>
       </c>
-      <c r="AK150" t="inlineStr">
-        <is>
-          <t>SEGOVE</t>
-        </is>
-      </c>
-      <c r="AL150" t="inlineStr"/>
+      <c r="AK150" t="inlineStr"/>
+      <c r="AL150" t="inlineStr">
+        <is>
+          <t>Desa. Mônica Libânio Rocha Bretas</t>
+        </is>
+      </c>
       <c r="AM150" t="inlineStr">
         <is>
-          <t>Mensal</t>
+          <t>Anual</t>
         </is>
       </c>
       <c r="AN150" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>PE , PROJEF 5.0</t>
         </is>
       </c>
       <c r="AO150" t="inlineStr">
@@ -34452,12 +34449,12 @@
       </c>
       <c r="AS150" t="inlineStr">
         <is>
-          <t>ASPLAGMETA-2774</t>
+          <t>ASPLAGMETA-2844</t>
         </is>
       </c>
       <c r="AT150" t="inlineStr">
         <is>
-          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2774 Janeiro Apuração Aberto ASPLAGMETA-2775 Fevereiro Apuração Aberto ASPLAGMETA-2776 Março Apuração Aberto ASPLAGMETA-2777 Abril Apuração Aberto ASPLAGMETA-2778 Maio Apuração Aberto ASPLAGMETA-2779 Junho Apuração Aberto ASPLAGMETA-2780 Julho Apuração Aberto ASPLAGMETA-2781 Agosto Apuração Aberto ASPLAGMETA-2782 Setembro Apuração Aberto ASPLAGMETA-2783 Outubro Apuração Aberto ASPLAGMETA-2784 Novembro Apuração Aberto ASPLAGMETA-2785 Dezembro Apuração Aberto ASPLAGMETA-2786 Apurado no período Apuração Aberto</t>
+          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2844 Janeiro Apuração Aberto ASPLAGMETA-2845 Fevereiro Apuração Aberto ASPLAGMETA-2846 Março Apuração Aberto ASPLAGMETA-2847 Abril Apuração Aberto ASPLAGMETA-2848 Maio Apuração Aberto ASPLAGMETA-2849 Junho Apuração Aberto ASPLAGMETA-2850 Julho Apuração Aberto ASPLAGMETA-2851 Agosto Apuração Aberto ASPLAGMETA-2852 Setembro Apuração Aberto ASPLAGMETA-2853 Outubro Apuração Aberto ASPLAGMETA-2854 Novembro Apuração Aberto ASPLAGMETA-2855 Dezembro Apuração Aberto ASPLAGMETA-2856 Apurado no período Apuração Aberto</t>
         </is>
       </c>
       <c r="AU150" t="inlineStr"/>
@@ -34473,18 +34470,18 @@
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>DIRTEC</t>
+          <t>CESUS</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
         <is>
-          <t>Unidade</t>
+          <t>Percentual</t>
         </is>
       </c>
       <c r="AZ150" t="inlineStr"/>
       <c r="BA150" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>100</t>
         </is>
       </c>
       <c r="BB150" t="inlineStr">
@@ -34513,7 +34510,7 @@
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>[ASPLAGMETA-2142] TJMG 137 - Concluir, até 19/12/2025, 40% do projeto de implantação Sistema de Gestão Financeira dos Depósitos Judiciais – SIDEJUD.</t>
+          <t>[ASPLAGMETA-2829] TJMG 151 – Publicar, no Portal TJMG, 2 (dois) boletins de informação à sociedade, até dezembro de 2025.</t>
         </is>
       </c>
       <c r="F151" t="inlineStr"/>
@@ -34527,11 +34524,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>Gerente</t>
-        </is>
-      </c>
+      <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr">
         <is>
@@ -34540,26 +34533,22 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>ASPLAG/TJMG</t>
+          <t>Bárbara Oliveira</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="N151" t="inlineStr"/>
       <c r="O151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Presidência</t>
-        </is>
-      </c>
-      <c r="Q151" t="inlineStr">
-        <is>
-          <t>viviane.cafaro@tjmg.jus.br</t>
-        </is>
-      </c>
+          <t>2ª Vice Presidência</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr"/>
       <c r="R151" t="inlineStr"/>
       <c r="S151" t="inlineStr">
         <is>
@@ -34573,11 +34562,7 @@
       </c>
       <c r="U151" t="inlineStr"/>
       <c r="V151" t="inlineStr"/>
-      <c r="W151" t="inlineStr">
-        <is>
-          <t>Cronograma da iniciativa estratégica</t>
-        </is>
-      </c>
+      <c r="W151" t="inlineStr"/>
       <c r="X151" t="inlineStr">
         <is>
           <t>Último Valor</t>
@@ -34585,40 +34570,28 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>Somatório das entregas relativas ao Módulo de Depósitos Judiciais homologadas pela DIRFIN em 2025.</t>
-        </is>
-      </c>
-      <c r="Z151" t="inlineStr">
-        <is>
-          <t>Viviane de Lima Cafaro</t>
-        </is>
-      </c>
+          <t>Quantidade de boletins publicados até dezembro de 2025</t>
+        </is>
+      </c>
+      <c r="Z151" t="inlineStr"/>
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025
-             - 11.2 - Taxa de cumprimento do "Projeto de Implantação do Sistema de Gestão Financeira dos Depósitos Judiciais - SIDEJUD".</t>
+             - 2.6 - Número de boletins publicados no portal TJMG.</t>
         </is>
       </c>
       <c r="AB151" t="inlineStr"/>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>57 - Implantação do Sistema de Gestão Financeira dos Depósitos Judiciais – SIDEJUD.</t>
-        </is>
-      </c>
-      <c r="AD151" t="inlineStr">
-        <is>
-          <t>2025-05-21</t>
-        </is>
-      </c>
-      <c r="AE151" t="inlineStr">
-        <is>
-          <t>2025-05-21</t>
-        </is>
-      </c>
+          <t>95 - Justiça Sustentável: Implementação da Governança ESG no TJMG.</t>
+        </is>
+      </c>
+      <c r="AD151" t="inlineStr"/>
+      <c r="AE151" t="inlineStr"/>
       <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="inlineStr">
         <is>
-          <t>11 - Modernização da Gestão Orçamentária e Financeira</t>
+          <t>2 - Ampliação da Relação Institucional do Judiciário com a Sociedade</t>
         </is>
       </c>
       <c r="AH151" t="inlineStr"/>
@@ -34630,22 +34603,22 @@
       </c>
       <c r="AK151" t="inlineStr">
         <is>
-          <t>DIRFOR</t>
+          <t>GEJUR</t>
         </is>
       </c>
       <c r="AL151" t="inlineStr">
         <is>
-          <t>Eduardo Antônio Codo</t>
+          <t>Dra. Marcela Maria Pereira Amaral Novais</t>
         </is>
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>Mensal</t>
+          <t>Anual</t>
         </is>
       </c>
       <c r="AN151" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>PE , PROJEF 5.0</t>
         </is>
       </c>
       <c r="AO151" t="inlineStr">
@@ -34670,19 +34643,15 @@
       </c>
       <c r="AS151" t="inlineStr">
         <is>
-          <t>ASPLAGMETA-2188</t>
+          <t>ASPLAGMETA-2830</t>
         </is>
       </c>
       <c r="AT151" t="inlineStr">
         <is>
-          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2188 Janeiro Apuração Aberto ASPLAGMETA-2193 Feveiro Apuração Aberto ASPLAGMETA-2195 Março Apuração Aberto ASPLAGMETA-2198 Abril Apuração Aberto ASPLAGMETA-2201 Maio Apuração Aberto ASPLAGMETA-2203 Junho Apuração Aberto ASPLAGMETA-2205 Julho Apuração Aberto ASPLAGMETA-2206 Agosto Apuração Aberto ASPLAGMETA-2207 Setembro Apuração Aberto ASPLAGMETA-2208 Outubro Apuração Aberto ASPLAGMETA-2210 Novembro Apuração Aberto ASPLAGMETA-2211 Dezembro Apuração Aberto ASPLAGMETA-2214 Apurado no período Apuração Aberto</t>
-        </is>
-      </c>
-      <c r="AU151" t="inlineStr">
-        <is>
-          <t>31 3207.7965</t>
-        </is>
-      </c>
+          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2830 Janeiro Apuração Aberto ASPLAGMETA-2831 Fevereiro Apuração Aberto ASPLAGMETA-2832 Março Apuração Aberto ASPLAGMETA-2833 Abril Apuração Aberto ASPLAGMETA-2834 Maio Apuração Aberto ASPLAGMETA-2835 Junho Apuração Aberto ASPLAGMETA-2836 Julho Apuração Aberto ASPLAGMETA-2837 Agosto Apuração Aberto ASPLAGMETA-2838 Setembro Apuração Aberto ASPLAGMETA-2839 Outubro Apuração Aberto ASPLAGMETA-2840 Novembro Apuração Aberto ASPLAGMETA-2841 Dezembro Apuração Aberto ASPLAGMETA-2842 Apurado no período Apuração Aberto</t>
+        </is>
+      </c>
+      <c r="AU151" t="inlineStr"/>
       <c r="AV151" t="inlineStr">
         <is>
           <t>Estado</t>
@@ -34695,18 +34664,18 @@
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>DIRFIN</t>
+          <t>DIRGED</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
         <is>
-          <t>Percentual</t>
+          <t>Unidade</t>
         </is>
       </c>
       <c r="AZ151" t="inlineStr"/>
       <c r="BA151" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>2</t>
         </is>
       </c>
       <c r="BB151" t="inlineStr">
@@ -34735,7 +34704,7 @@
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>[ASPLAGMETA-2141] TJMG 69 - Cumprir, até 31/12/2025, 90% (noventa por cento) das atividades relacionadas ao Projeto de Gestão de Receitas do TJMG previstas para o ano de 2025.</t>
+          <t>[ASPLAGMETA-2815] TJMG 150 – Garantir, no ano de 2025, a reserva de vagas para pessoas em condição de vulnerabilidade em pelo menos 01 (um) contrato de prestação de serviços continuados e terceirizados.</t>
         </is>
       </c>
       <c r="F152" t="inlineStr"/>
@@ -34762,12 +34731,12 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>ASPLAG/TJMG</t>
+          <t>Bárbara Oliveira</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="N152" t="inlineStr"/>
@@ -34791,11 +34760,7 @@
       </c>
       <c r="U152" t="inlineStr"/>
       <c r="V152" t="inlineStr"/>
-      <c r="W152" t="inlineStr">
-        <is>
-          <t>Cronograma da iniciativa estratégica.</t>
-        </is>
-      </c>
+      <c r="W152" t="inlineStr"/>
       <c r="X152" t="inlineStr">
         <is>
           <t>Último Valor</t>
@@ -34803,40 +34768,32 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>∑ atividades executadas em 2025 / ∑ atividades previstas para conclusão em 2025.</t>
+          <t>Somatório do número de contratos</t>
         </is>
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>Leonardo Honorio Rodrigues</t>
+          <t>Sra. Luiza Augusta de Souza</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025
-             - 11.3 - Taxa de cumprimento das atividades relacionadas ao Projeto de Gestão de Receitas do TJMG.</t>
+             - 1.21 - Número de contratos com reserva de vagas para pessoas em condição de vulnerabilidade.</t>
         </is>
       </c>
       <c r="AB152" t="inlineStr"/>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>55 - Gestão de Receitas do TJMG.</t>
-        </is>
-      </c>
-      <c r="AD152" t="inlineStr">
-        <is>
-          <t>2025-05-21</t>
-        </is>
-      </c>
-      <c r="AE152" t="inlineStr">
-        <is>
-          <t>2025-05-21</t>
-        </is>
-      </c>
+          <t>95 - Justiça Sustentável: Implementação da Governança ESG no TJMG.</t>
+        </is>
+      </c>
+      <c r="AD152" t="inlineStr"/>
+      <c r="AE152" t="inlineStr"/>
       <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="inlineStr">
         <is>
-          <t>11 - Modernização da Gestão Orçamentária e Financeira</t>
+          <t>1 - Garantia dos Direitos Fundamentais e do Estado Democrático de Direito</t>
         </is>
       </c>
       <c r="AH152" t="inlineStr"/>
@@ -34846,20 +34803,24 @@
           <t>16 - Paz, Justiça e Instituições Eficazes</t>
         </is>
       </c>
-      <c r="AK152" t="inlineStr"/>
+      <c r="AK152" t="inlineStr">
+        <is>
+          <t>GESEG</t>
+        </is>
+      </c>
       <c r="AL152" t="inlineStr">
         <is>
-          <t>Eduardo Antonio Codo Santos</t>
+          <t>Dra. Marcela Maria Pereira Amaral Novais.</t>
         </is>
       </c>
       <c r="AM152" t="inlineStr">
         <is>
-          <t>Mensal</t>
+          <t>Anual</t>
         </is>
       </c>
       <c r="AN152" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>PE , PROJEF 5.0</t>
         </is>
       </c>
       <c r="AO152" t="inlineStr">
@@ -34884,12 +34845,12 @@
       </c>
       <c r="AS152" t="inlineStr">
         <is>
-          <t>ASPLAGMETA-2217</t>
+          <t>ASPLAGMETA-2816</t>
         </is>
       </c>
       <c r="AT152" t="inlineStr">
         <is>
-          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2217 Janeiro Apuração Aberto ASPLAGMETA-2219 Fevereiro Apuração Aberto ASPLAGMETA-2221 Março Apuração Aberto ASPLAGMETA-2223 Abril Apuração Aberto ASPLAGMETA-2225 Maio Apuração Aberto ASPLAGMETA-2227 Junho Apuração Aberto ASPLAGMETA-2231 Julho Apuração Aberto ASPLAGMETA-2232 Agosto Apuração Aberto ASPLAGMETA-2233 Setembro Apuração Aberto ASPLAGMETA-2234 Outubro Apuração Aberto ASPLAGMETA-2235 Novembro Apuração Aberto ASPLAGMETA-2236 Dezembro Apuração Aberto ASPLAGMETA-2237 Apurado no período Apuração Aberto</t>
+          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2816 Janeiro Apuração Aberto ASPLAGMETA-2817 Fevereiro Apuração Aberto ASPLAGMETA-2818 Março Apuração Aberto ASPLAGMETA-2819 Abril Apuração Aberto ASPLAGMETA-2820 Maio Apuração Aberto ASPLAGMETA-2821 Junho Apuração Aberto ASPLAGMETA-2822 Julho Apuração Aberto ASPLAGMETA-2823 Agosto Apuração Aberto ASPLAGMETA-2824 Setembro Apuração Aberto ASPLAGMETA-2825 Outubro Apuração Aberto ASPLAGMETA-2826 Novembro Apuração Aberto ASPLAGMETA-2827 Dezembro Apuração Aberto ASPLAGMETA-2828 Apurado no período Apuração Aberto</t>
         </is>
       </c>
       <c r="AU152" t="inlineStr"/>
@@ -34905,18 +34866,18 @@
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>DIRFIN</t>
+          <t>DIRSEP</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>Percentual</t>
+          <t>Unidade</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr"/>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>1</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
@@ -34945,7 +34906,7 @@
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>[ASPLAGMETA-2140] TJMG 104 - Executar, em 2025, 100% (cem por cento) das atividades previstas para o ano para a implementação da Política de Prevenção e Enfrentamento ao Assédio Moral, Assédio Sexual e Discriminação no âmbito da Justiça de Primeira e Segunda Instâncias.</t>
+          <t>[ASPLAGMETA-2801] TJMG 129 - Executar 100% (cem por cento) do projeto de Painel de Gestão Automatizada de Receitas Judiciais até dezembro de 2025.</t>
         </is>
       </c>
       <c r="F153" t="inlineStr"/>
@@ -34959,32 +34920,44 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="I153" t="inlineStr"/>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Diretora de Secretaria</t>
+        </is>
+      </c>
       <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr">
         <is>
-          <t>Plano Estratégico 2025</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>ASPLAG/TJMG</t>
+          <t>Bárbara Oliveira</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="N153" t="inlineStr"/>
       <c r="O153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Presidência</t>
-        </is>
-      </c>
-      <c r="Q153" t="inlineStr"/>
-      <c r="R153" t="inlineStr"/>
+          <t>Corregedoria</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>seplan@tjmg.jus.br</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>asplag@tjmg.jus.br</t>
+        </is>
+      </c>
       <c r="S153" t="inlineStr">
         <is>
           <t>Responsável</t>
@@ -34997,7 +34970,11 @@
       </c>
       <c r="U153" t="inlineStr"/>
       <c r="V153" t="inlineStr"/>
-      <c r="W153" t="inlineStr"/>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>Cronograma de acompanhamento da Iniciativa 93 - Painel de Gestão Automatizada de Receitas Judiciais</t>
+        </is>
+      </c>
       <c r="X153" t="inlineStr">
         <is>
           <t>Último Valor</t>
@@ -35005,58 +34982,58 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>Total de Atividades Implementadas/ Total das Atividades previstas x 100.</t>
+          <t>(atividades concluídas no período / atividades previstas para serem realizadas até dezembro/2025) x 100. Considerando o peso definido para cada uma delas.</t>
         </is>
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>Coordenadores dos Comitês de Primeira e Segunda Instâncias</t>
+          <t>Sra. Bruna Eduarda Medeiros de Sousa</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025
-             - 5.6 - Número de procedimentos pré-processuais de reconhecimento de paternidade tratados no âmbito dos Centros Judiciários de Solução de Conflitos e Cidadania no setor pré-processual ou no programa Paternidade para Todos.</t>
+             - 9.29 - Taxa de implantação do Painel de Gestão Automatizada de Receitas Judiciais.</t>
         </is>
       </c>
       <c r="AB153" t="inlineStr"/>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>78 - Implementação de Política de Prevenção e Enfrentamento ao Assédio Moral, Assédio Sexual e Discriminação.</t>
-        </is>
-      </c>
-      <c r="AD153" t="inlineStr">
-        <is>
-          <t>2025-05-21</t>
-        </is>
-      </c>
-      <c r="AE153" t="inlineStr">
-        <is>
-          <t>2025-05-21</t>
-        </is>
-      </c>
+          <t>93 - Painel de gestão Automatizada de Receitas Judiciais.</t>
+        </is>
+      </c>
+      <c r="AD153" t="inlineStr"/>
+      <c r="AE153" t="inlineStr"/>
       <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="inlineStr">
         <is>
-          <t>10 - Otimização da Gestão de Pessoas</t>
+          <t>9 - Aprimoramento da Gestão Administrativa e da Governança Judiciária</t>
         </is>
       </c>
       <c r="AH153" t="inlineStr"/>
-      <c r="AI153" t="inlineStr"/>
+      <c r="AI153" t="inlineStr">
+        <is>
+          <t>ASPLAG</t>
+        </is>
+      </c>
       <c r="AJ153" t="inlineStr">
         <is>
           <t>16 - Paz, Justiça e Instituições Eficazes</t>
         </is>
       </c>
-      <c r="AK153" t="inlineStr"/>
+      <c r="AK153" t="inlineStr">
+        <is>
+          <t>COAPE , COSIS , DIRFOR , GACOR</t>
+        </is>
+      </c>
       <c r="AL153" t="inlineStr">
         <is>
-          <t>Desembargador Pedro Bernardes de Oliveira</t>
+          <t>Des. Estevão Lucchesi de Carvalho</t>
         </is>
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>Trimestral</t>
+          <t>Mensal</t>
         </is>
       </c>
       <c r="AN153" t="inlineStr">
@@ -35086,15 +35063,19 @@
       </c>
       <c r="AS153" t="inlineStr">
         <is>
-          <t>ASPLAGMETA-2238</t>
+          <t>ASPLAGMETA-2802</t>
         </is>
       </c>
       <c r="AT153" t="inlineStr">
         <is>
-          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2238 Janeiro Apuração Aberto ASPLAGMETA-2239 Fevereiro Apuração Aberto ASPLAGMETA-2240 Março Apuração Aberto ASPLAGMETA-2242 Abril Apuração Aberto ASPLAGMETA-2244 Maio Apuração Aberto ASPLAGMETA-2245 Junho Apuração Aberto ASPLAGMETA-2247 Julho Apuração Aberto ASPLAGMETA-2249 Agosto Apuração Aberto ASPLAGMETA-2251 Setembro Apuração Aberto ASPLAGMETA-2253 Outubro Apuração Aberto ASPLAGMETA-2255 Novembro Apuração Aberto ASPLAGMETA-2257 Dezembro Apuração Aberto ASPLAGMETA-2259 Apurado no período Apuração Aberto</t>
-        </is>
-      </c>
-      <c r="AU153" t="inlineStr"/>
+          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2802 Janeiro Apuração Aberto ASPLAGMETA-2803 Fevereiro Apuração Aberto ASPLAGMETA-2804 Março Apuração Aberto ASPLAGMETA-2805 Abril Apuração Aberto ASPLAGMETA-2806 Maio Apuração Aberto ASPLAGMETA-2807 Junho Apuração Aberto ASPLAGMETA-2808 Julho Apuração Aberto ASPLAGMETA-2809 Agosto Apuração Aberto ASPLAGMETA-2810 Setembro Apuração Aberto ASPLAGMETA-2811 Outubro Apuração Aberto ASPLAGMETA-2812 Novembro Apuração Aberto ASPLAGMETA-2813 Dezembro Apuração Aberto ASPLAGMETA-2814 Apurado no período Apuração Aberto</t>
+        </is>
+      </c>
+      <c r="AU153" t="inlineStr">
+        <is>
+          <t>(31) 3237-8229</t>
+        </is>
+      </c>
       <c r="AV153" t="inlineStr">
         <is>
           <t>Estado</t>
@@ -35107,7 +35088,7 @@
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Presidência</t>
+          <t>SEPLAN</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
@@ -35147,7 +35128,7 @@
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
-          <t>[ASPLAGMETA-2139] TJMG 67 - Cumprir, até o final de 2025, 94% (noventa e quatro por cento) das etapas/entregas de consolidação do Programa de Pós-Graduação da EJEF previstas para o período de 2021-2026.</t>
+          <t>[ASPLAGMETA-2787] TJMG 155  – Concluir o estudo Diagnóstico dos 39 cartórios judiciais da Segunda Instância até 19 de dezembro de 2025.</t>
         </is>
       </c>
       <c r="F154" t="inlineStr"/>
@@ -35165,24 +35146,24 @@
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr">
         <is>
-          <t>Plano Estratégico 2025</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>ASPLAG/TJMG</t>
+          <t>Valéria Areal Guerra Soares</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="N154" t="inlineStr"/>
       <c r="O154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>2ª Vice Presidência</t>
+          <t>1ª Vice Presidência</t>
         </is>
       </c>
       <c r="Q154" t="inlineStr"/>
@@ -35199,50 +35180,25 @@
       </c>
       <c r="U154" t="inlineStr"/>
       <c r="V154" t="inlineStr"/>
-      <c r="W154" t="inlineStr"/>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>Resultado = Nº de Cartórios Judiciais em que foi realizado o diagnóstico/ 39 cartórios X 100</t>
+        </is>
+      </c>
       <c r="X154" t="inlineStr">
         <is>
           <t>Último Valor</t>
         </is>
       </c>
-      <c r="Y154" t="inlineStr">
-        <is>
-          <t>∑ECC / ECP x 100, onde: ECC = Quantidade de etapas de consolidação dos programas de pós-graduação cumpridas até o ano considerado; ECP = Quantidade total de etapas de consolidação dos programas de pós-graduação planejadas para o período de 2021-2026. Obs: para fins de monitoramento pelo cronograma da iniciativa, as etapas de consolidação equivalem às entregas definidas no cronograma.</t>
-        </is>
-      </c>
-      <c r="Z154" t="inlineStr">
-        <is>
-          <t>Maiana Silva Carvalho</t>
-        </is>
-      </c>
-      <c r="AA154" t="inlineStr">
-        <is>
-          <t>2025
-             - 10.5 - Taxa de consolidação do Programa de Pós-Graduação da Escola Judicial Desembargador Edésio Fernandes.</t>
-        </is>
-      </c>
+      <c r="Y154" t="inlineStr"/>
+      <c r="Z154" t="inlineStr"/>
+      <c r="AA154" t="inlineStr"/>
       <c r="AB154" t="inlineStr"/>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>50 - Plano de Desenvolvimento Institucional da EJEF ciclo 2021 a 2026 - Programa Pós-Graduação da EJEF.</t>
-        </is>
-      </c>
-      <c r="AD154" t="inlineStr">
-        <is>
-          <t>2025-05-21</t>
-        </is>
-      </c>
-      <c r="AE154" t="inlineStr">
-        <is>
-          <t>2025-05-21</t>
-        </is>
-      </c>
+      <c r="AC154" t="inlineStr"/>
+      <c r="AD154" t="inlineStr"/>
+      <c r="AE154" t="inlineStr"/>
       <c r="AF154" t="inlineStr"/>
-      <c r="AG154" t="inlineStr">
-        <is>
-          <t>10 - Otimização da Gestão de Pessoas</t>
-        </is>
-      </c>
+      <c r="AG154" t="inlineStr"/>
       <c r="AH154" t="inlineStr"/>
       <c r="AI154" t="inlineStr"/>
       <c r="AJ154" t="inlineStr">
@@ -35250,19 +35206,11 @@
           <t>16 - Paz, Justiça e Instituições Eficazes</t>
         </is>
       </c>
-      <c r="AK154" t="inlineStr">
-        <is>
-          <t>DEPLAG , DIRCOM , DIRDEP , DIRGED , DIRSEP</t>
-        </is>
-      </c>
-      <c r="AL154" t="inlineStr">
-        <is>
-          <t>Dr. Thiago Grazziane Gandra</t>
-        </is>
-      </c>
+      <c r="AK154" t="inlineStr"/>
+      <c r="AL154" t="inlineStr"/>
       <c r="AM154" t="inlineStr">
         <is>
-          <t>Trimestral</t>
+          <t>Mensal</t>
         </is>
       </c>
       <c r="AN154" t="inlineStr">
@@ -35292,12 +35240,12 @@
       </c>
       <c r="AS154" t="inlineStr">
         <is>
-          <t>ASPLAGMETA-2347</t>
+          <t>ASPLAGMETA-2788</t>
         </is>
       </c>
       <c r="AT154" t="inlineStr">
         <is>
-          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2347 Janeiro Apuração Aberto ASPLAGMETA-2350 Fevereiro Apuração Aberto ASPLAGMETA-2353 Março Apuração Aberto ASPLAGMETA-2355 Abril Apuração Aberto ASPLAGMETA-2356 Maio Apuração Aberto ASPLAGMETA-2358 Junho Apuração Aberto ASPLAGMETA-2359 Julho Apuração Aberto ASPLAGMETA-2361 Agosto Apuração Aberto ASPLAGMETA-2363 Setembro Apuração Aberto ASPLAGMETA-2365 Outubro Apuração Aberto ASPLAGMETA-2369 Novembro Apuração Aberto ASPLAGMETA-2371 Dezembro Apuração Aberto ASPLAGMETA-2373 Apurado no período Apuração Aberto</t>
+          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2788 Janeiro Apuração Aberto ASPLAGMETA-2789 Fevereiro Apuração Aberto ASPLAGMETA-2790 Março Apuração Aberto ASPLAGMETA-2791 Abril Apuração Aberto ASPLAGMETA-2792 Maio Apuração Aberto ASPLAGMETA-2793 Junho Apuração Aberto ASPLAGMETA-2794 Julho Apuração Aberto ASPLAGMETA-2795 Agosto Apuração Aberto ASPLAGMETA-2796 Setembro Apuração Aberto ASPLAGMETA-2797 Outubro Apuração Aberto ASPLAGMETA-2798 Novembro Apuração Aberto ASPLAGMETA-2799 Dezembro Apuração Aberto ASPLAGMETA-2800 Apurado no período Apuração Aberto</t>
         </is>
       </c>
       <c r="AU154" t="inlineStr"/>
@@ -35313,18 +35261,18 @@
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>2ª Vice Presidência</t>
+          <t>Superintendência Judiciária</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
         <is>
-          <t>Percentual</t>
+          <t>Unidade</t>
         </is>
       </c>
       <c r="AZ154" t="inlineStr"/>
       <c r="BA154" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>39</t>
         </is>
       </c>
       <c r="BB154" t="inlineStr">
@@ -35353,7 +35301,7 @@
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>[ASPLAGMETA-2138] TJMG 136 - Colocar, pelo menos, 1 (um) Mínimo Produto Viável (MVP) relativo ao Sistema de Gestão Financeira e Orçamentária em produção até 31/10/2025.</t>
+          <t>[ASPLAGMETA-2773] TJMG 156 - Implantar o eproc em 84 (oitenta e quatro) comarcas do Interior com competência cível lato sensu, conforme os ciclos previstos na Portaria Conjunta nº 1.681/2025, até dezembro de 2025.</t>
         </is>
       </c>
       <c r="F155" t="inlineStr"/>
@@ -35367,15 +35315,11 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>Comitê</t>
-        </is>
-      </c>
+      <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr">
         <is>
-          <t>Plano Estratégico 2025</t>
+          <t>Aline , Plano Estratégico 2025</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -35383,7 +35327,11 @@
           <t>ASPLAG/TJMG</t>
         </is>
       </c>
-      <c r="M155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
       <c r="N155" t="inlineStr"/>
       <c r="O155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
@@ -35407,7 +35355,7 @@
       <c r="V155" t="inlineStr"/>
       <c r="W155" t="inlineStr">
         <is>
-          <t>Comitê Tático do PMGFO</t>
+          <t>DIRTEC</t>
         </is>
       </c>
       <c r="X155" t="inlineStr">
@@ -35417,40 +35365,28 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>Somatório do número de MVP’s colocados em produção no ano vigente.</t>
-        </is>
-      </c>
-      <c r="Z155" t="inlineStr">
-        <is>
-          <t>Comitê Tático</t>
-        </is>
-      </c>
+          <t>Σ comarcas com competência cível lato sensu contempladas com a instalação do sistema eproc.</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr"/>
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025
-             - 11.8 - Número de MVPs relativo ao Sistema de Gestão Financeira e Orçamentária colocados em produção.</t>
+             - 3.69 - Número de comarcas do interior com competência cível lato senso com o eproc implantado.</t>
         </is>
       </c>
       <c r="AB155" t="inlineStr"/>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>88 - Programa de Soluções Tecnológicas para Modernização da Gestão Financeira e Orçamentária do TJMG.</t>
-        </is>
-      </c>
-      <c r="AD155" t="inlineStr">
-        <is>
-          <t>2025-05-21</t>
-        </is>
-      </c>
-      <c r="AE155" t="inlineStr">
-        <is>
-          <t>2025-05-21</t>
-        </is>
-      </c>
+          <t>87 - Programa Estadual de Governança Estratégica de Unidades Judiciárias - Implantação do Sistema Eletrônico para Tramitação de Processos Judiciais Eproc.</t>
+        </is>
+      </c>
+      <c r="AD155" t="inlineStr"/>
+      <c r="AE155" t="inlineStr"/>
       <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="inlineStr">
         <is>
-          <t>11 - Modernização da Gestão Orçamentária e Financeira</t>
+          <t>3 - Agilidade e Produtividade na Prestação Jurisdicional</t>
         </is>
       </c>
       <c r="AH155" t="inlineStr"/>
@@ -35462,17 +35398,13 @@
       </c>
       <c r="AK155" t="inlineStr">
         <is>
-          <t>DEPLAG , DIRFIN , SEGOVE</t>
-        </is>
-      </c>
-      <c r="AL155" t="inlineStr">
-        <is>
-          <t>Eduardo Antônio Codo Santos / Alessandra da Silva Campos / João Victor Silveira Rezende</t>
-        </is>
-      </c>
+          <t>SEGOVE</t>
+        </is>
+      </c>
+      <c r="AL155" t="inlineStr"/>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>Anual</t>
+          <t>Mensal</t>
         </is>
       </c>
       <c r="AN155" t="inlineStr">
@@ -35502,12 +35434,12 @@
       </c>
       <c r="AS155" t="inlineStr">
         <is>
-          <t>ASPLAGMETA-2392</t>
+          <t>ASPLAGMETA-2774</t>
         </is>
       </c>
       <c r="AT155" t="inlineStr">
         <is>
-          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2392 Janeiro Apuração Aberto ASPLAGMETA-2393 Fevereiro Apuração Aberto ASPLAGMETA-2394 Março Apuração Aberto ASPLAGMETA-2395 Abril Apuração Aberto ASPLAGMETA-2396 Maio Apuração Aberto ASPLAGMETA-2397 Junho Apuração Aberto ASPLAGMETA-2398 Julho Apuração Aberto ASPLAGMETA-2399 Agosto Apuração Aberto ASPLAGMETA-2400 Setembro Apuração Aberto ASPLAGMETA-2401 Outubro Apuração Aberto ASPLAGMETA-2402 Novembro Apuração Aberto ASPLAGMETA-2403 Dezembro Apuração Aberto ASPLAGMETA-2404 Apurado no período Apuração Aberto</t>
+          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2774 Janeiro Apuração Aberto ASPLAGMETA-2775 Fevereiro Apuração Aberto ASPLAGMETA-2776 Março Apuração Aberto ASPLAGMETA-2777 Abril Apuração Aberto ASPLAGMETA-2778 Maio Apuração Aberto ASPLAGMETA-2779 Junho Apuração Aberto ASPLAGMETA-2780 Julho Apuração Aberto ASPLAGMETA-2781 Agosto Apuração Aberto ASPLAGMETA-2782 Setembro Apuração Aberto ASPLAGMETA-2783 Outubro Apuração Aberto ASPLAGMETA-2784 Novembro Apuração Aberto ASPLAGMETA-2785 Dezembro Apuração Aberto ASPLAGMETA-2786 Apurado no período Apuração Aberto</t>
         </is>
       </c>
       <c r="AU155" t="inlineStr"/>
@@ -35534,7 +35466,7 @@
       <c r="AZ155" t="inlineStr"/>
       <c r="BA155" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BB155" t="inlineStr">
@@ -35563,7 +35495,7 @@
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
-          <t>[ASPLAGMETA-2137] TJMG 129 - Executar 100% (cem por cento) das entregas previstas na iniciativa Painel de Gestão Automatizada de Receitas Judiciais até junho de 2025.</t>
+          <t>[ASPLAGMETA-2142] TJMG 137 - Concluir, até 19/12/2025, 40% do projeto de implantação Sistema de Gestão Financeira dos Depósitos Judiciais – SIDEJUD.</t>
         </is>
       </c>
       <c r="F156" t="inlineStr"/>
@@ -35579,7 +35511,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Diretora de Secretaria</t>
+          <t>Gerente</t>
         </is>
       </c>
       <c r="J156" t="inlineStr"/>
@@ -35602,19 +35534,15 @@
       <c r="O156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Corregedoria</t>
+          <t>Presidência</t>
         </is>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>seplan@tjmg.jus.br</t>
-        </is>
-      </c>
-      <c r="R156" t="inlineStr">
-        <is>
-          <t>asplag@tjmg.jus.br</t>
-        </is>
-      </c>
+          <t>viviane.cafaro@tjmg.jus.br</t>
+        </is>
+      </c>
+      <c r="R156" t="inlineStr"/>
       <c r="S156" t="inlineStr">
         <is>
           <t>Responsável</t>
@@ -35629,7 +35557,7 @@
       <c r="V156" t="inlineStr"/>
       <c r="W156" t="inlineStr">
         <is>
-          <t>Cronograma de acompanhamento da Iniciativa 93 - Painel de Gestão Automatizada de Receitas Judiciais</t>
+          <t>Cronograma da iniciativa estratégica</t>
         </is>
       </c>
       <c r="X156" t="inlineStr">
@@ -35639,24 +35567,24 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>(atividades concluídas no período / atividades previstas para serem realizadas até junho/2025) x 100. Considerando o peso definido para cada uma delas.</t>
+          <t>Somatório das entregas relativas ao Módulo de Depósitos Judiciais homologadas pela DIRFIN em 2025.</t>
         </is>
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>Sra. Bruna Eduarda Medeiros de Sousa</t>
+          <t>Viviane de Lima Cafaro</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025
-             - 9.29 - Taxa de implantação do Painel de Gestão Automatizada de Receitas Judiciais.</t>
+             - 11.2 - Taxa de cumprimento do "Projeto de Implantação do Sistema de Gestão Financeira dos Depósitos Judiciais - SIDEJUD".</t>
         </is>
       </c>
       <c r="AB156" t="inlineStr"/>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>93 - Painel de gestão Automatizada de Receitas Judiciais.</t>
+          <t>57 - Implantação do Sistema de Gestão Financeira dos Depósitos Judiciais – SIDEJUD.</t>
         </is>
       </c>
       <c r="AD156" t="inlineStr">
@@ -35672,15 +35600,11 @@
       <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="inlineStr">
         <is>
-          <t>9 - Aprimoramento da Gestão Administrativa e da Governança Judiciária</t>
+          <t>11 - Modernização da Gestão Orçamentária e Financeira</t>
         </is>
       </c>
       <c r="AH156" t="inlineStr"/>
-      <c r="AI156" t="inlineStr">
-        <is>
-          <t>ASPLAG</t>
-        </is>
-      </c>
+      <c r="AI156" t="inlineStr"/>
       <c r="AJ156" t="inlineStr">
         <is>
           <t>16 - Paz, Justiça e Instituições Eficazes</t>
@@ -35688,12 +35612,12 @@
       </c>
       <c r="AK156" t="inlineStr">
         <is>
-          <t>COAPE , COSIS , DIRFOR , GACOR</t>
+          <t>DIRFOR</t>
         </is>
       </c>
       <c r="AL156" t="inlineStr">
         <is>
-          <t>Des. Estevão Lucchesi de Carvalho</t>
+          <t>Eduardo Antônio Codo</t>
         </is>
       </c>
       <c r="AM156" t="inlineStr">
@@ -35728,17 +35652,17 @@
       </c>
       <c r="AS156" t="inlineStr">
         <is>
-          <t>ASPLAGMETA-2405</t>
+          <t>ASPLAGMETA-2188</t>
         </is>
       </c>
       <c r="AT156" t="inlineStr">
         <is>
-          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2405 Janeiro Apuração Aberto ASPLAGMETA-2406 Fevereiro Apuração Aberto ASPLAGMETA-2407 Março Apuração Aberto ASPLAGMETA-2408 Abril Apuração Aberto ASPLAGMETA-2409 Maio Apuração Aberto ASPLAGMETA-2410 Junho Apuração Aberto ASPLAGMETA-2411 Julho Apuração Aberto ASPLAGMETA-2412 Agosto Apuração Aberto ASPLAGMETA-2413 Setembro Apuração Aberto ASPLAGMETA-2414 Outubro Apuração Aberto ASPLAGMETA-2415 Novembro Apuração Aberto ASPLAGMETA-2416 Dezembro Apuração Aberto ASPLAGMETA-2417 Apurado no período Apuração Aberto</t>
+          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2188 Janeiro Apuração Aberto ASPLAGMETA-2193 Feveiro Apuração Aberto ASPLAGMETA-2195 Março Apuração Aberto ASPLAGMETA-2198 Abril Apuração Aberto ASPLAGMETA-2201 Maio Apuração Aberto ASPLAGMETA-2203 Junho Apuração Aberto ASPLAGMETA-2205 Julho Apuração Aberto ASPLAGMETA-2206 Agosto Apuração Aberto ASPLAGMETA-2207 Setembro Apuração Aberto ASPLAGMETA-2208 Outubro Apuração Aberto ASPLAGMETA-2210 Novembro Apuração Aberto ASPLAGMETA-2211 Dezembro Apuração Aberto ASPLAGMETA-2214 Apurado no período Apuração Aberto</t>
         </is>
       </c>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>(31) 3237-8229</t>
+          <t>31 3207.7965</t>
         </is>
       </c>
       <c r="AV156" t="inlineStr">
@@ -35753,7 +35677,7 @@
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>SEPLAN</t>
+          <t>DIRFIN</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
@@ -35793,7 +35717,7 @@
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
-          <t>[ASPLAGMETA-2136] TJMG 126 - Realizar 100% (cem por cento) das etapas necessárias para a informatização do setor de precatórios do TJMG até 19/12/2025.</t>
+          <t>[ASPLAGMETA-2141] TJMG 69 - Cumprir, até 31/12/2025, 90% (noventa por cento) das atividades relacionadas ao Projeto de Gestão de Receitas do TJMG previstas para o ano de 2025.</t>
         </is>
       </c>
       <c r="F157" t="inlineStr"/>
@@ -35807,7 +35731,11 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr"/>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Gerente</t>
+        </is>
+      </c>
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr">
         <is>
@@ -35819,7 +35747,11 @@
           <t>ASPLAG/TJMG</t>
         </is>
       </c>
-      <c r="M157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
       <c r="N157" t="inlineStr"/>
       <c r="O157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
@@ -35841,24 +35773,36 @@
       </c>
       <c r="U157" t="inlineStr"/>
       <c r="V157" t="inlineStr"/>
-      <c r="W157" t="inlineStr"/>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>Cronograma da iniciativa estratégica.</t>
+        </is>
+      </c>
       <c r="X157" t="inlineStr">
         <is>
           <t>Último Valor</t>
         </is>
       </c>
-      <c r="Y157" t="inlineStr"/>
-      <c r="Z157" t="inlineStr"/>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>∑ atividades executadas em 2025 / ∑ atividades previstas para conclusão em 2025.</t>
+        </is>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>Leonardo Honorio Rodrigues</t>
+        </is>
+      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025
-             - 9.28 - Taxa de execução das etapas necessárias para a informatização do setor de precatórios do TJMG.</t>
+             - 11.3 - Taxa de cumprimento das atividades relacionadas ao Projeto de Gestão de Receitas do TJMG.</t>
         </is>
       </c>
       <c r="AB157" t="inlineStr"/>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>89 - Informatização do setor de Precatórios do TJMG.</t>
+          <t>55 - Gestão de Receitas do TJMG.</t>
         </is>
       </c>
       <c r="AD157" t="inlineStr">
@@ -35874,7 +35818,7 @@
       <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="inlineStr">
         <is>
-          <t>9 - Aprimoramento da Gestão Administrativa e da Governança Judiciária</t>
+          <t>11 - Modernização da Gestão Orçamentária e Financeira</t>
         </is>
       </c>
       <c r="AH157" t="inlineStr"/>
@@ -35885,7 +35829,11 @@
         </is>
       </c>
       <c r="AK157" t="inlineStr"/>
-      <c r="AL157" t="inlineStr"/>
+      <c r="AL157" t="inlineStr">
+        <is>
+          <t>Eduardo Antonio Codo Santos</t>
+        </is>
+      </c>
       <c r="AM157" t="inlineStr">
         <is>
           <t>Mensal</t>
@@ -35918,12 +35866,12 @@
       </c>
       <c r="AS157" t="inlineStr">
         <is>
-          <t>ASPLAGMETA-2418</t>
+          <t>ASPLAGMETA-2217</t>
         </is>
       </c>
       <c r="AT157" t="inlineStr">
         <is>
-          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2418 Janeiro Apuração Aberto ASPLAGMETA-2419 Fevereiro Apuração Aberto ASPLAGMETA-2420 Março Apuração Aberto ASPLAGMETA-2421 Abril Apuração Aberto ASPLAGMETA-2422 Maio Apuração Aberto ASPLAGMETA-2423 Junho Apuração Aberto ASPLAGMETA-2424 Julho Apuração Aberto ASPLAGMETA-2425 Agosto Apuração Aberto ASPLAGMETA-2426 Setembro Apuração Aberto ASPLAGMETA-2427 Outubro Apuração Aberto ASPLAGMETA-2428 Novembro Apuração Aberto ASPLAGMETA-2429 Dezembro Apuração Aberto ASPLAGMETA-2430 Apurado no período Apuração Aberto</t>
+          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2217 Janeiro Apuração Aberto ASPLAGMETA-2219 Fevereiro Apuração Aberto ASPLAGMETA-2221 Março Apuração Aberto ASPLAGMETA-2223 Abril Apuração Aberto ASPLAGMETA-2225 Maio Apuração Aberto ASPLAGMETA-2227 Junho Apuração Aberto ASPLAGMETA-2231 Julho Apuração Aberto ASPLAGMETA-2232 Agosto Apuração Aberto ASPLAGMETA-2233 Setembro Apuração Aberto ASPLAGMETA-2234 Outubro Apuração Aberto ASPLAGMETA-2235 Novembro Apuração Aberto ASPLAGMETA-2236 Dezembro Apuração Aberto ASPLAGMETA-2237 Apurado no período Apuração Aberto</t>
         </is>
       </c>
       <c r="AU157" t="inlineStr"/>
@@ -35939,7 +35887,7 @@
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>ASPREC</t>
+          <t>DIRFIN</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
@@ -35950,7 +35898,7 @@
       <c r="AZ157" t="inlineStr"/>
       <c r="BA157" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BB157" t="inlineStr">
@@ -35979,7 +35927,7 @@
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
-          <t>[ASPLAGMETA-2135] TJMG 123 - Concluir 100% (cem por cento) das entregas previstas para o “Programa de Modernização dos Plenários, suas Áreas Externas e dos Painéis de Comunicação” até dezembro de 2025.</t>
+          <t>[ASPLAGMETA-2140] TJMG 104 - Executar, em 2025, 100% (cem por cento) das atividades previstas para o ano para a implementação da Política de Prevenção e Enfrentamento ao Assédio Moral, Assédio Sexual e Discriminação no âmbito da Justiça de Primeira e Segunda Instâncias.</t>
         </is>
       </c>
       <c r="F158" t="inlineStr"/>
@@ -35993,11 +35941,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>Secretário Geral</t>
-        </is>
-      </c>
+      <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr">
         <is>
@@ -36022,11 +35966,7 @@
         </is>
       </c>
       <c r="Q158" t="inlineStr"/>
-      <c r="R158" t="inlineStr">
-        <is>
-          <t>asplag@tjmg.jus.br</t>
-        </is>
-      </c>
+      <c r="R158" t="inlineStr"/>
       <c r="S158" t="inlineStr">
         <is>
           <t>Responsável</t>
@@ -36039,11 +35979,7 @@
       </c>
       <c r="U158" t="inlineStr"/>
       <c r="V158" t="inlineStr"/>
-      <c r="W158" t="inlineStr">
-        <is>
-          <t>Cronograma de acompanhamento da Iniciativa Estratégica 81 - Programa de Modernização dos Plenários, suas Áreas Externas e dos Painéis de Comunicação.</t>
-        </is>
-      </c>
+      <c r="W158" t="inlineStr"/>
       <c r="X158" t="inlineStr">
         <is>
           <t>Último Valor</t>
@@ -36051,24 +35987,24 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>Entregas concluídas/ Entregas previstas no “Programa de Modernização dos Plenários, suas Áreas Externas e dos Painéis de Comunicação”. &gt; Considera o "peso" de cada entrega no cronograma.</t>
+          <t>Total de Atividades Implementadas/ Total das Atividades previstas x 100.</t>
         </is>
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>Dr. Guilherme Augusto Mendes do Valle</t>
+          <t>Coordenadores dos Comitês de Primeira e Segunda Instâncias</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025
-             - 9.26 - Taxa de execução do "Programa de Modernização dos Plenários, suas Áreas Externas e dos Painéis de Comunicação”.</t>
+             - 5.6 - Número de procedimentos pré-processuais de reconhecimento de paternidade tratados no âmbito dos Centros Judiciários de Solução de Conflitos e Cidadania no setor pré-processual ou no programa Paternidade para Todos.</t>
         </is>
       </c>
       <c r="AB158" t="inlineStr"/>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>81 - Programa de Modernização dos Plenários, suas Áreas Externas e dos Painéis de Comunicação.</t>
+          <t>78 - Implementação de Política de Prevenção e Enfrentamento ao Assédio Moral, Assédio Sexual e Discriminação.</t>
         </is>
       </c>
       <c r="AD158" t="inlineStr">
@@ -36084,33 +36020,25 @@
       <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="inlineStr">
         <is>
-          <t>9 - Aprimoramento da Gestão Administrativa e da Governança Judiciária</t>
+          <t>10 - Otimização da Gestão de Pessoas</t>
         </is>
       </c>
       <c r="AH158" t="inlineStr"/>
-      <c r="AI158" t="inlineStr">
-        <is>
-          <t>ASPLAG</t>
-        </is>
-      </c>
+      <c r="AI158" t="inlineStr"/>
       <c r="AJ158" t="inlineStr">
         <is>
           <t>16 - Paz, Justiça e Instituições Eficazes</t>
         </is>
       </c>
-      <c r="AK158" t="inlineStr">
-        <is>
-          <t>DENGEP , DIRCOM , DIRFOR , DIRSEP , DIRSUP , SEOESP , SEGOVE</t>
-        </is>
-      </c>
+      <c r="AK158" t="inlineStr"/>
       <c r="AL158" t="inlineStr">
         <is>
-          <t>Des. Luiz Carlos de Azevedo Corrêa Junior</t>
+          <t>Desembargador Pedro Bernardes de Oliveira</t>
         </is>
       </c>
       <c r="AM158" t="inlineStr">
         <is>
-          <t>Bimestral</t>
+          <t>Trimestral</t>
         </is>
       </c>
       <c r="AN158" t="inlineStr">
@@ -36140,19 +36068,15 @@
       </c>
       <c r="AS158" t="inlineStr">
         <is>
-          <t>ASPLAGMETA-2431</t>
+          <t>ASPLAGMETA-2238</t>
         </is>
       </c>
       <c r="AT158" t="inlineStr">
         <is>
-          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2431 Janeiro Apuração Aberto ASPLAGMETA-2432 Fevereiro Apuração Aberto ASPLAGMETA-2433 Março Apuração Aberto ASPLAGMETA-2434 Abril Apuração Aberto ASPLAGMETA-2435 Maio Apuração Aberto ASPLAGMETA-2436 Junho Apuração Aberto ASPLAGMETA-2437 Julho Apuração Aberto ASPLAGMETA-2438 Agosto Apuração Aberto ASPLAGMETA-2439 Setembro Apuração Aberto ASPLAGMETA-2440 Outubro Apuração Aberto ASPLAGMETA-2441 Novembro Apuração Aberto ASPLAGMETA-2442 Dezembro Apuração Aberto ASPLAGMETA-2443 Apurado no período Apuração Aberto</t>
-        </is>
-      </c>
-      <c r="AU158" t="inlineStr">
-        <is>
-          <t>(31) 3307-2566</t>
-        </is>
-      </c>
+          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2238 Janeiro Apuração Aberto ASPLAGMETA-2239 Fevereiro Apuração Aberto ASPLAGMETA-2240 Março Apuração Aberto ASPLAGMETA-2242 Abril Apuração Aberto ASPLAGMETA-2244 Maio Apuração Aberto ASPLAGMETA-2245 Junho Apuração Aberto ASPLAGMETA-2247 Julho Apuração Aberto ASPLAGMETA-2249 Agosto Apuração Aberto ASPLAGMETA-2251 Setembro Apuração Aberto ASPLAGMETA-2253 Outubro Apuração Aberto ASPLAGMETA-2255 Novembro Apuração Aberto ASPLAGMETA-2257 Dezembro Apuração Aberto ASPLAGMETA-2259 Apurado no período Apuração Aberto</t>
+        </is>
+      </c>
+      <c r="AU158" t="inlineStr"/>
       <c r="AV158" t="inlineStr">
         <is>
           <t>Estado</t>
@@ -36205,7 +36129,7 @@
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
-          <t>[ASPLAGMETA-2134] TJMG 109 - Emitir, até 31/12/2025, Termo de Autorização de Ocupação - TAO ou, quando não houver ocupação, Termo de Recebimento Provisório - TRP, para pelo menos 70% (setenta por cento) das obras previstas no para o ano no Plano de Obras.</t>
+          <t>[ASPLAGMETA-2139] TJMG 67 - Cumprir, até o final de 2025, 94% (noventa e quatro por cento) das etapas/entregas de consolidação do Programa de Pós-Graduação da EJEF previstas para o período de 2021-2026.</t>
         </is>
       </c>
       <c r="F159" t="inlineStr"/>
@@ -36240,7 +36164,7 @@
       <c r="O159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Presidência</t>
+          <t>2ª Vice Presidência</t>
         </is>
       </c>
       <c r="Q159" t="inlineStr"/>
@@ -36257,11 +36181,7 @@
       </c>
       <c r="U159" t="inlineStr"/>
       <c r="V159" t="inlineStr"/>
-      <c r="W159" t="inlineStr">
-        <is>
-          <t>Cronograma da iniciativa estratégica.</t>
-        </is>
-      </c>
+      <c r="W159" t="inlineStr"/>
       <c r="X159" t="inlineStr">
         <is>
           <t>Último Valor</t>
@@ -36269,20 +36189,24 @@
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>Resultado do indicador = QR/QP X 100. QR =  Quantidade de obras emissão do termo de autorização para ocupação ou termo de recebimento provisório emitidos. QP = Quantidade total de obras planejadas para 2025.</t>
-        </is>
-      </c>
-      <c r="Z159" t="inlineStr"/>
+          <t>∑ECC / ECP x 100, onde: ECC = Quantidade de etapas de consolidação dos programas de pós-graduação cumpridas até o ano considerado; ECP = Quantidade total de etapas de consolidação dos programas de pós-graduação planejadas para o período de 2021-2026. Obs: para fins de monitoramento pelo cronograma da iniciativa, as etapas de consolidação equivalem às entregas definidas no cronograma.</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>Maiana Silva Carvalho</t>
+        </is>
+      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025
-             - 9.25 - Taxa de Termos de Autorização para Ocupação emitidos.</t>
+             - 10.5 - Taxa de consolidação do Programa de Pós-Graduação da Escola Judicial Desembargador Edésio Fernandes.</t>
         </is>
       </c>
       <c r="AB159" t="inlineStr"/>
       <c r="AC159" t="inlineStr">
         <is>
-          <t>20 - Plano de Aceleração de Obras.</t>
+          <t>50 - Plano de Desenvolvimento Institucional da EJEF ciclo 2021 a 2026 - Programa Pós-Graduação da EJEF.</t>
         </is>
       </c>
       <c r="AD159" t="inlineStr">
@@ -36298,7 +36222,7 @@
       <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="inlineStr">
         <is>
-          <t>9 - Aprimoramento da Gestão Administrativa e da Governança Judiciária</t>
+          <t>10 - Otimização da Gestão de Pessoas</t>
         </is>
       </c>
       <c r="AH159" t="inlineStr"/>
@@ -36308,11 +36232,19 @@
           <t>16 - Paz, Justiça e Instituições Eficazes</t>
         </is>
       </c>
-      <c r="AK159" t="inlineStr"/>
-      <c r="AL159" t="inlineStr"/>
+      <c r="AK159" t="inlineStr">
+        <is>
+          <t>DEPLAG , DIRCOM , DIRDEP , DIRGED , DIRSEP</t>
+        </is>
+      </c>
+      <c r="AL159" t="inlineStr">
+        <is>
+          <t>Dr. Thiago Grazziane Gandra</t>
+        </is>
+      </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>Mensal</t>
+          <t>Trimestral</t>
         </is>
       </c>
       <c r="AN159" t="inlineStr">
@@ -36342,12 +36274,12 @@
       </c>
       <c r="AS159" t="inlineStr">
         <is>
-          <t>ASPLAGMETA-2444</t>
+          <t>ASPLAGMETA-2347</t>
         </is>
       </c>
       <c r="AT159" t="inlineStr">
         <is>
-          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2444 Janeiro Apuração Aberto ASPLAGMETA-2445 Fevereiro Apuração Aberto ASPLAGMETA-2446 Março Apuração Aberto ASPLAGMETA-2447 Abril Apuração Aberto ASPLAGMETA-2448 Maio Apuração Aberto ASPLAGMETA-2449 Junho Apuração Aberto ASPLAGMETA-2450 Julho Apuração Aberto ASPLAGMETA-2451 Agosto Apuração Aberto ASPLAGMETA-2452 Setembro Apuração Aberto ASPLAGMETA-2453 Outubro Apuração Aberto ASPLAGMETA-2454 Novembro Apuração Aberto ASPLAGMETA-2455 Dezembro Apuração Aberto ASPLAGMETA-2456 Apurado no período Apuração Aberto</t>
+          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2347 Janeiro Apuração Aberto ASPLAGMETA-2350 Fevereiro Apuração Aberto ASPLAGMETA-2353 Março Apuração Aberto ASPLAGMETA-2355 Abril Apuração Aberto ASPLAGMETA-2356 Maio Apuração Aberto ASPLAGMETA-2358 Junho Apuração Aberto ASPLAGMETA-2359 Julho Apuração Aberto ASPLAGMETA-2361 Agosto Apuração Aberto ASPLAGMETA-2363 Setembro Apuração Aberto ASPLAGMETA-2365 Outubro Apuração Aberto ASPLAGMETA-2369 Novembro Apuração Aberto ASPLAGMETA-2371 Dezembro Apuração Aberto ASPLAGMETA-2373 Apurado no período Apuração Aberto</t>
         </is>
       </c>
       <c r="AU159" t="inlineStr"/>
@@ -36363,7 +36295,7 @@
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>DENGEP</t>
+          <t>2ª Vice Presidência</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
@@ -36374,7 +36306,7 @@
       <c r="AZ159" t="inlineStr"/>
       <c r="BA159" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>94</t>
         </is>
       </c>
       <c r="BB159" t="inlineStr">
@@ -36403,7 +36335,7 @@
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
-          <t>[ASPLAGMETA-2133] TJMG 96 - Executar, em 2025, 100% (cem por cento) das atividades previstas, para o ano, no programa de Ampliação da Eficácia da Sistemática dos Precedentes Qualificados.</t>
+          <t>[ASPLAGMETA-2138] TJMG 136 - Colocar, pelo menos, 1 (um) Mínimo Produto Viável (MVP) relativo ao Sistema de Gestão Financeira e Orçamentária em produção até 31/10/2025.</t>
         </is>
       </c>
       <c r="F160" t="inlineStr"/>
@@ -36419,7 +36351,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Diretora de Secretaria</t>
+          <t>Comitê</t>
         </is>
       </c>
       <c r="J160" t="inlineStr"/>
@@ -36433,23 +36365,15 @@
           <t>ASPLAG/TJMG</t>
         </is>
       </c>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>2025-05-15</t>
-        </is>
-      </c>
+      <c r="M160" t="inlineStr"/>
       <c r="N160" t="inlineStr"/>
       <c r="O160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>1ª Vice Presidência</t>
-        </is>
-      </c>
-      <c r="Q160" t="inlineStr">
-        <is>
-          <t>sepad@tjmg.jus.br</t>
-        </is>
-      </c>
+          <t>Presidência</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr"/>
       <c r="R160" t="inlineStr"/>
       <c r="S160" t="inlineStr">
         <is>
@@ -36465,34 +36389,34 @@
       <c r="V160" t="inlineStr"/>
       <c r="W160" t="inlineStr">
         <is>
-          <t>Cronograma da Iniciativa Estratégica.</t>
+          <t>Comitê Tático do PMGFO</t>
         </is>
       </c>
       <c r="X160" t="inlineStr">
         <is>
-          <t>Último Valor</t>
+          <t>Soma</t>
         </is>
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>Resultado do indicador = QAE/QAP X 100, onde: QME = Quantidade de atividades executadas. QAP = Quantidade de atividades previstas.</t>
+          <t>Somatório do número de MVP’s colocados em produção no ano vigente.</t>
         </is>
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>Sra. Elaine Batista Costa Souza</t>
+          <t>Comitê Tático</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025
-             - 9.23 - Taxa de cumprimento das atividades previstas no Projeto de Ampliação da Eficácia da Sistemática dos Precedentes Qualificadas.</t>
+             - 11.8 - Número de MVPs relativo ao Sistema de Gestão Financeira e Orçamentária colocados em produção.</t>
         </is>
       </c>
       <c r="AB160" t="inlineStr"/>
       <c r="AC160" t="inlineStr">
         <is>
-          <t>75 - Ampliação da Eficácia da Sistemática dos Precedentes Qualificados.</t>
+          <t>88 - Programa de Soluções Tecnológicas para Modernização da Gestão Financeira e Orçamentária do TJMG.</t>
         </is>
       </c>
       <c r="AD160" t="inlineStr">
@@ -36508,7 +36432,7 @@
       <c r="AF160" t="inlineStr"/>
       <c r="AG160" t="inlineStr">
         <is>
-          <t>9 - Aprimoramento da Gestão Administrativa e da Governança Judiciária</t>
+          <t>11 - Modernização da Gestão Orçamentária e Financeira</t>
         </is>
       </c>
       <c r="AH160" t="inlineStr"/>
@@ -36520,17 +36444,17 @@
       </c>
       <c r="AK160" t="inlineStr">
         <is>
-          <t>CIJMG , DIRCOM , DIRDEP , NUGEP , 1º GAVIP</t>
+          <t>DEPLAG , DIRFIN , SEGOVE</t>
         </is>
       </c>
       <c r="AL160" t="inlineStr">
         <is>
-          <t>Des. Habib Jabour</t>
+          <t>Eduardo Antônio Codo Santos / Alessandra da Silva Campos / João Victor Silveira Rezende</t>
         </is>
       </c>
       <c r="AM160" t="inlineStr">
         <is>
-          <t>Trimestral</t>
+          <t>Anual</t>
         </is>
       </c>
       <c r="AN160" t="inlineStr">
@@ -36560,19 +36484,15 @@
       </c>
       <c r="AS160" t="inlineStr">
         <is>
-          <t>ASPLAGMETA-2503</t>
+          <t>ASPLAGMETA-2392</t>
         </is>
       </c>
       <c r="AT160" t="inlineStr">
         <is>
-          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2503 Janeiro Apuração Aberto ASPLAGMETA-2506 Fevereiro Apuração Aberto ASPLAGMETA-2508 Março Apuração Aberto ASPLAGMETA-2510 Abril Apuração Aberto ASPLAGMETA-2511 Maio Apuração Aberto ASPLAGMETA-2512 Junho Apuração Aberto ASPLAGMETA-2513 Julho Apuração Aberto ASPLAGMETA-2514 Agosto Apuração Aberto ASPLAGMETA-2516 Setembro Apuração Aberto ASPLAGMETA-2517 Outubro Apuração Aberto ASPLAGMETA-2518 Novembro Apuração Aberto ASPLAGMETA-2520 Dezembro Apuração Aberto ASPLAGMETA-2521 Apurado no período Apuração Aberto</t>
-        </is>
-      </c>
-      <c r="AU160" t="inlineStr">
-        <is>
-          <t>(31) 3232-2687</t>
-        </is>
-      </c>
+          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2392 Janeiro Apuração Aberto ASPLAGMETA-2393 Fevereiro Apuração Aberto ASPLAGMETA-2394 Março Apuração Aberto ASPLAGMETA-2395 Abril Apuração Aberto ASPLAGMETA-2396 Maio Apuração Aberto ASPLAGMETA-2397 Junho Apuração Aberto ASPLAGMETA-2398 Julho Apuração Aberto ASPLAGMETA-2399 Agosto Apuração Aberto ASPLAGMETA-2400 Setembro Apuração Aberto ASPLAGMETA-2401 Outubro Apuração Aberto ASPLAGMETA-2402 Novembro Apuração Aberto ASPLAGMETA-2403 Dezembro Apuração Aberto ASPLAGMETA-2404 Apurado no período Apuração Aberto</t>
+        </is>
+      </c>
+      <c r="AU160" t="inlineStr"/>
       <c r="AV160" t="inlineStr">
         <is>
           <t>Estado</t>
@@ -36585,18 +36505,18 @@
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>SEPAD</t>
+          <t>DIRTEC</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
         <is>
-          <t>Percentual</t>
+          <t>Unidade</t>
         </is>
       </c>
       <c r="AZ160" t="inlineStr"/>
       <c r="BA160" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="BB160" t="inlineStr">
@@ -36625,7 +36545,7 @@
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
-          <t>[ASPLAGMETA-2132] TJMG 95 - Executar, no ano de 2025, 100% (cem por cento) das atividades previstas no projeto de Aprimoramento da Gestão de Cobrança de Custas Processuais.</t>
+          <t>[ASPLAGMETA-2137] TJMG 129 - Executar 100% (cem por cento) das entregas previstas na iniciativa Painel de Gestão Automatizada de Receitas Judiciais até dezembro de 2025.</t>
         </is>
       </c>
       <c r="F161" t="inlineStr"/>
@@ -36641,7 +36561,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>Diretora</t>
+          <t>Diretora de Secretaria</t>
         </is>
       </c>
       <c r="J161" t="inlineStr"/>
@@ -36664,15 +36584,19 @@
       <c r="O161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Presidência</t>
+          <t>Corregedoria</t>
         </is>
       </c>
       <c r="Q161" t="inlineStr">
         <is>
-          <t>dirsup@tjmg.jus.br</t>
-        </is>
-      </c>
-      <c r="R161" t="inlineStr"/>
+          <t>seplan@tjmg.jus.br</t>
+        </is>
+      </c>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>asplag@tjmg.jus.br</t>
+        </is>
+      </c>
       <c r="S161" t="inlineStr">
         <is>
           <t>Responsável</t>
@@ -36687,7 +36611,7 @@
       <c r="V161" t="inlineStr"/>
       <c r="W161" t="inlineStr">
         <is>
-          <t>Cronograma da Iniciativa Estratégica.</t>
+          <t>Cronograma de acompanhamento da Iniciativa 93 - Painel de Gestão Automatizada de Receitas Judiciais</t>
         </is>
       </c>
       <c r="X161" t="inlineStr">
@@ -36697,24 +36621,24 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>QAE/QAP X100, onde: QAP: Quantidade de atividades previstas. QAE: Quantidade de atividades executadas.</t>
+          <t>(atividades concluídas no período / atividades previstas para serem realizadas até junho/2025) x 100. Considerando o peso definido para cada uma delas.</t>
         </is>
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>Sra. Elena Costa de Oliveira Vidigal</t>
+          <t>Sra. Bruna Eduarda Medeiros de Sousa</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025
-             - 9.22 - Taxa de execução do projeto de Aprimoramento da Gestão de Cobrança de Custas Processuais.</t>
+             - 9.29 - Taxa de implantação do Painel de Gestão Automatizada de Receitas Judiciais.</t>
         </is>
       </c>
       <c r="AB161" t="inlineStr"/>
       <c r="AC161" t="inlineStr">
         <is>
-          <t>72 - Aprimoramento da Gestão de Cobrança de Custas Processuais.</t>
+          <t>93 - Painel de gestão Automatizada de Receitas Judiciais.</t>
         </is>
       </c>
       <c r="AD161" t="inlineStr">
@@ -36734,7 +36658,11 @@
         </is>
       </c>
       <c r="AH161" t="inlineStr"/>
-      <c r="AI161" t="inlineStr"/>
+      <c r="AI161" t="inlineStr">
+        <is>
+          <t>ASPLAG</t>
+        </is>
+      </c>
       <c r="AJ161" t="inlineStr">
         <is>
           <t>16 - Paz, Justiça e Instituições Eficazes</t>
@@ -36742,17 +36670,17 @@
       </c>
       <c r="AK161" t="inlineStr">
         <is>
-          <t>DEPLAG , DIRFIN , SEPAD , SEGOVE , CORREGEDORIA</t>
+          <t>COAPE , COSIS , DIRFOR , GACOR</t>
         </is>
       </c>
       <c r="AL161" t="inlineStr">
         <is>
-          <t>Dr. Marcelo Paulo Salgado</t>
+          <t>Des. Estevão Lucchesi de Carvalho</t>
         </is>
       </c>
       <c r="AM161" t="inlineStr">
         <is>
-          <t>Trimestral</t>
+          <t>Mensal</t>
         </is>
       </c>
       <c r="AN161" t="inlineStr">
@@ -36782,17 +36710,17 @@
       </c>
       <c r="AS161" t="inlineStr">
         <is>
-          <t>ASPLAGMETA-2522</t>
+          <t>ASPLAGMETA-2405</t>
         </is>
       </c>
       <c r="AT161" t="inlineStr">
         <is>
-          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2522 Janeiro Apuração Aberto ASPLAGMETA-2523 Fevereiro Apuração Aberto ASPLAGMETA-2524 Março Apuração Aberto ASPLAGMETA-2525 Abril Apuração Aberto ASPLAGMETA-2526 Maio Apuração Aberto ASPLAGMETA-2527 Junho Apuração Aberto ASPLAGMETA-2528 Julho Apuração Aberto ASPLAGMETA-2529 Agosto Apuração Aberto ASPLAGMETA-2530 Setembro Apuração Aberto ASPLAGMETA-2531 Outubro Apuração Aberto ASPLAGMETA-2532 Novembro Apuração Aberto ASPLAGMETA-2533 Dezembro Apuração Aberto ASPLAGMETA-2534 Apurado no período Apuração Aberto</t>
+          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2405 Janeiro Apuração Aberto ASPLAGMETA-2406 Fevereiro Apuração Aberto ASPLAGMETA-2407 Março Apuração Aberto ASPLAGMETA-2408 Abril Apuração Aberto ASPLAGMETA-2409 Maio Apuração Aberto ASPLAGMETA-2410 Junho Apuração Aberto ASPLAGMETA-2411 Julho Apuração Aberto ASPLAGMETA-2412 Agosto Apuração Aberto ASPLAGMETA-2413 Setembro Apuração Aberto ASPLAGMETA-2414 Outubro Apuração Aberto ASPLAGMETA-2415 Novembro Apuração Aberto ASPLAGMETA-2416 Dezembro Apuração Aberto ASPLAGMETA-2417 Apurado no período Apuração Aberto</t>
         </is>
       </c>
       <c r="AU161" t="inlineStr">
         <is>
-          <t>3232-2628</t>
+          <t>(31) 3237-8229</t>
         </is>
       </c>
       <c r="AV161" t="inlineStr">
@@ -36807,7 +36735,7 @@
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>DIRSUP</t>
+          <t>SEPLAN</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
@@ -36847,7 +36775,7 @@
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>[ASPLAGMETA-2131] TJMG 62 - Cumprir, até dezembro de 2025, 100% (cem por cento) das entregas previstas, para o ano, no Programa INOVA TJMG.</t>
+          <t>[ASPLAGMETA-2136] TJMG 126 - Realizar 100% (cem por cento) das etapas necessárias para a informatização do setor de precatórios do TJMG até 19/12/2025.</t>
         </is>
       </c>
       <c r="F162" t="inlineStr"/>
@@ -36861,11 +36789,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>Assessor Técnico II</t>
-        </is>
-      </c>
+      <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr">
         <is>
@@ -36877,11 +36801,7 @@
           <t>ASPLAG/TJMG</t>
         </is>
       </c>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>2025-05-15</t>
-        </is>
-      </c>
+      <c r="M162" t="inlineStr"/>
       <c r="N162" t="inlineStr"/>
       <c r="O162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
@@ -36903,36 +36823,24 @@
       </c>
       <c r="U162" t="inlineStr"/>
       <c r="V162" t="inlineStr"/>
-      <c r="W162" t="inlineStr">
-        <is>
-          <t>Cronograma da Iniciativa Estratégica.</t>
-        </is>
-      </c>
+      <c r="W162" t="inlineStr"/>
       <c r="X162" t="inlineStr">
         <is>
           <t>Último Valor</t>
         </is>
       </c>
-      <c r="Y162" t="inlineStr">
-        <is>
-          <t>Quantidade de entregas implementadas / Quantidade total de entregas previstas X 100.</t>
-        </is>
-      </c>
-      <c r="Z162" t="inlineStr">
-        <is>
-          <t>Priscila Pereira de Souza</t>
-        </is>
-      </c>
+      <c r="Y162" t="inlineStr"/>
+      <c r="Z162" t="inlineStr"/>
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025
-             - 9.13 - Taxa de entregas realizadas pelo UAI-Lab previstas no Programa Inova TJMG.</t>
+             - 9.28 - Taxa de execução das etapas necessárias para a informatização do setor de precatórios do TJMG.</t>
         </is>
       </c>
       <c r="AB162" t="inlineStr"/>
       <c r="AC162" t="inlineStr">
         <is>
-          <t>43 - Programa INOVA TJMG.</t>
+          <t>89 - Informatização do setor de Precatórios do TJMG.</t>
         </is>
       </c>
       <c r="AD162" t="inlineStr">
@@ -36958,19 +36866,11 @@
           <t>16 - Paz, Justiça e Instituições Eficazes</t>
         </is>
       </c>
-      <c r="AK162" t="inlineStr">
-        <is>
-          <t>DIRDEP</t>
-        </is>
-      </c>
-      <c r="AL162" t="inlineStr">
-        <is>
-          <t>Desembargador Luiz Carlos de Azevedo Corrêa Junior</t>
-        </is>
-      </c>
+      <c r="AK162" t="inlineStr"/>
+      <c r="AL162" t="inlineStr"/>
       <c r="AM162" t="inlineStr">
         <is>
-          <t>Trimestral</t>
+          <t>Mensal</t>
         </is>
       </c>
       <c r="AN162" t="inlineStr">
@@ -37000,12 +36900,12 @@
       </c>
       <c r="AS162" t="inlineStr">
         <is>
-          <t>ASPLAGMETA-2535</t>
+          <t>ASPLAGMETA-2418</t>
         </is>
       </c>
       <c r="AT162" t="inlineStr">
         <is>
-          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2535 Janeiro Apuração Aberto ASPLAGMETA-2536 Fevereiro Apuração Aberto ASPLAGMETA-2537 Março Apuração Aberto ASPLAGMETA-2538 Abril Apuração Aberto ASPLAGMETA-2539 Maio Apuração Aberto ASPLAGMETA-2540 Junho Apuração Aberto ASPLAGMETA-2541 Julho Apuração Aberto ASPLAGMETA-2542 Agosto Apuração Aberto ASPLAGMETA-2543 Setembro Apuração Aberto ASPLAGMETA-2544 Outubro Apuração Aberto ASPLAGMETA-2545 Novembro Apuração Aberto ASPLAGMETA-2546 Dezembro Apuração Aberto ASPLAGMETA-2547 Apurado no período Apuração Aberto</t>
+          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2418 Janeiro Apuração Aberto ASPLAGMETA-2419 Fevereiro Apuração Aberto ASPLAGMETA-2420 Março Apuração Aberto ASPLAGMETA-2421 Abril Apuração Aberto ASPLAGMETA-2422 Maio Apuração Aberto ASPLAGMETA-2423 Junho Apuração Aberto ASPLAGMETA-2424 Julho Apuração Aberto ASPLAGMETA-2425 Agosto Apuração Aberto ASPLAGMETA-2426 Setembro Apuração Aberto ASPLAGMETA-2427 Outubro Apuração Aberto ASPLAGMETA-2428 Novembro Apuração Aberto ASPLAGMETA-2429 Dezembro Apuração Aberto ASPLAGMETA-2430 Apurado no período Apuração Aberto</t>
         </is>
       </c>
       <c r="AU162" t="inlineStr"/>
@@ -37021,7 +36921,7 @@
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>NUGIN</t>
+          <t>ASPREC</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
@@ -37061,7 +36961,7 @@
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
-          <t>[ASPLAGMETA-2130] TJMG 40 - Implantar o Desdobramento do Planejamento Estratégico - DPE em 30 (trinta) Unidades Judiciárias de 1º grau até 31/12/2025.</t>
+          <t>[ASPLAGMETA-2135] TJMG 123 - Concluir 100% (cem por cento) das entregas previstas para o “Programa de Modernização dos Plenários, suas Áreas Externas e dos Painéis de Comunicação” até dezembro de 2025.</t>
         </is>
       </c>
       <c r="F163" t="inlineStr"/>
@@ -37077,7 +36977,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Diretora de Secretaria</t>
+          <t>Secretário Geral</t>
         </is>
       </c>
       <c r="J163" t="inlineStr"/>
@@ -37100,14 +37000,10 @@
       <c r="O163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Corregedoria</t>
-        </is>
-      </c>
-      <c r="Q163" t="inlineStr">
-        <is>
-          <t>seplan@tjmg.jus.br</t>
-        </is>
-      </c>
+          <t>Presidência</t>
+        </is>
+      </c>
+      <c r="Q163" t="inlineStr"/>
       <c r="R163" t="inlineStr">
         <is>
           <t>asplag@tjmg.jus.br</t>
@@ -37127,34 +37023,34 @@
       <c r="V163" t="inlineStr"/>
       <c r="W163" t="inlineStr">
         <is>
-          <t>NUPLAN - Núcleo de Suporte ao Planejamento e à Gestão da Primeira Instância. Cronograma da iniciativa 11 em 2025.</t>
+          <t>Cronograma de acompanhamento da Iniciativa Estratégica 81 - Programa de Modernização dos Plenários, suas Áreas Externas e dos Painéis de Comunicação.</t>
         </is>
       </c>
       <c r="X163" t="inlineStr">
         <is>
-          <t>Soma</t>
+          <t>Último Valor</t>
         </is>
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>Somatório de Unidades Judiciárias de 1º grau que implantaram a metodologia do Desdobramento do Planejamento Estratégico no ano.</t>
+          <t>Entregas concluídas/ Entregas previstas no “Programa de Modernização dos Plenários, suas Áreas Externas e dos Painéis de Comunicação”. &gt; Considera o "peso" de cada entrega no cronograma.</t>
         </is>
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>Sra. Bruna Eduarda Medeiros de Sousa</t>
+          <t>Dr. Guilherme Augusto Mendes do Valle</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
           <t>2025
-             - 9.1 - Número de Unidades Judiciárias de 1º grau que implantaram o Desdobramento do Planejamento Estratégico.</t>
+             - 9.26 - Taxa de execução do "Programa de Modernização dos Plenários, suas Áreas Externas e dos Painéis de Comunicação”.</t>
         </is>
       </c>
       <c r="AB163" t="inlineStr"/>
       <c r="AC163" t="inlineStr">
         <is>
-          <t>11 - Desdobramento do Planejamento Estratégico pelas Unidades Judiciárias de 1º grau de jurisdição.</t>
+          <t>81 - Programa de Modernização dos Plenários, suas Áreas Externas e dos Painéis de Comunicação.</t>
         </is>
       </c>
       <c r="AD163" t="inlineStr">
@@ -37186,17 +37082,17 @@
       </c>
       <c r="AK163" t="inlineStr">
         <is>
-          <t>NUPLAN , EJEF</t>
+          <t>DENGEP , DIRCOM , DIRFOR , DIRSEP , DIRSUP , SEOESP , SEGOVE</t>
         </is>
       </c>
       <c r="AL163" t="inlineStr">
         <is>
-          <t>Dr. Guilherme Lima Nogueira da Silva</t>
+          <t>Des. Luiz Carlos de Azevedo Corrêa Junior</t>
         </is>
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>Mensal</t>
+          <t>Bimestral</t>
         </is>
       </c>
       <c r="AN163" t="inlineStr">
@@ -37226,17 +37122,17 @@
       </c>
       <c r="AS163" t="inlineStr">
         <is>
-          <t>ASPLAGMETA-2548</t>
+          <t>ASPLAGMETA-2431</t>
         </is>
       </c>
       <c r="AT163" t="inlineStr">
         <is>
-          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2548 Janeiro Apuração Aberto ASPLAGMETA-2549 Fevereiro Apuração Aberto ASPLAGMETA-2550 Março Apuração Aberto ASPLAGMETA-2551 Abril Apuração Aberto ASPLAGMETA-2552 Maio Apuração Aberto ASPLAGMETA-2553 Junho Apuração Aberto ASPLAGMETA-2554 Julho Apuração Aberto ASPLAGMETA-2555 Agosto Apuração Aberto ASPLAGMETA-2556 Setembro Apuração Aberto ASPLAGMETA-2557 Outubro Apuração Aberto ASPLAGMETA-2558 Novembro Apuração Aberto ASPLAGMETA-2559 Dezembro Apuração Aberto ASPLAGMETA-2560 Apurado no período Apuração Aberto</t>
+          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2431 Janeiro Apuração Aberto ASPLAGMETA-2432 Fevereiro Apuração Aberto ASPLAGMETA-2433 Março Apuração Aberto ASPLAGMETA-2434 Abril Apuração Aberto ASPLAGMETA-2435 Maio Apuração Aberto ASPLAGMETA-2436 Junho Apuração Aberto ASPLAGMETA-2437 Julho Apuração Aberto ASPLAGMETA-2438 Agosto Apuração Aberto ASPLAGMETA-2439 Setembro Apuração Aberto ASPLAGMETA-2440 Outubro Apuração Aberto ASPLAGMETA-2441 Novembro Apuração Aberto ASPLAGMETA-2442 Dezembro Apuração Aberto ASPLAGMETA-2443 Apurado no período Apuração Aberto</t>
         </is>
       </c>
       <c r="AU163" t="inlineStr">
         <is>
-          <t>(31) 3237-1904</t>
+          <t>(31) 3307-2566</t>
         </is>
       </c>
       <c r="AV163" t="inlineStr">
@@ -37251,18 +37147,18 @@
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>SEPLAN</t>
+          <t>Presidência</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
         <is>
-          <t>Unidade</t>
+          <t>Percentual</t>
         </is>
       </c>
       <c r="AZ163" t="inlineStr"/>
       <c r="BA163" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>100</t>
         </is>
       </c>
       <c r="BB163" t="inlineStr">
@@ -37291,7 +37187,7 @@
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
-          <t>[ASPLAGMETA-2129] TJMG 135 - Exercer, em 2025, o juízo de admissibilidade em 100% (cem por cento) dos processos relacionados a IRDRs/IACs em até 150 (cento e cinquenta) dias após a distribuição do requerimento.</t>
+          <t>[ASPLAGMETA-2134] TJMG 109 - Emitir, até 31/12/2025, Termo de Autorização de Ocupação - TAO ou, quando não houver ocupação, Termo de Recebimento Provisório - TRP, para pelo menos 70% (setenta por cento) das obras previstas no para o ano no Plano de Obras.</t>
         </is>
       </c>
       <c r="F164" t="inlineStr"/>
@@ -37326,7 +37222,7 @@
       <c r="O164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>1ª Vice Presidência</t>
+          <t>Presidência</t>
         </is>
       </c>
       <c r="Q164" t="inlineStr"/>
@@ -37343,28 +37239,32 @@
       </c>
       <c r="U164" t="inlineStr"/>
       <c r="V164" t="inlineStr"/>
-      <c r="W164" t="inlineStr"/>
+      <c r="W164" t="inlineStr">
+        <is>
+          <t>Cronograma da iniciativa estratégica.</t>
+        </is>
+      </c>
       <c r="X164" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Último Valor</t>
         </is>
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>Número de juízos de admissibilidade em até 150 dias/ número de juízos de admissibilidade no período X 100 = percentual de alcance da meta.</t>
+          <t>Resultado do indicador = QR/QP X 100. QR =  Quantidade de obras emissão do termo de autorização para ocupação ou termo de recebimento provisório emitidos. QP = Quantidade total de obras planejadas para 2025.</t>
         </is>
       </c>
       <c r="Z164" t="inlineStr"/>
       <c r="AA164" t="inlineStr">
         <is>
           <t>2025
-             - 6.7 - Taxa de Juízo de admissibilidade de IRDR/IAC em até 150 (cento e cinquenta) dias.</t>
+             - 9.25 - Taxa de Termos de Autorização para Ocupação emitidos.</t>
         </is>
       </c>
       <c r="AB164" t="inlineStr"/>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>04 - Programa Agiliza-Jus. , 75 - Ampliação da Eficácia da Sistemática dos Precedentes Qualificados. , 94 - Programa 1ª Vice SOMA - Suporte à organização, cumprimento de metas e aperfeiçoamento gerencial.</t>
+          <t>20 - Plano de Aceleração de Obras.</t>
         </is>
       </c>
       <c r="AD164" t="inlineStr">
@@ -37380,7 +37280,7 @@
       <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="inlineStr">
         <is>
-          <t>6 - Consolidação do Sistema de Precedentes Obrigatórios</t>
+          <t>9 - Aprimoramento da Gestão Administrativa e da Governança Judiciária</t>
         </is>
       </c>
       <c r="AH164" t="inlineStr"/>
@@ -37424,12 +37324,12 @@
       </c>
       <c r="AS164" t="inlineStr">
         <is>
-          <t>ASPLAGMETA-2561</t>
+          <t>ASPLAGMETA-2444</t>
         </is>
       </c>
       <c r="AT164" t="inlineStr">
         <is>
-          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2561 Janeiro Apuração Aberto ASPLAGMETA-2562 Fevereiro Apuração Aberto ASPLAGMETA-2563 Março Apuração Aberto ASPLAGMETA-2564 Abril Apuração Aberto ASPLAGMETA-2565 Maio Apuração Aberto ASPLAGMETA-2566 Junho Apuração Aberto ASPLAGMETA-2567 Julho Apuração Aberto ASPLAGMETA-2568 Agosto Apuração Aberto ASPLAGMETA-2569 Setembro Apuração Aberto ASPLAGMETA-2570 Outubro Apuração Aberto ASPLAGMETA-2571 Outubro Apuração Aberto ASPLAGMETA-2572 Novembro Apuração Aberto ASPLAGMETA-2573 Dezembro Apuração Aberto ASPLAGMETA-2574 Apurado no período Apuração Aberto</t>
+          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2444 Janeiro Apuração Aberto ASPLAGMETA-2445 Fevereiro Apuração Aberto ASPLAGMETA-2446 Março Apuração Aberto ASPLAGMETA-2447 Abril Apuração Aberto ASPLAGMETA-2448 Maio Apuração Aberto ASPLAGMETA-2449 Junho Apuração Aberto ASPLAGMETA-2450 Julho Apuração Aberto ASPLAGMETA-2451 Agosto Apuração Aberto ASPLAGMETA-2452 Setembro Apuração Aberto ASPLAGMETA-2453 Outubro Apuração Aberto ASPLAGMETA-2454 Novembro Apuração Aberto ASPLAGMETA-2455 Dezembro Apuração Aberto ASPLAGMETA-2456 Apurado no período Apuração Aberto</t>
         </is>
       </c>
       <c r="AU164" t="inlineStr"/>
@@ -37445,7 +37345,7 @@
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>SEPAD</t>
+          <t>DENGEP</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
@@ -37456,7 +37356,7 @@
       <c r="AZ164" t="inlineStr"/>
       <c r="BA164" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BB164" t="inlineStr">
@@ -37485,7 +37385,7 @@
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
-          <t>[ASPLAGMETA-2128] TJMG 134 - Julgar, em 2025, 60% (sessenta por cento) dos IRDRs/IACS em até 320 (trezentos e vinte) dias após a admissão, (desconsiderado o tempo médio de permanência em carga a Advogados ou Órgãos Externos, 25 (vinte e cinco) dias).</t>
+          <t>[ASPLAGMETA-2133] TJMG 96 - Executar, em 2025, 100% (cem por cento) das atividades previstas, para o ano, no programa de Ampliação da Eficácia da Sistemática dos Precedentes Qualificados.</t>
         </is>
       </c>
       <c r="F165" t="inlineStr"/>
@@ -37499,7 +37399,11 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="I165" t="inlineStr"/>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Diretora de Secretaria</t>
+        </is>
+      </c>
       <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr">
         <is>
@@ -37523,7 +37427,11 @@
           <t>1ª Vice Presidência</t>
         </is>
       </c>
-      <c r="Q165" t="inlineStr"/>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>sepad@tjmg.jus.br</t>
+        </is>
+      </c>
       <c r="R165" t="inlineStr"/>
       <c r="S165" t="inlineStr">
         <is>
@@ -37537,7 +37445,11 @@
       </c>
       <c r="U165" t="inlineStr"/>
       <c r="V165" t="inlineStr"/>
-      <c r="W165" t="inlineStr"/>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>Cronograma da Iniciativa Estratégica.</t>
+        </is>
+      </c>
       <c r="X165" t="inlineStr">
         <is>
           <t>Último Valor</t>
@@ -37545,20 +37457,24 @@
       </c>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>JIRDR-IAC280d/TJ X 100, onde: JIRDR-IAC320d = Número de julgamentos de mérito realizados em até 320dias. TJ = Total de julgamentos realizados no período. JIRDR-IAC280d = ∑ dos processos com julgamento de mérito [(data de conclusão após a admissibilidade do processo) - (data do julgamento) =&lt; 320dias</t>
-        </is>
-      </c>
-      <c r="Z165" t="inlineStr"/>
+          <t>Resultado do indicador = QAE/QAP X 100, onde: QME = Quantidade de atividades executadas. QAP = Quantidade de atividades previstas.</t>
+        </is>
+      </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>Sra. Elaine Batista Costa Souza</t>
+        </is>
+      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>2025
-             - 6.6 - Taxa de julgamento de IRDR/IAC em até 320 (trezentos e vinte) dias.</t>
+             - 9.23 - Taxa de cumprimento das atividades previstas no Projeto de Ampliação da Eficácia da Sistemática dos Precedentes Qualificadas.</t>
         </is>
       </c>
       <c r="AB165" t="inlineStr"/>
       <c r="AC165" t="inlineStr">
         <is>
-          <t>04 - Programa Agiliza-Jus. , 75 - Ampliação da Eficácia da Sistemática dos Precedentes Qualificados. , 94 - Programa 1ª Vice SOMA - Suporte à organização, cumprimento de metas e aperfeiçoamento gerencial.</t>
+          <t>75 - Ampliação da Eficácia da Sistemática dos Precedentes Qualificados.</t>
         </is>
       </c>
       <c r="AD165" t="inlineStr">
@@ -37574,7 +37490,7 @@
       <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="inlineStr">
         <is>
-          <t>6 - Consolidação do Sistema de Precedentes Obrigatórios</t>
+          <t>9 - Aprimoramento da Gestão Administrativa e da Governança Judiciária</t>
         </is>
       </c>
       <c r="AH165" t="inlineStr"/>
@@ -37584,8 +37500,16 @@
           <t>16 - Paz, Justiça e Instituições Eficazes</t>
         </is>
       </c>
-      <c r="AK165" t="inlineStr"/>
-      <c r="AL165" t="inlineStr"/>
+      <c r="AK165" t="inlineStr">
+        <is>
+          <t>CIJMG , DIRCOM , DIRDEP , NUGEP , 1º GAVIP</t>
+        </is>
+      </c>
+      <c r="AL165" t="inlineStr">
+        <is>
+          <t>Des. Habib Jabour</t>
+        </is>
+      </c>
       <c r="AM165" t="inlineStr">
         <is>
           <t>Trimestral</t>
@@ -37618,15 +37542,19 @@
       </c>
       <c r="AS165" t="inlineStr">
         <is>
-          <t>ASPLAGMETA-2575</t>
+          <t>ASPLAGMETA-2503</t>
         </is>
       </c>
       <c r="AT165" t="inlineStr">
         <is>
-          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2575 Janeiro Apuração Aberto ASPLAGMETA-2576 Fevereiro Apuração Aberto ASPLAGMETA-2577 Março Apuração Aberto ASPLAGMETA-2578 Abril Apuração Aberto ASPLAGMETA-2579 Maio Apuração Aberto ASPLAGMETA-2580 Junho Apuração Aberto ASPLAGMETA-2581 Julho Apuração Aberto ASPLAGMETA-2582 Agosto Apuração Aberto ASPLAGMETA-2583 Setembro Apuração Aberto ASPLAGMETA-2584 Outubro Apuração Aberto ASPLAGMETA-2586 Novembro Apuração Aberto ASPLAGMETA-2587 Dezembro Apuração Aberto ASPLAGMETA-2591 Apurado no período Apuração Aberto</t>
-        </is>
-      </c>
-      <c r="AU165" t="inlineStr"/>
+          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2503 Janeiro Apuração Aberto ASPLAGMETA-2506 Fevereiro Apuração Aberto ASPLAGMETA-2508 Março Apuração Aberto ASPLAGMETA-2510 Abril Apuração Aberto ASPLAGMETA-2511 Maio Apuração Aberto ASPLAGMETA-2512 Junho Apuração Aberto ASPLAGMETA-2513 Julho Apuração Aberto ASPLAGMETA-2514 Agosto Apuração Aberto ASPLAGMETA-2516 Setembro Apuração Aberto ASPLAGMETA-2517 Outubro Apuração Aberto ASPLAGMETA-2518 Novembro Apuração Aberto ASPLAGMETA-2520 Dezembro Apuração Aberto ASPLAGMETA-2521 Apurado no período Apuração Aberto</t>
+        </is>
+      </c>
+      <c r="AU165" t="inlineStr">
+        <is>
+          <t>(31) 3232-2687</t>
+        </is>
+      </c>
       <c r="AV165" t="inlineStr">
         <is>
           <t>Estado</t>
@@ -37650,7 +37578,7 @@
       <c r="AZ165" t="inlineStr"/>
       <c r="BA165" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>100</t>
         </is>
       </c>
       <c r="BB165" t="inlineStr">
@@ -37679,7 +37607,7 @@
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
-          <t>[ASPLAGMETA-2127] TJMG 59 - Julgar, até 31/12/2025, 85% (oitenta e cinco por cento) das ações coletivas distribuídas até 31/12/2023 no 2º Grau.</t>
+          <t>[ASPLAGMETA-2132] TJMG 95 - Executar, no ano de 2025, 100% (cem por cento) das atividades previstas no projeto de Aprimoramento da Gestão de Cobrança de Custas Processuais.</t>
         </is>
       </c>
       <c r="F166" t="inlineStr"/>
@@ -37695,7 +37623,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Diretora de Secretaria</t>
+          <t>Diretora</t>
         </is>
       </c>
       <c r="J166" t="inlineStr"/>
@@ -37718,19 +37646,15 @@
       <c r="O166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>1ª Vice Presidência</t>
+          <t>Presidência</t>
         </is>
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>sepad@tjmg.jus.br</t>
-        </is>
-      </c>
-      <c r="R166" t="inlineStr">
-        <is>
-          <t>asplag@tjmg.jus.br</t>
-        </is>
-      </c>
+          <t>dirsup@tjmg.jus.br</t>
+        </is>
+      </c>
+      <c r="R166" t="inlineStr"/>
       <c r="S166" t="inlineStr">
         <is>
           <t>Responsável</t>
@@ -37745,7 +37669,7 @@
       <c r="V166" t="inlineStr"/>
       <c r="W166" t="inlineStr">
         <is>
-          <t>CEINJUR.</t>
+          <t>Cronograma da Iniciativa Estratégica.</t>
         </is>
       </c>
       <c r="X166" t="inlineStr">
@@ -37755,24 +37679,24 @@
       </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>Fórmula = ((∑ item4 + item5) / (item1 + item5 + ∑item2 - ∑item 3)) X 1000/k, onde: k = 8 para o período de referência “Até 31/12/2023”. Conforme parâmetros da Meta CNJ 6 no Glossário de 2020.</t>
+          <t>QAE/QAP X100, onde: QAP: Quantidade de atividades previstas. QAE: Quantidade de atividades executadas.</t>
         </is>
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>Sra. Elaine Batista Costa Souza</t>
+          <t>Sra. Elena Costa de Oliveira Vidigal</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025
-             - 6.5 - Índice de priorização de ações coletivas</t>
+             - 9.22 - Taxa de execução do projeto de Aprimoramento da Gestão de Cobrança de Custas Processuais.</t>
         </is>
       </c>
       <c r="AB166" t="inlineStr"/>
       <c r="AC166" t="inlineStr">
         <is>
-          <t>04 - Programa Agiliza-Jus. , 94 - Programa 1ª Vice SOMA - Suporte à organização, cumprimento de metas e aperfeiçoamento gerencial.</t>
+          <t>72 - Aprimoramento da Gestão de Cobrança de Custas Processuais.</t>
         </is>
       </c>
       <c r="AD166" t="inlineStr">
@@ -37788,21 +37712,21 @@
       <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="inlineStr">
         <is>
-          <t>6 - Consolidação do Sistema de Precedentes Obrigatórios</t>
+          <t>9 - Aprimoramento da Gestão Administrativa e da Governança Judiciária</t>
         </is>
       </c>
       <c r="AH166" t="inlineStr"/>
-      <c r="AI166" t="inlineStr">
-        <is>
-          <t>ASPLAG</t>
-        </is>
-      </c>
+      <c r="AI166" t="inlineStr"/>
       <c r="AJ166" t="inlineStr">
         <is>
           <t>16 - Paz, Justiça e Instituições Eficazes</t>
         </is>
       </c>
-      <c r="AK166" t="inlineStr"/>
+      <c r="AK166" t="inlineStr">
+        <is>
+          <t>DEPLAG , DIRFIN , SEPAD , SEGOVE , CORREGEDORIA</t>
+        </is>
+      </c>
       <c r="AL166" t="inlineStr">
         <is>
           <t>Dr. Marcelo Paulo Salgado</t>
@@ -37840,17 +37764,17 @@
       </c>
       <c r="AS166" t="inlineStr">
         <is>
-          <t>ASPLAGMETA-2602</t>
+          <t>ASPLAGMETA-2522</t>
         </is>
       </c>
       <c r="AT166" t="inlineStr">
         <is>
-          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2602 Janeiro Apuração Aberto ASPLAGMETA-2603 Fevereiro Apuração Aberto ASPLAGMETA-2604 Março Apuração Aberto ASPLAGMETA-2605 Abril Apuração Aberto ASPLAGMETA-2606 Maio Apuração Aberto ASPLAGMETA-2607 Junho Apuração Aberto ASPLAGMETA-2608 Julho Apuração Aberto ASPLAGMETA-2609 Agosto Apuração Aberto ASPLAGMETA-2610 Setembro Apuração Aberto ASPLAGMETA-2611 Outubro Apuração Aberto ASPLAGMETA-2612 Novembro Apuração Aberto ASPLAGMETA-2613 Dezembro Apuração Aberto ASPLAGMETA-2614 Apurado no período Apuração Aberto</t>
+          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2522 Janeiro Apuração Aberto ASPLAGMETA-2523 Fevereiro Apuração Aberto ASPLAGMETA-2524 Março Apuração Aberto ASPLAGMETA-2525 Abril Apuração Aberto ASPLAGMETA-2526 Maio Apuração Aberto ASPLAGMETA-2527 Junho Apuração Aberto ASPLAGMETA-2528 Julho Apuração Aberto ASPLAGMETA-2529 Agosto Apuração Aberto ASPLAGMETA-2530 Setembro Apuração Aberto ASPLAGMETA-2531 Outubro Apuração Aberto ASPLAGMETA-2532 Novembro Apuração Aberto ASPLAGMETA-2533 Dezembro Apuração Aberto ASPLAGMETA-2534 Apurado no período Apuração Aberto</t>
         </is>
       </c>
       <c r="AU166" t="inlineStr">
         <is>
-          <t>(31) 3232-2687</t>
+          <t>3232-2628</t>
         </is>
       </c>
       <c r="AV166" t="inlineStr">
@@ -37865,7 +37789,7 @@
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>SEPAD</t>
+          <t>DIRSUP</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr">
@@ -37876,7 +37800,7 @@
       <c r="AZ166" t="inlineStr"/>
       <c r="BA166" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>100</t>
         </is>
       </c>
       <c r="BB166" t="inlineStr">
@@ -37905,7 +37829,7 @@
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
-          <t>[ASPLAGMETA-2126] TJMG 29 - Julgar, em 2025, em até 100 (cem) dias, 80% (oitenta por cento) dos processos vinculados em razão de repercussão geral e repetitividade de recursos e feitos após trânsito em julgado do tema 2º Grau.</t>
+          <t>[ASPLAGMETA-2131] TJMG 62 - Cumprir, até dezembro de 2025, 100% (cem por cento) das entregas previstas, para o ano, no Programa INOVA TJMG.</t>
         </is>
       </c>
       <c r="F167" t="inlineStr"/>
@@ -37921,7 +37845,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Diretora de Secretaria</t>
+          <t>Assessor Técnico II</t>
         </is>
       </c>
       <c r="J167" t="inlineStr"/>
@@ -37944,19 +37868,11 @@
       <c r="O167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>1ª Vice Presidência</t>
-        </is>
-      </c>
-      <c r="Q167" t="inlineStr">
-        <is>
-          <t>sepad@tjmg.jus.br</t>
-        </is>
-      </c>
-      <c r="R167" t="inlineStr">
-        <is>
-          <t>asplag@tjmg.jus.br</t>
-        </is>
-      </c>
+          <t>Presidência</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr"/>
+      <c r="R167" t="inlineStr"/>
       <c r="S167" t="inlineStr">
         <is>
           <t>Responsável</t>
@@ -37971,7 +37887,7 @@
       <c r="V167" t="inlineStr"/>
       <c r="W167" t="inlineStr">
         <is>
-          <t>CEINJUR</t>
+          <t>Cronograma da Iniciativa Estratégica.</t>
         </is>
       </c>
       <c r="X167" t="inlineStr">
@@ -37981,24 +37897,24 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>Resultado do indicador: PVTTJ/TPV X 100, onde: PVTTJ = Processos Vinculados a Tema de repercussão geral e repetitividade Transitados em Julgado, julgados em até 100 dias. TPV = Total de Processos Vinculados a tema de repercussão geral e repetitividade. PVTT  ∑ Processos Vinculados a Tema de repercussão geral e repetitividade Transitados em Julgado, julgados em até 100 dias. [(data da conclusão do processo) - (data de julgamento) =&lt; 100 dias}</t>
+          <t>Quantidade de entregas implementadas / Quantidade total de entregas previstas X 100.</t>
         </is>
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>Sra. Elaine Batista Costa Souza</t>
+          <t>Priscila Pereira de Souza</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025
-             - 6.1 - Taxa de julgamento de processos vinculados em razão de repercussão geral e repetitividade em até 100 (cem) dias</t>
+             - 9.13 - Taxa de entregas realizadas pelo UAI-Lab previstas no Programa Inova TJMG.</t>
         </is>
       </c>
       <c r="AB167" t="inlineStr"/>
       <c r="AC167" t="inlineStr">
         <is>
-          <t>04 - Programa Agiliza-Jus. , 94 - Programa 1ª Vice SOMA - Suporte à organização, cumprimento de metas e aperfeiçoamento gerencial.</t>
+          <t>43 - Programa INOVA TJMG.</t>
         </is>
       </c>
       <c r="AD167" t="inlineStr">
@@ -38014,29 +37930,29 @@
       <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="inlineStr">
         <is>
-          <t>6 - Consolidação do Sistema de Precedentes Obrigatórios</t>
+          <t>9 - Aprimoramento da Gestão Administrativa e da Governança Judiciária</t>
         </is>
       </c>
       <c r="AH167" t="inlineStr"/>
-      <c r="AI167" t="inlineStr">
-        <is>
-          <t>ASPLAG</t>
-        </is>
-      </c>
+      <c r="AI167" t="inlineStr"/>
       <c r="AJ167" t="inlineStr">
         <is>
           <t>16 - Paz, Justiça e Instituições Eficazes</t>
         </is>
       </c>
-      <c r="AK167" t="inlineStr"/>
+      <c r="AK167" t="inlineStr">
+        <is>
+          <t>DIRDEP</t>
+        </is>
+      </c>
       <c r="AL167" t="inlineStr">
         <is>
-          <t>Dr.  Marcelo Paulo Salgado</t>
+          <t>Desembargador Luiz Carlos de Azevedo Corrêa Junior</t>
         </is>
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>Mensal</t>
+          <t>Trimestral</t>
         </is>
       </c>
       <c r="AN167" t="inlineStr">
@@ -38066,19 +37982,15 @@
       </c>
       <c r="AS167" t="inlineStr">
         <is>
-          <t>ASPLAGMETA-2615</t>
+          <t>ASPLAGMETA-2535</t>
         </is>
       </c>
       <c r="AT167" t="inlineStr">
         <is>
-          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2615 Janeiro Apuração Aberto ASPLAGMETA-2616 Fevereiro Apuração Aberto ASPLAGMETA-2617 Março Apuração Aberto ASPLAGMETA-2618 Abril Apuração Aberto ASPLAGMETA-2619 Maio Apuração Aberto ASPLAGMETA-2620 Junho Apuração Aberto ASPLAGMETA-2621 Julho Apuração Aberto ASPLAGMETA-2622 Agosto Apuração Aberto ASPLAGMETA-2623 Setembro Apuração Aberto ASPLAGMETA-2624 Outubro Apuração Aberto ASPLAGMETA-2625 Novembro Apuração Aberto ASPLAGMETA-2626 Dezembro Apuração Aberto ASPLAGMETA-2627 Apurado no período Apuração Aberto</t>
-        </is>
-      </c>
-      <c r="AU167" t="inlineStr">
-        <is>
-          <t>(31) 3232-2687</t>
-        </is>
-      </c>
+          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2535 Janeiro Apuração Aberto ASPLAGMETA-2536 Fevereiro Apuração Aberto ASPLAGMETA-2537 Março Apuração Aberto ASPLAGMETA-2538 Abril Apuração Aberto ASPLAGMETA-2539 Maio Apuração Aberto ASPLAGMETA-2540 Junho Apuração Aberto ASPLAGMETA-2541 Julho Apuração Aberto ASPLAGMETA-2542 Agosto Apuração Aberto ASPLAGMETA-2543 Setembro Apuração Aberto ASPLAGMETA-2544 Outubro Apuração Aberto ASPLAGMETA-2545 Novembro Apuração Aberto ASPLAGMETA-2546 Dezembro Apuração Aberto ASPLAGMETA-2547 Apurado no período Apuração Aberto</t>
+        </is>
+      </c>
+      <c r="AU167" t="inlineStr"/>
       <c r="AV167" t="inlineStr">
         <is>
           <t>Estado</t>
@@ -38091,7 +38003,7 @@
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>SEPAD</t>
+          <t>NUGIN</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
@@ -38102,7 +38014,7 @@
       <c r="AZ167" t="inlineStr"/>
       <c r="BA167" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>100</t>
         </is>
       </c>
       <c r="BB167" t="inlineStr">
@@ -38131,7 +38043,7 @@
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
-          <t>[ASPLAGMETA-2125] TJMG 140 - Realizar ao menos 25 (vinte e cinco) círculos de construção de paz utilizando as técnicas da justiça restaurativa, no ano de 2025.</t>
+          <t>[ASPLAGMETA-2130] TJMG 40 - Implantar o Desdobramento do Planejamento Estratégico - DPE em 30 (trinta) Unidades Judiciárias de 1º grau até 31/12/2025.</t>
         </is>
       </c>
       <c r="F168" t="inlineStr"/>
@@ -38145,7 +38057,11 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="I168" t="inlineStr"/>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Diretora de Secretaria</t>
+        </is>
+      </c>
       <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr">
         <is>
@@ -38166,12 +38082,12 @@
       <c r="O168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>3ª Vice Presidência</t>
+          <t>Corregedoria</t>
         </is>
       </c>
       <c r="Q168" t="inlineStr">
         <is>
-          <t>agin@tjmg.jus.br</t>
+          <t>seplan@tjmg.jus.br</t>
         </is>
       </c>
       <c r="R168" t="inlineStr">
@@ -38191,24 +38107,36 @@
       </c>
       <c r="U168" t="inlineStr"/>
       <c r="V168" t="inlineStr"/>
-      <c r="W168" t="inlineStr"/>
+      <c r="W168" t="inlineStr">
+        <is>
+          <t>NUPLAN - Núcleo de Suporte ao Planejamento e à Gestão da Primeira Instância. Cronograma da iniciativa 11 em 2025.</t>
+        </is>
+      </c>
       <c r="X168" t="inlineStr">
         <is>
           <t>Soma</t>
         </is>
       </c>
-      <c r="Y168" t="inlineStr"/>
-      <c r="Z168" t="inlineStr"/>
+      <c r="Y168" t="inlineStr">
+        <is>
+          <t>Somatório de Unidades Judiciárias de 1º grau que implantaram a metodologia do Desdobramento do Planejamento Estratégico no ano.</t>
+        </is>
+      </c>
+      <c r="Z168" t="inlineStr">
+        <is>
+          <t>Sra. Bruna Eduarda Medeiros de Sousa</t>
+        </is>
+      </c>
       <c r="AA168" t="inlineStr">
         <is>
           <t>2025
-             - 5. 12 - Número de círculos de construção de paz realizados.</t>
+             - 9.1 - Número de Unidades Judiciárias de 1º grau que implantaram o Desdobramento do Planejamento Estratégico.</t>
         </is>
       </c>
       <c r="AB168" t="inlineStr"/>
       <c r="AC168" t="inlineStr">
         <is>
-          <t>07 - Programa de estruturação de políticas públicas autocompositivas de solução de conflitos. , 47 - Programa de otimização do funcionamento dos CEJUSCs - Centros Judiciários de Solução de Conflitos e Cidadania.</t>
+          <t>11 - Desdobramento do Planejamento Estratégico pelas Unidades Judiciárias de 1º grau de jurisdição.</t>
         </is>
       </c>
       <c r="AD168" t="inlineStr">
@@ -38224,7 +38152,7 @@
       <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="inlineStr">
         <is>
-          <t>5 - Prevenção de Litígios e Adoção de Soluções Consensuais para os Conflitos</t>
+          <t>9 - Aprimoramento da Gestão Administrativa e da Governança Judiciária</t>
         </is>
       </c>
       <c r="AH168" t="inlineStr"/>
@@ -38240,17 +38168,17 @@
       </c>
       <c r="AK168" t="inlineStr">
         <is>
-          <t>AGIN</t>
+          <t>NUPLAN , EJEF</t>
         </is>
       </c>
       <c r="AL168" t="inlineStr">
         <is>
-          <t>Rogério Medeiros Garcia de Lima</t>
+          <t>Dr. Guilherme Lima Nogueira da Silva</t>
         </is>
       </c>
       <c r="AM168" t="inlineStr">
         <is>
-          <t>Trimestral</t>
+          <t>Mensal</t>
         </is>
       </c>
       <c r="AN168" t="inlineStr">
@@ -38280,17 +38208,17 @@
       </c>
       <c r="AS168" t="inlineStr">
         <is>
-          <t>ASPLAGMETA-2628</t>
+          <t>ASPLAGMETA-2548</t>
         </is>
       </c>
       <c r="AT168" t="inlineStr">
         <is>
-          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2628 Janeiro Apuração Aberto ASPLAGMETA-2629 Fevereiro Apuração Aberto ASPLAGMETA-2630 Março Apuração Aberto ASPLAGMETA-2631 Abril Apuração Aberto ASPLAGMETA-2632 Maio Apuração Aberto ASPLAGMETA-2633 Junho Apuração Aberto ASPLAGMETA-2634 Julho Apuração Aberto ASPLAGMETA-2635 Agosto Apuração Aberto ASPLAGMETA-2636 Setembro Apuração Aberto ASPLAGMETA-2637 Outubro Apuração Aberto ASPLAGMETA-2638 Novembro Apuração Aberto ASPLAGMETA-2639 Dezembro Apuração Aberto ASPLAGMETA-2640 Apurado no período Apuração Aberto</t>
+          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2548 Janeiro Apuração Aberto ASPLAGMETA-2549 Fevereiro Apuração Aberto ASPLAGMETA-2550 Março Apuração Aberto ASPLAGMETA-2551 Abril Apuração Aberto ASPLAGMETA-2552 Maio Apuração Aberto ASPLAGMETA-2553 Junho Apuração Aberto ASPLAGMETA-2554 Julho Apuração Aberto ASPLAGMETA-2555 Agosto Apuração Aberto ASPLAGMETA-2556 Setembro Apuração Aberto ASPLAGMETA-2557 Outubro Apuração Aberto ASPLAGMETA-2558 Novembro Apuração Aberto ASPLAGMETA-2559 Dezembro Apuração Aberto ASPLAGMETA-2560 Apurado no período Apuração Aberto</t>
         </is>
       </c>
       <c r="AU168" t="inlineStr">
         <is>
-          <t>(31) 3232-2615</t>
+          <t>(31) 3237-1904</t>
         </is>
       </c>
       <c r="AV168" t="inlineStr">
@@ -38305,7 +38233,7 @@
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Superintendência da Gestão de Inovação</t>
+          <t>SEPLAN</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
@@ -38316,7 +38244,7 @@
       <c r="AZ168" t="inlineStr"/>
       <c r="BA168" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="BB168" t="inlineStr">
@@ -38345,7 +38273,7 @@
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr">
         <is>
-          <t>[ASPLAGMETA-2124] TJMG 139 - Implementar ao menos 5 (cinco) projetos em Justiça Restaurativa no ano de 2025.</t>
+          <t>[ASPLAGMETA-2129] TJMG 135 - Exercer, em 2025, o juízo de admissibilidade em 100% (cem por cento) dos processos relacionados a IRDRs/IACs em até 150 (cento e cinquenta) dias após a distribuição do requerimento.</t>
         </is>
       </c>
       <c r="F169" t="inlineStr"/>
@@ -38359,11 +38287,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>Gerente</t>
-        </is>
-      </c>
+      <c r="I169" t="inlineStr"/>
       <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr">
         <is>
@@ -38384,19 +38308,11 @@
       <c r="O169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>3ª Vice Presidência</t>
-        </is>
-      </c>
-      <c r="Q169" t="inlineStr">
-        <is>
-          <t>agin@tjmg.jus.br</t>
-        </is>
-      </c>
-      <c r="R169" t="inlineStr">
-        <is>
-          <t>asplag@tjmg.jus.br</t>
-        </is>
-      </c>
+          <t>1ª Vice Presidência</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr"/>
+      <c r="R169" t="inlineStr"/>
       <c r="S169" t="inlineStr">
         <is>
           <t>Responsável</t>
@@ -38412,25 +38328,25 @@
       <c r="W169" t="inlineStr"/>
       <c r="X169" t="inlineStr">
         <is>
-          <t>Soma</t>
+          <t>Média</t>
         </is>
       </c>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>Somatório do número de círculos de construção de paz realizados no ano de 2025.</t>
+          <t>Número de juízos de admissibilidade em até 150 dias/ número de juízos de admissibilidade no período X 100 = percentual de alcance da meta.</t>
         </is>
       </c>
       <c r="Z169" t="inlineStr"/>
       <c r="AA169" t="inlineStr">
         <is>
           <t>2025
-             - 5. 11 - Número de projetos em Justiça Restaurativa implementados.</t>
+             - 6.7 - Taxa de Juízo de admissibilidade de IRDR/IAC em até 150 (cento e cinquenta) dias.</t>
         </is>
       </c>
       <c r="AB169" t="inlineStr"/>
       <c r="AC169" t="inlineStr">
         <is>
-          <t>07 - Programa de estruturação de políticas públicas autocompositivas de solução de conflitos. , 47 - Programa de otimização do funcionamento dos CEJUSCs - Centros Judiciários de Solução de Conflitos e Cidadania.</t>
+          <t>04 - Programa Agiliza-Jus. , 75 - Ampliação da Eficácia da Sistemática dos Precedentes Qualificados. , 94 - Programa 1ª Vice SOMA - Suporte à organização, cumprimento de metas e aperfeiçoamento gerencial.</t>
         </is>
       </c>
       <c r="AD169" t="inlineStr">
@@ -38446,33 +38362,21 @@
       <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="inlineStr">
         <is>
-          <t>5 - Prevenção de Litígios e Adoção de Soluções Consensuais para os Conflitos</t>
+          <t>6 - Consolidação do Sistema de Precedentes Obrigatórios</t>
         </is>
       </c>
       <c r="AH169" t="inlineStr"/>
-      <c r="AI169" t="inlineStr">
-        <is>
-          <t>ASPLAG</t>
-        </is>
-      </c>
+      <c r="AI169" t="inlineStr"/>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>5 - Igualdade de Gênero , 16 - Paz, Justiça e Instituições Eficazes</t>
-        </is>
-      </c>
-      <c r="AK169" t="inlineStr">
-        <is>
-          <t>AGIN</t>
-        </is>
-      </c>
-      <c r="AL169" t="inlineStr">
-        <is>
-          <t>Rogério Medeiros Garcia de Lima</t>
-        </is>
-      </c>
+          <t>16 - Paz, Justiça e Instituições Eficazes</t>
+        </is>
+      </c>
+      <c r="AK169" t="inlineStr"/>
+      <c r="AL169" t="inlineStr"/>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>Trimestral</t>
+          <t>Mensal</t>
         </is>
       </c>
       <c r="AN169" t="inlineStr">
@@ -38502,19 +38406,15 @@
       </c>
       <c r="AS169" t="inlineStr">
         <is>
-          <t>ASPLAGMETA-2169</t>
+          <t>ASPLAGMETA-2561</t>
         </is>
       </c>
       <c r="AT169" t="inlineStr">
         <is>
-          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2169 Janeiro Apuração Aberto ASPLAGMETA-2170 Fevereiro Apuração Aberto ASPLAGMETA-2171 Março Apuração Aberto ASPLAGMETA-2172 Abril Apuração Aberto ASPLAGMETA-2173 Maio Apuração Aberto ASPLAGMETA-2174 Junho Apuração Aberto ASPLAGMETA-2175 Julho Apuração Aberto ASPLAGMETA-2176 Agosto Apuração Aberto ASPLAGMETA-2177 Setembro Apuração Aberto ASPLAGMETA-2178 Outubro Apuração Aberto ASPLAGMETA-2179 Novembro Apuração Aberto ASPLAGMETA-2180 Dezembro Apuração Aberto ASPLAGMETA-2181 Apurado no período Apuração Aberto</t>
-        </is>
-      </c>
-      <c r="AU169" t="inlineStr">
-        <is>
-          <t>(31) 3232-2615</t>
-        </is>
-      </c>
+          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2561 Janeiro Apuração Aberto ASPLAGMETA-2562 Fevereiro Apuração Aberto ASPLAGMETA-2563 Março Apuração Aberto ASPLAGMETA-2564 Abril Apuração Aberto ASPLAGMETA-2565 Maio Apuração Aberto ASPLAGMETA-2566 Junho Apuração Aberto ASPLAGMETA-2567 Julho Apuração Aberto ASPLAGMETA-2568 Agosto Apuração Aberto ASPLAGMETA-2569 Setembro Apuração Aberto ASPLAGMETA-2570 Outubro Apuração Aberto ASPLAGMETA-2571 Outubro Apuração Aberto ASPLAGMETA-2572 Novembro Apuração Aberto ASPLAGMETA-2573 Dezembro Apuração Aberto ASPLAGMETA-2574 Apurado no período Apuração Aberto</t>
+        </is>
+      </c>
+      <c r="AU169" t="inlineStr"/>
       <c r="AV169" t="inlineStr">
         <is>
           <t>Estado</t>
@@ -38527,18 +38427,18 @@
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Superintendência da Gestão de Inovação</t>
+          <t>SEPAD</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
         <is>
-          <t>Unidade</t>
+          <t>Percentual</t>
         </is>
       </c>
       <c r="AZ169" t="inlineStr"/>
       <c r="BA169" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>100</t>
         </is>
       </c>
       <c r="BB169" t="inlineStr">
@@ -38567,7 +38467,7 @@
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
-          <t>[ASPLAGMETA-2123] TJMG 138 - Promover, em 2025, um atendimento de, no mínimo, 1200 (um mil e duzentos) procedimentos pré-processuais de reconhecimento de paternidade.</t>
+          <t>[ASPLAGMETA-2128] TJMG 134 - Julgar, em 2025, 60% (sessenta por cento) dos IRDRs/IACS em até 320 (trezentos e vinte) dias após a admissão, (desconsiderado o tempo médio de permanência em carga a Advogados ou Órgãos Externos, 25 (vinte e cinco) dias).</t>
         </is>
       </c>
       <c r="F170" t="inlineStr"/>
@@ -38602,19 +38502,11 @@
       <c r="O170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>3ª Vice Presidência</t>
-        </is>
-      </c>
-      <c r="Q170" t="inlineStr">
-        <is>
-          <t>agin@tjmg.jus.br</t>
-        </is>
-      </c>
-      <c r="R170" t="inlineStr">
-        <is>
-          <t>asplag@tjmg.jus.br</t>
-        </is>
-      </c>
+          <t>1ª Vice Presidência</t>
+        </is>
+      </c>
+      <c r="Q170" t="inlineStr"/>
+      <c r="R170" t="inlineStr"/>
       <c r="S170" t="inlineStr">
         <is>
           <t>Responsável</t>
@@ -38630,21 +38522,25 @@
       <c r="W170" t="inlineStr"/>
       <c r="X170" t="inlineStr">
         <is>
-          <t>Soma</t>
-        </is>
-      </c>
-      <c r="Y170" t="inlineStr"/>
+          <t>Último Valor</t>
+        </is>
+      </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>JIRDR-IAC280d/TJ X 100, onde: JIRDR-IAC320d = Número de julgamentos de mérito realizados em até 320dias. TJ = Total de julgamentos realizados no período. JIRDR-IAC280d = ∑ dos processos com julgamento de mérito [(data de conclusão após a admissibilidade do processo) - (data do julgamento) =&lt; 320dias</t>
+        </is>
+      </c>
       <c r="Z170" t="inlineStr"/>
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025
-             - 5.6 - Número de procedimentos pré-processuais de reconhecimento de paternidade tratados no âmbito dos Centros Judiciários de Solução de Conflitos e Cidadania no setor pré-processual ou no programa Paternidade para Todos.</t>
+             - 6.6 - Taxa de julgamento de IRDR/IAC em até 320 (trezentos e vinte) dias.</t>
         </is>
       </c>
       <c r="AB170" t="inlineStr"/>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>07 - Programa de estruturação de políticas públicas autocompositivas de solução de conflitos. , 47 - Programa de otimização do funcionamento dos CEJUSCs - Centros Judiciários de Solução de Conflitos e Cidadania.</t>
+          <t>04 - Programa Agiliza-Jus. , 75 - Ampliação da Eficácia da Sistemática dos Precedentes Qualificados. , 94 - Programa 1ª Vice SOMA - Suporte à organização, cumprimento de metas e aperfeiçoamento gerencial.</t>
         </is>
       </c>
       <c r="AD170" t="inlineStr">
@@ -38660,26 +38556,18 @@
       <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="inlineStr">
         <is>
-          <t>5 - Prevenção de Litígios e Adoção de Soluções Consensuais para os Conflitos</t>
+          <t>6 - Consolidação do Sistema de Precedentes Obrigatórios</t>
         </is>
       </c>
       <c r="AH170" t="inlineStr"/>
-      <c r="AI170" t="inlineStr">
-        <is>
-          <t>ASPLAG</t>
-        </is>
-      </c>
+      <c r="AI170" t="inlineStr"/>
       <c r="AJ170" t="inlineStr">
         <is>
           <t>16 - Paz, Justiça e Instituições Eficazes</t>
         </is>
       </c>
       <c r="AK170" t="inlineStr"/>
-      <c r="AL170" t="inlineStr">
-        <is>
-          <t>Rogério Medeiros Garcia de Lima</t>
-        </is>
-      </c>
+      <c r="AL170" t="inlineStr"/>
       <c r="AM170" t="inlineStr">
         <is>
           <t>Trimestral</t>
@@ -38712,19 +38600,15 @@
       </c>
       <c r="AS170" t="inlineStr">
         <is>
-          <t>ASPLAGMETA-2641</t>
+          <t>ASPLAGMETA-2575</t>
         </is>
       </c>
       <c r="AT170" t="inlineStr">
         <is>
-          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2641 Janeiro Apuração Aberto ASPLAGMETA-2642 Fevereiro Apuração Aberto ASPLAGMETA-2643 Março Apuração Aberto ASPLAGMETA-2644 Abril Apuração Aberto ASPLAGMETA-2645 Maio Apuração Aberto ASPLAGMETA-2646 Junho Apuração Aberto ASPLAGMETA-2647 Julho Apuração Aberto ASPLAGMETA-2648 Agosto Apuração Aberto ASPLAGMETA-2649 Setembro Apuração Aberto ASPLAGMETA-2650 Outubro Apuração Aberto ASPLAGMETA-2651 Novembro Apuração Aberto ASPLAGMETA-2652 Dezembro Apuração Aberto ASPLAGMETA-2653 Apurado no período Apuração Aberto</t>
-        </is>
-      </c>
-      <c r="AU170" t="inlineStr">
-        <is>
-          <t>(31) 3232-2615</t>
-        </is>
-      </c>
+          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2575 Janeiro Apuração Aberto ASPLAGMETA-2576 Fevereiro Apuração Aberto ASPLAGMETA-2577 Março Apuração Aberto ASPLAGMETA-2578 Abril Apuração Aberto ASPLAGMETA-2579 Maio Apuração Aberto ASPLAGMETA-2580 Junho Apuração Aberto ASPLAGMETA-2581 Julho Apuração Aberto ASPLAGMETA-2582 Agosto Apuração Aberto ASPLAGMETA-2583 Setembro Apuração Aberto ASPLAGMETA-2584 Outubro Apuração Aberto ASPLAGMETA-2586 Novembro Apuração Aberto ASPLAGMETA-2587 Dezembro Apuração Aberto ASPLAGMETA-2591 Apurado no período Apuração Aberto</t>
+        </is>
+      </c>
+      <c r="AU170" t="inlineStr"/>
       <c r="AV170" t="inlineStr">
         <is>
           <t>Estado</t>
@@ -38737,18 +38621,18 @@
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Superintendência da Gestão de Inovação</t>
+          <t>SEPAD</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr">
         <is>
-          <t>Unidade</t>
+          <t>Percentual</t>
         </is>
       </c>
       <c r="AZ170" t="inlineStr"/>
       <c r="BA170" t="inlineStr">
         <is>
-          <t>1.200</t>
+          <t>60</t>
         </is>
       </c>
       <c r="BB170" t="inlineStr">
@@ -38777,7 +38661,7 @@
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
-          <t>[ASPLAGMETA-2122] TJMG 97 - Aumentar, em 2025, uma média de pelo menos 1% (um por cento) no número de sessões agendadas nos CEJUSCs em relação ao ano anterior.</t>
+          <t>[ASPLAGMETA-2127] TJMG 59 - Julgar, até 31/12/2025, 85% (oitenta e cinco por cento) das ações coletivas distribuídas até 31/12/2023 no 2º Grau.</t>
         </is>
       </c>
       <c r="F171" t="inlineStr"/>
@@ -38793,7 +38677,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Gerente</t>
+          <t>Diretora de Secretaria</t>
         </is>
       </c>
       <c r="J171" t="inlineStr"/>
@@ -38816,12 +38700,12 @@
       <c r="O171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>3ª Vice Presidência</t>
+          <t>1ª Vice Presidência</t>
         </is>
       </c>
       <c r="Q171" t="inlineStr">
         <is>
-          <t>agin@tjmg.jus.br</t>
+          <t>sepad@tjmg.jus.br</t>
         </is>
       </c>
       <c r="R171" t="inlineStr">
@@ -38841,7 +38725,11 @@
       </c>
       <c r="U171" t="inlineStr"/>
       <c r="V171" t="inlineStr"/>
-      <c r="W171" t="inlineStr"/>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>CEINJUR.</t>
+        </is>
+      </c>
       <c r="X171" t="inlineStr">
         <is>
           <t>Último Valor</t>
@@ -38849,20 +38737,24 @@
       </c>
       <c r="Y171" t="inlineStr">
         <is>
-          <t>Quantidade de sessões de conciliação processuais agendadas + Nùmero de Sessões de Conciliação Pré-Processuais Agendadas + Número de Sessões de Mediação Processuais Agendadas + Nùmero de Sessões de Mediação Pré-Processuais Agendadas em 2025 no âmbito dos CEJUSCs / (sobre) qtd de Sessões de Conciliação Processuais Agendadas + Número de Sessões de Conciliação Pré-Processuais Agendadas + Número de Sessões de Mediação Processuais Agendadas + Número de Sessões de Mediação Pré-Processuais Agendadas em 2024 no âmbito dos CEJUSCs)-1]x100</t>
-        </is>
-      </c>
-      <c r="Z171" t="inlineStr"/>
+          <t>Fórmula = ((∑ item4 + item5) / (item1 + item5 + ∑item2 - ∑item 3)) X 1000/k, onde: k = 8 para o período de referência “Até 31/12/2023”. Conforme parâmetros da Meta CNJ 6 no Glossário de 2020.</t>
+        </is>
+      </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>Sra. Elaine Batista Costa Souza</t>
+        </is>
+      </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>2025
-             - 5.9 - Percentual de sessões agendadas nos Cejuscs.</t>
+             - 6.5 - Índice de priorização de ações coletivas</t>
         </is>
       </c>
       <c r="AB171" t="inlineStr"/>
       <c r="AC171" t="inlineStr">
         <is>
-          <t>07 - Programa de estruturação de políticas públicas autocompositivas de solução de conflitos. , 47 - Programa de otimização do funcionamento dos CEJUSCs - Centros Judiciários de Solução de Conflitos e Cidadania.</t>
+          <t>04 - Programa Agiliza-Jus. , 94 - Programa 1ª Vice SOMA - Suporte à organização, cumprimento de metas e aperfeiçoamento gerencial.</t>
         </is>
       </c>
       <c r="AD171" t="inlineStr">
@@ -38878,7 +38770,7 @@
       <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="inlineStr">
         <is>
-          <t>5 - Prevenção de Litígios e Adoção de Soluções Consensuais para os Conflitos</t>
+          <t>6 - Consolidação do Sistema de Precedentes Obrigatórios</t>
         </is>
       </c>
       <c r="AH171" t="inlineStr"/>
@@ -38895,7 +38787,7 @@
       <c r="AK171" t="inlineStr"/>
       <c r="AL171" t="inlineStr">
         <is>
-          <t>Rogério Medeiros Garcia de Lima.</t>
+          <t>Dr. Marcelo Paulo Salgado</t>
         </is>
       </c>
       <c r="AM171" t="inlineStr">
@@ -38930,17 +38822,17 @@
       </c>
       <c r="AS171" t="inlineStr">
         <is>
-          <t>ASPLAGMETA-2143</t>
+          <t>ASPLAGMETA-2602</t>
         </is>
       </c>
       <c r="AT171" t="inlineStr">
         <is>
-          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2143 Janeiro Apuração Aberto ASPLAGMETA-2144 Fevereiro Apuração Aberto ASPLAGMETA-2145 Março Apuração Aberto ASPLAGMETA-2146 Abril Apuração Aberto ASPLAGMETA-2147 Maio Apuração Aberto ASPLAGMETA-2148 Junho Apuração Aberto ASPLAGMETA-2149 Julho Apuração Aberto ASPLAGMETA-2150 Agosto Apuração Aberto ASPLAGMETA-2151 Setembro Apuração Aberto ASPLAGMETA-2152 Outubro Apuração Aberto ASPLAGMETA-2153 Novembro Apuração Aberto ASPLAGMETA-2154 Dezembro Apuração Aberto ASPLAGMETA-2155 Apurado no período Apuração Aberto</t>
+          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2602 Janeiro Apuração Aberto ASPLAGMETA-2603 Fevereiro Apuração Aberto ASPLAGMETA-2604 Março Apuração Aberto ASPLAGMETA-2605 Abril Apuração Aberto ASPLAGMETA-2606 Maio Apuração Aberto ASPLAGMETA-2607 Junho Apuração Aberto ASPLAGMETA-2608 Julho Apuração Aberto ASPLAGMETA-2609 Agosto Apuração Aberto ASPLAGMETA-2610 Setembro Apuração Aberto ASPLAGMETA-2611 Outubro Apuração Aberto ASPLAGMETA-2612 Novembro Apuração Aberto ASPLAGMETA-2613 Dezembro Apuração Aberto ASPLAGMETA-2614 Apurado no período Apuração Aberto</t>
         </is>
       </c>
       <c r="AU171" t="inlineStr">
         <is>
-          <t>(31) 3232-2615</t>
+          <t>(31) 3232-2687</t>
         </is>
       </c>
       <c r="AV171" t="inlineStr">
@@ -38955,7 +38847,7 @@
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Superintendência da Gestão de Inovação</t>
+          <t>SEPAD</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr">
@@ -38966,7 +38858,7 @@
       <c r="AZ171" t="inlineStr"/>
       <c r="BA171" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BB171" t="inlineStr">
@@ -38995,7 +38887,7 @@
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
-          <t>[ASPLAGMETA-2121] TJMG 149 - Reduzir, até 31/12/2025, 50% (cinquenta por cento) dos feitos em que tenha cadastrado réu falecido.</t>
+          <t>[ASPLAGMETA-2126] TJMG 29 - Julgar, em 2025, em até 100 (cem) dias, 80% (oitenta por cento) dos processos vinculados em razão de repercussão geral e repetitividade de recursos e feitos após trânsito em julgado do tema 2º Grau.</t>
         </is>
       </c>
       <c r="F172" t="inlineStr"/>
@@ -39011,7 +38903,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>Diretor Executivo</t>
+          <t>Diretora de Secretaria</t>
         </is>
       </c>
       <c r="J172" t="inlineStr"/>
@@ -39034,12 +38926,12 @@
       <c r="O172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Corregedoria</t>
+          <t>1ª Vice Presidência</t>
         </is>
       </c>
       <c r="Q172" t="inlineStr">
         <is>
-          <t>dircor@tjmg.jus.br</t>
+          <t>sepad@tjmg.jus.br</t>
         </is>
       </c>
       <c r="R172" t="inlineStr">
@@ -39061,7 +38953,7 @@
       <c r="V172" t="inlineStr"/>
       <c r="W172" t="inlineStr">
         <is>
-          <t>Centro de Estatística Aplicada à Justiça de Primeira Instância (CEJUR) com informações extraídas de sistemas judiciais e paineis do TJMG.</t>
+          <t>CEINJUR</t>
         </is>
       </c>
       <c r="X172" t="inlineStr">
@@ -39071,24 +38963,24 @@
       </c>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>[(Quantidade de feitos em que tenha cadastrado réu falecido na data de apuração (RFf)) dividida Quantidade de feitos em que tenha cadastrado réu falecido em 31/12/2024 (RFi)) - 1] x 100</t>
+          <t>Resultado do indicador: PVTTJ/TPV X 100, onde: PVTTJ = Processos Vinculados a Tema de repercussão geral e repetitividade Transitados em Julgado, julgados em até 100 dias. TPV = Total de Processos Vinculados a tema de repercussão geral e repetitividade. PVTT  ∑ Processos Vinculados a Tema de repercussão geral e repetitividade Transitados em Julgado, julgados em até 100 dias. [(data da conclusão do processo) - (data de julgamento) =&lt; 100 dias}</t>
         </is>
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>Sr. Ricardo de Freitas Reis</t>
+          <t>Sra. Elaine Batista Costa Souza</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>2025
-             - 3.66 - Taxa de redução de feitos com indicação de réu falecido.</t>
+             - 6.1 - Taxa de julgamento de processos vinculados em razão de repercussão geral e repetitividade em até 100 (cem) dias</t>
         </is>
       </c>
       <c r="AB172" t="inlineStr"/>
       <c r="AC172" t="inlineStr">
         <is>
-          <t>05 - Programa de Melhoria de Indicadores do IPC-Jus TJMG.</t>
+          <t>04 - Programa Agiliza-Jus. , 94 - Programa 1ª Vice SOMA - Suporte à organização, cumprimento de metas e aperfeiçoamento gerencial.</t>
         </is>
       </c>
       <c r="AD172" t="inlineStr">
@@ -39104,7 +38996,7 @@
       <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="inlineStr">
         <is>
-          <t>3 - Agilidade e Produtividade na Prestação Jurisdicional</t>
+          <t>6 - Consolidação do Sistema de Precedentes Obrigatórios</t>
         </is>
       </c>
       <c r="AH172" t="inlineStr"/>
@@ -39118,19 +39010,15 @@
           <t>16 - Paz, Justiça e Instituições Eficazes</t>
         </is>
       </c>
-      <c r="AK172" t="inlineStr">
-        <is>
-          <t>CEJUR , COAPE , COSIS , GEFIS , GEINF , GESIS , SEPLAN</t>
-        </is>
-      </c>
+      <c r="AK172" t="inlineStr"/>
       <c r="AL172" t="inlineStr">
         <is>
-          <t>Dr. Guilherme Lima Nogueira da Silva</t>
+          <t>Dr.  Marcelo Paulo Salgado</t>
         </is>
       </c>
       <c r="AM172" t="inlineStr">
         <is>
-          <t>Trimestral</t>
+          <t>Mensal</t>
         </is>
       </c>
       <c r="AN172" t="inlineStr">
@@ -39160,17 +39048,17 @@
       </c>
       <c r="AS172" t="inlineStr">
         <is>
-          <t>ASPLAGMETA-2654</t>
+          <t>ASPLAGMETA-2615</t>
         </is>
       </c>
       <c r="AT172" t="inlineStr">
         <is>
-          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2654 Janeiro Apuração Aberto ASPLAGMETA-2655 Fevereiro Apuração Aberto ASPLAGMETA-2656 Março Apuração Aberto ASPLAGMETA-2657 Abril Apuração Aberto ASPLAGMETA-2658 Maio Apuração Aberto ASPLAGMETA-2659 Junho Apuração Aberto ASPLAGMETA-2660 Julho Apuração Aberto ASPLAGMETA-2661 Agosto Apuração Aberto ASPLAGMETA-2662 Setembro Apuração Aberto ASPLAGMETA-2663 Outubro Apuração Aberto ASPLAGMETA-2664 Novembro Apuração Aberto ASPLAGMETA-2665 Dezembro Apuração Aberto ASPLAGMETA-2666 Apurado no período Apuração Aberto</t>
+          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2615 Janeiro Apuração Aberto ASPLAGMETA-2616 Fevereiro Apuração Aberto ASPLAGMETA-2617 Março Apuração Aberto ASPLAGMETA-2618 Abril Apuração Aberto ASPLAGMETA-2619 Maio Apuração Aberto ASPLAGMETA-2620 Junho Apuração Aberto ASPLAGMETA-2621 Julho Apuração Aberto ASPLAGMETA-2622 Agosto Apuração Aberto ASPLAGMETA-2623 Setembro Apuração Aberto ASPLAGMETA-2624 Outubro Apuração Aberto ASPLAGMETA-2625 Novembro Apuração Aberto ASPLAGMETA-2626 Dezembro Apuração Aberto ASPLAGMETA-2627 Apurado no período Apuração Aberto</t>
         </is>
       </c>
       <c r="AU172" t="inlineStr">
         <is>
-          <t>(31) 3237-8259</t>
+          <t>(31) 3232-2687</t>
         </is>
       </c>
       <c r="AV172" t="inlineStr">
@@ -39185,7 +39073,7 @@
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>DIRCOR</t>
+          <t>SEPAD</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
@@ -39196,7 +39084,7 @@
       <c r="AZ172" t="inlineStr"/>
       <c r="BA172" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BB172" t="inlineStr">
@@ -39225,7 +39113,7 @@
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
-          <t>[ASPLAGMETA-2120] TJMG 148 - Reduzir, até 31/12/2025, em 4% (quatro por cento), o tempo médio de tramitação, em dias, dos feitos do acervo gerenciável, a partir da data de distribuição até a data da baixa, na Justiça Comum e no JESP</t>
+          <t>[ASPLAGMETA-2125] TJMG 140 - Realizar ao menos 25 (vinte e cinco) círculos de construção de paz utilizando as técnicas da justiça restaurativa, no ano de 2025.</t>
         </is>
       </c>
       <c r="F173" t="inlineStr"/>
@@ -39239,11 +39127,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>Diretor Executivo</t>
-        </is>
-      </c>
+      <c r="I173" t="inlineStr"/>
       <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr">
         <is>
@@ -39264,12 +39148,12 @@
       <c r="O173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Corregedoria</t>
+          <t>3ª Vice Presidência</t>
         </is>
       </c>
       <c r="Q173" t="inlineStr">
         <is>
-          <t>dircor@tjmg.jus.br</t>
+          <t>agin@tjmg.jus.br</t>
         </is>
       </c>
       <c r="R173" t="inlineStr">
@@ -39289,36 +39173,24 @@
       </c>
       <c r="U173" t="inlineStr"/>
       <c r="V173" t="inlineStr"/>
-      <c r="W173" t="inlineStr">
-        <is>
-          <t>Centro de Estatística Aplicada à Justiça de Primeira Instância (CEJUR) com informações extraídas de sistemas judiciais e paineis do TJMG.</t>
-        </is>
-      </c>
+      <c r="W173" t="inlineStr"/>
       <c r="X173" t="inlineStr">
         <is>
-          <t>Último Valor</t>
-        </is>
-      </c>
-      <c r="Y173" t="inlineStr">
-        <is>
-          <t>[(Tempo médio de tramitação dos feitos, da distribuição até a 1ª baixa, considerando os feitos que foram baixados até a data de apuração (TMTf) dividido pelo Tempo médio de tramitação dos feitos, da distribuição até a 1ª baixa, considerando os feitos que foram baixados até 31/12/2024 (TMTi)) -1] x 100 Consideram-se, no cômputo da meta, todos os feitos que tramitaram na Unidade Judiciária e não só os casos novos, o que justifica a expressão “acervo gerenciável” no texto da meta. Nesse sentido, são considerados, por exemplo, precatório e inquéritos.</t>
-        </is>
-      </c>
-      <c r="Z173" t="inlineStr">
-        <is>
-          <t>Sr. Ricardo de Freitas Reis</t>
-        </is>
-      </c>
+          <t>Soma</t>
+        </is>
+      </c>
+      <c r="Y173" t="inlineStr"/>
+      <c r="Z173" t="inlineStr"/>
       <c r="AA173" t="inlineStr">
         <is>
           <t>2025
-             - 3.65 - Taxa de redução do tempo médio de tramitação até a baixa do processo.</t>
+             - 5. 12 - Número de círculos de construção de paz realizados.</t>
         </is>
       </c>
       <c r="AB173" t="inlineStr"/>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>05 - Programa de Melhoria de Indicadores do IPC-Jus TJMG.</t>
+          <t>07 - Programa de estruturação de políticas públicas autocompositivas de solução de conflitos. , 47 - Programa de otimização do funcionamento dos CEJUSCs - Centros Judiciários de Solução de Conflitos e Cidadania.</t>
         </is>
       </c>
       <c r="AD173" t="inlineStr">
@@ -39334,7 +39206,7 @@
       <c r="AF173" t="inlineStr"/>
       <c r="AG173" t="inlineStr">
         <is>
-          <t>3 - Agilidade e Produtividade na Prestação Jurisdicional</t>
+          <t>5 - Prevenção de Litígios e Adoção de Soluções Consensuais para os Conflitos</t>
         </is>
       </c>
       <c r="AH173" t="inlineStr"/>
@@ -39350,12 +39222,12 @@
       </c>
       <c r="AK173" t="inlineStr">
         <is>
-          <t>CEJUR , COAPE , COSIS , GEFIS , GEINF , GESIS , SEPLAN</t>
+          <t>AGIN</t>
         </is>
       </c>
       <c r="AL173" t="inlineStr">
         <is>
-          <t>Dr. Guilherme Lima Nogueira da Silva</t>
+          <t>Rogério Medeiros Garcia de Lima</t>
         </is>
       </c>
       <c r="AM173" t="inlineStr">
@@ -39390,17 +39262,17 @@
       </c>
       <c r="AS173" t="inlineStr">
         <is>
-          <t>ASPLAGMETA-2667</t>
+          <t>ASPLAGMETA-2628</t>
         </is>
       </c>
       <c r="AT173" t="inlineStr">
         <is>
-          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2667 Janeiro Apuração Aberto ASPLAGMETA-2668 Fevereiro Apuração Aberto ASPLAGMETA-2669 Março Apuração Aberto ASPLAGMETA-2670 Abril Apuração Aberto ASPLAGMETA-2671 Maio Apuração Aberto ASPLAGMETA-2672 Junho Apuração Aberto ASPLAGMETA-2673 Julho Apuração Aberto ASPLAGMETA-2674 Agosto Apuração Aberto ASPLAGMETA-2675 Setembro Apuração Aberto ASPLAGMETA-2676 Outubro Apuração Aberto ASPLAGMETA-2677 Novembro Apuração Aberto ASPLAGMETA-2678 Dezembro Apuração Aberto ASPLAGMETA-2679 Apurado no período Apuração Aberto</t>
+          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2628 Janeiro Apuração Aberto ASPLAGMETA-2629 Fevereiro Apuração Aberto ASPLAGMETA-2630 Março Apuração Aberto ASPLAGMETA-2631 Abril Apuração Aberto ASPLAGMETA-2632 Maio Apuração Aberto ASPLAGMETA-2633 Junho Apuração Aberto ASPLAGMETA-2634 Julho Apuração Aberto ASPLAGMETA-2635 Agosto Apuração Aberto ASPLAGMETA-2636 Setembro Apuração Aberto ASPLAGMETA-2637 Outubro Apuração Aberto ASPLAGMETA-2638 Novembro Apuração Aberto ASPLAGMETA-2639 Dezembro Apuração Aberto ASPLAGMETA-2640 Apurado no período Apuração Aberto</t>
         </is>
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>(31) 3237-8259</t>
+          <t>(31) 3232-2615</t>
         </is>
       </c>
       <c r="AV173" t="inlineStr">
@@ -39415,18 +39287,18 @@
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>DIRCOR</t>
+          <t>Superintendência da Gestão de Inovação</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
         <is>
-          <t>Percentual</t>
+          <t>Unidade</t>
         </is>
       </c>
       <c r="AZ173" t="inlineStr"/>
       <c r="BA173" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>25</t>
         </is>
       </c>
       <c r="BB173" t="inlineStr">
@@ -39455,7 +39327,7 @@
       <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr">
         <is>
-          <t>[ASPLAGMETA-2119] TJMG 147 - Reduzir, até 31/12/2025, em 30% (dez por cento) o estoque dos processos paralisados sem motivo legal, há mais de 120 (cento e vinte) dias, em secretaria na Justiça Comum e no JESP (excluídos os feitos do SEEU).</t>
+          <t>[ASPLAGMETA-2124] TJMG 139 - Implementar ao menos 5 (cinco) projetos em Justiça Restaurativa no ano de 2025.</t>
         </is>
       </c>
       <c r="F174" t="inlineStr"/>
@@ -39471,7 +39343,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Diretor Executivo</t>
+          <t>Gerente</t>
         </is>
       </c>
       <c r="J174" t="inlineStr"/>
@@ -39494,12 +39366,12 @@
       <c r="O174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Corregedoria</t>
+          <t>3ª Vice Presidência</t>
         </is>
       </c>
       <c r="Q174" t="inlineStr">
         <is>
-          <t>dircor@tjmg.jus.br</t>
+          <t>agin@tjmg.jus.br</t>
         </is>
       </c>
       <c r="R174" t="inlineStr">
@@ -39519,36 +39391,28 @@
       </c>
       <c r="U174" t="inlineStr"/>
       <c r="V174" t="inlineStr"/>
-      <c r="W174" t="inlineStr">
-        <is>
-          <t>Centro de Estatística Aplicada à Justiça de Primeira Instância (CEJUR) com informações extraídas de sistemas judiciais e paineis do TJMG.</t>
-        </is>
-      </c>
+      <c r="W174" t="inlineStr"/>
       <c r="X174" t="inlineStr">
         <is>
-          <t>Último Valor</t>
+          <t>Soma</t>
         </is>
       </c>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>[(Quantidade de processos paralisados sem motivo legal há mais de 100 dias em secretaria na data de apuração (PSML120f) dividida pela Quantidade de processos paralisados sem motivo legal há mais de 100 dias em secretaria em 31/12/2024 (PSML120i)) -1] x 100</t>
-        </is>
-      </c>
-      <c r="Z174" t="inlineStr">
-        <is>
-          <t>Sr. Ricardo de Freitas Reis</t>
-        </is>
-      </c>
+          <t>Somatório do número de círculos de construção de paz realizados no ano de 2025.</t>
+        </is>
+      </c>
+      <c r="Z174" t="inlineStr"/>
       <c r="AA174" t="inlineStr">
         <is>
           <t>2025
-             - 3.64 - Taxa de redução de processos paralisados em secretaria sem motivo legal há mais de 120 (cento e vinte) dias.</t>
+             - 5. 11 - Número de projetos em Justiça Restaurativa implementados.</t>
         </is>
       </c>
       <c r="AB174" t="inlineStr"/>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>05 - Programa de Melhoria de Indicadores do IPC-Jus TJMG.</t>
+          <t>07 - Programa de estruturação de políticas públicas autocompositivas de solução de conflitos. , 47 - Programa de otimização do funcionamento dos CEJUSCs - Centros Judiciários de Solução de Conflitos e Cidadania.</t>
         </is>
       </c>
       <c r="AD174" t="inlineStr">
@@ -39564,7 +39428,7 @@
       <c r="AF174" t="inlineStr"/>
       <c r="AG174" t="inlineStr">
         <is>
-          <t>3 - Agilidade e Produtividade na Prestação Jurisdicional</t>
+          <t>5 - Prevenção de Litígios e Adoção de Soluções Consensuais para os Conflitos</t>
         </is>
       </c>
       <c r="AH174" t="inlineStr"/>
@@ -39575,17 +39439,17 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>16 - Paz, Justiça e Instituições Eficazes</t>
+          <t>5 - Igualdade de Gênero , 16 - Paz, Justiça e Instituições Eficazes</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
         <is>
-          <t>CEJUR , COAPE , COSIS , GEFIS , GEINF , GESIS , SEPLAN</t>
+          <t>AGIN</t>
         </is>
       </c>
       <c r="AL174" t="inlineStr">
         <is>
-          <t>Dr. Guilherme Lima Nogueira da Silva</t>
+          <t>Rogério Medeiros Garcia de Lima</t>
         </is>
       </c>
       <c r="AM174" t="inlineStr">
@@ -39620,17 +39484,17 @@
       </c>
       <c r="AS174" t="inlineStr">
         <is>
-          <t>ASPLAGMETA-2680</t>
+          <t>ASPLAGMETA-2169</t>
         </is>
       </c>
       <c r="AT174" t="inlineStr">
         <is>
-          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2680 Janeiro Apuração Aberto ASPLAGMETA-2681 Fevereiro Apuração Aberto ASPLAGMETA-2682 Março Apuração Aberto ASPLAGMETA-2683 Abril Apuração Aberto ASPLAGMETA-2684 Maio Apuração Aberto ASPLAGMETA-2685 Junho Apuração Aberto ASPLAGMETA-2686 Julho Apuração Aberto ASPLAGMETA-2687 Agosto Apuração Aberto ASPLAGMETA-2688 Setembro Apuração Aberto ASPLAGMETA-2689 Outubro Apuração Aberto ASPLAGMETA-2690 Novembro Apuração Aberto ASPLAGMETA-2691 Novembro Apuração Aberto ASPLAGMETA-2692 Dezembro Apuração Aberto ASPLAGMETA-2693 Apurado no período Apuração Aberto</t>
+          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2169 Janeiro Apuração Aberto ASPLAGMETA-2170 Fevereiro Apuração Aberto ASPLAGMETA-2171 Março Apuração Aberto ASPLAGMETA-2172 Abril Apuração Aberto ASPLAGMETA-2173 Maio Apuração Aberto ASPLAGMETA-2174 Junho Apuração Aberto ASPLAGMETA-2175 Julho Apuração Aberto ASPLAGMETA-2176 Agosto Apuração Aberto ASPLAGMETA-2177 Setembro Apuração Aberto ASPLAGMETA-2178 Outubro Apuração Aberto ASPLAGMETA-2179 Novembro Apuração Aberto ASPLAGMETA-2180 Dezembro Apuração Aberto ASPLAGMETA-2181 Apurado no período Apuração Aberto</t>
         </is>
       </c>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>(31) 3237-8259</t>
+          <t>(31) 3232-2615</t>
         </is>
       </c>
       <c r="AV174" t="inlineStr">
@@ -39645,18 +39509,18 @@
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>DIRCOR</t>
+          <t>Superintendência da Gestão de Inovação</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr">
         <is>
-          <t>Percentual</t>
+          <t>Unidade</t>
         </is>
       </c>
       <c r="AZ174" t="inlineStr"/>
       <c r="BA174" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="BB174" t="inlineStr">
@@ -39685,7 +39549,7 @@
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>[ASPLAGMETA-2118] TJMG 146 - Reduzir, até 31/12/2025, em 10% (dez por cento) o estoque dos processos conclusos para Sentença, Decisão e Despacho há mais de 100 (cem) dias na Justiça Comum e no JESP.</t>
+          <t>[ASPLAGMETA-2123] TJMG 138 - Promover, em 2025, um atendimento de, no mínimo, 1200 (um mil e duzentos) procedimentos pré-processuais de reconhecimento de paternidade.</t>
         </is>
       </c>
       <c r="F175" t="inlineStr"/>
@@ -39699,11 +39563,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>Diretor Executivo</t>
-        </is>
-      </c>
+      <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr">
         <is>
@@ -39724,12 +39584,12 @@
       <c r="O175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Corregedoria</t>
+          <t>3ª Vice Presidência</t>
         </is>
       </c>
       <c r="Q175" t="inlineStr">
         <is>
-          <t>dircor@tjmg.jus.br</t>
+          <t>agin@tjmg.jus.br</t>
         </is>
       </c>
       <c r="R175" t="inlineStr">
@@ -39749,36 +39609,24 @@
       </c>
       <c r="U175" t="inlineStr"/>
       <c r="V175" t="inlineStr"/>
-      <c r="W175" t="inlineStr">
-        <is>
-          <t>Centro de Estatística Aplicada à Justiça de Primeira Instância (CEJUR) com informações extraídas de sistemas judiciais e paineis do TJMG.</t>
-        </is>
-      </c>
+      <c r="W175" t="inlineStr"/>
       <c r="X175" t="inlineStr">
         <is>
-          <t>Último Valor</t>
-        </is>
-      </c>
-      <c r="Y175" t="inlineStr">
-        <is>
-          <t>[(Estoque de processos conclusos para Sentença, Decisão e Despacho há mais de 100 dias na data de apuração (C120f) dividido pelo Estoque de processos conclusos para Sentença, Decisão e Despacho há mais de 100 dias em 31/12/2024 (C120i)) -1] x 100.</t>
-        </is>
-      </c>
-      <c r="Z175" t="inlineStr">
-        <is>
-          <t>Sr. Ricardo de Freitas Reis</t>
-        </is>
-      </c>
+          <t>Soma</t>
+        </is>
+      </c>
+      <c r="Y175" t="inlineStr"/>
+      <c r="Z175" t="inlineStr"/>
       <c r="AA175" t="inlineStr">
         <is>
           <t>2025
-             - 3.63 - Taxa de redução de processos conclusos para Sentença, Decisão e Despacho há mais de 120 (cento e vinte) dias.</t>
+             - 5.6 - Número de procedimentos pré-processuais de reconhecimento de paternidade tratados no âmbito dos Centros Judiciários de Solução de Conflitos e Cidadania no setor pré-processual ou no programa Paternidade para Todos.</t>
         </is>
       </c>
       <c r="AB175" t="inlineStr"/>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>05 - Programa de Melhoria de Indicadores do IPC-Jus TJMG.</t>
+          <t>07 - Programa de estruturação de políticas públicas autocompositivas de solução de conflitos. , 47 - Programa de otimização do funcionamento dos CEJUSCs - Centros Judiciários de Solução de Conflitos e Cidadania.</t>
         </is>
       </c>
       <c r="AD175" t="inlineStr">
@@ -39794,7 +39642,7 @@
       <c r="AF175" t="inlineStr"/>
       <c r="AG175" t="inlineStr">
         <is>
-          <t>3 - Agilidade e Produtividade na Prestação Jurisdicional</t>
+          <t>5 - Prevenção de Litígios e Adoção de Soluções Consensuais para os Conflitos</t>
         </is>
       </c>
       <c r="AH175" t="inlineStr"/>
@@ -39808,14 +39656,10 @@
           <t>16 - Paz, Justiça e Instituições Eficazes</t>
         </is>
       </c>
-      <c r="AK175" t="inlineStr">
-        <is>
-          <t>CEJUR , COAPE , COSIS , GEFIS , GEINF , GESIS , SEPLAN</t>
-        </is>
-      </c>
+      <c r="AK175" t="inlineStr"/>
       <c r="AL175" t="inlineStr">
         <is>
-          <t>Dr. Guilherme Lima Nogueira da Silva</t>
+          <t>Rogério Medeiros Garcia de Lima</t>
         </is>
       </c>
       <c r="AM175" t="inlineStr">
@@ -39850,17 +39694,17 @@
       </c>
       <c r="AS175" t="inlineStr">
         <is>
-          <t>ASPLAGMETA-2694</t>
+          <t>ASPLAGMETA-2641</t>
         </is>
       </c>
       <c r="AT175" t="inlineStr">
         <is>
-          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2694 Janeiro Apuração Aberto ASPLAGMETA-2695 Fevereiro Apuração Aberto ASPLAGMETA-2696 Março Apuração Aberto ASPLAGMETA-2697 Abril Apuração Aberto ASPLAGMETA-2698 Maio Apuração Aberto ASPLAGMETA-2699 Junho Apuração Aberto ASPLAGMETA-2700 Julho Apuração Aberto ASPLAGMETA-2701 Agosto Apuração Aberto ASPLAGMETA-2702 Setembro Apuração Aberto ASPLAGMETA-2703 Outubro Apuração Aberto ASPLAGMETA-2704 Novembro Apuração Aberto ASPLAGMETA-2705 Dezembro Apuração Aberto ASPLAGMETA-2706 Apurado no período Apuração Aberto</t>
+          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2641 Janeiro Apuração Aberto ASPLAGMETA-2642 Fevereiro Apuração Aberto ASPLAGMETA-2643 Março Apuração Aberto ASPLAGMETA-2644 Abril Apuração Aberto ASPLAGMETA-2645 Maio Apuração Aberto ASPLAGMETA-2646 Junho Apuração Aberto ASPLAGMETA-2647 Julho Apuração Aberto ASPLAGMETA-2648 Agosto Apuração Aberto ASPLAGMETA-2649 Setembro Apuração Aberto ASPLAGMETA-2650 Outubro Apuração Aberto ASPLAGMETA-2651 Novembro Apuração Aberto ASPLAGMETA-2652 Dezembro Apuração Aberto ASPLAGMETA-2653 Apurado no período Apuração Aberto</t>
         </is>
       </c>
       <c r="AU175" t="inlineStr">
         <is>
-          <t>(31) 3237-8259</t>
+          <t>(31) 3232-2615</t>
         </is>
       </c>
       <c r="AV175" t="inlineStr">
@@ -39875,18 +39719,18 @@
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>DIRCOR</t>
+          <t>Superintendência da Gestão de Inovação</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
         <is>
-          <t>Percentual</t>
+          <t>Unidade</t>
         </is>
       </c>
       <c r="AZ175" t="inlineStr"/>
       <c r="BA175" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1.200</t>
         </is>
       </c>
       <c r="BB175" t="inlineStr">
@@ -39915,7 +39759,7 @@
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr">
         <is>
-          <t>[ASPLAGMETA-2117] TJMG 142 - Expandir o PJE para a classe inquéritos policiais em 100% (cem por cento) das comarcas em 2025.</t>
+          <t>[ASPLAGMETA-2122] TJMG 97 - Aumentar, em 2025, uma média de pelo menos 1% (um por cento) no número de sessões agendadas nos CEJUSCs em relação ao ano anterior.</t>
         </is>
       </c>
       <c r="F176" t="inlineStr"/>
@@ -39931,7 +39775,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>Diretor de Secretaria</t>
+          <t>Gerente</t>
         </is>
       </c>
       <c r="J176" t="inlineStr"/>
@@ -39954,12 +39798,12 @@
       <c r="O176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Corregedoria</t>
+          <t>3ª Vice Presidência</t>
         </is>
       </c>
       <c r="Q176" t="inlineStr">
         <is>
-          <t>bruna.sousa@tjmg.jus.br</t>
+          <t>agin@tjmg.jus.br</t>
         </is>
       </c>
       <c r="R176" t="inlineStr">
@@ -39979,11 +39823,7 @@
       </c>
       <c r="U176" t="inlineStr"/>
       <c r="V176" t="inlineStr"/>
-      <c r="W176" t="inlineStr">
-        <is>
-          <t>Cronograma de acompanhamento da Iniciativa 92 - Implementação da tramitação eletrônica de inquéritos policiais na Primeira Instância do TJMG</t>
-        </is>
-      </c>
+      <c r="W176" t="inlineStr"/>
       <c r="X176" t="inlineStr">
         <is>
           <t>Último Valor</t>
@@ -39991,24 +39831,20 @@
       </c>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>Total de comarcas com o Pje implantado na classe inquérito policial / total de comarcas do Estado (298)</t>
-        </is>
-      </c>
-      <c r="Z176" t="inlineStr">
-        <is>
-          <t>Sra. Bruna Eduarda Medeiros de Sousa</t>
-        </is>
-      </c>
+          <t>Quantidade de sessões de conciliação processuais agendadas + Nùmero de Sessões de Conciliação Pré-Processuais Agendadas + Número de Sessões de Mediação Processuais Agendadas + Nùmero de Sessões de Mediação Pré-Processuais Agendadas em 2025 no âmbito dos CEJUSCs / (sobre) qtd de Sessões de Conciliação Processuais Agendadas + Número de Sessões de Conciliação Pré-Processuais Agendadas + Número de Sessões de Mediação Processuais Agendadas + Número de Sessões de Mediação Pré-Processuais Agendadas em 2024 no âmbito dos CEJUSCs)-1]x100</t>
+        </is>
+      </c>
+      <c r="Z176" t="inlineStr"/>
       <c r="AA176" t="inlineStr">
         <is>
           <t>2025
-             - 3.62 - Taxa de expansão do Pje para a classe inquérito policial nas comarcas do Estado.</t>
+             - 5.9 - Percentual de sessões agendadas nos Cejuscs.</t>
         </is>
       </c>
       <c r="AB176" t="inlineStr"/>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>92 - Implementação da tramitação eletrônica de inquéritos policiais na Primeira Instância do TJMG.</t>
+          <t>07 - Programa de estruturação de políticas públicas autocompositivas de solução de conflitos. , 47 - Programa de otimização do funcionamento dos CEJUSCs - Centros Judiciários de Solução de Conflitos e Cidadania.</t>
         </is>
       </c>
       <c r="AD176" t="inlineStr">
@@ -40024,7 +39860,7 @@
       <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="inlineStr">
         <is>
-          <t>3 - Agilidade e Produtividade na Prestação Jurisdicional</t>
+          <t>5 - Prevenção de Litígios e Adoção de Soluções Consensuais para os Conflitos</t>
         </is>
       </c>
       <c r="AH176" t="inlineStr"/>
@@ -40038,19 +39874,15 @@
           <t>16 - Paz, Justiça e Instituições Eficazes</t>
         </is>
       </c>
-      <c r="AK176" t="inlineStr">
-        <is>
-          <t>COAPE , DIRCOR , DIRFOR , GESIS</t>
-        </is>
-      </c>
+      <c r="AK176" t="inlineStr"/>
       <c r="AL176" t="inlineStr">
         <is>
-          <t>Des. Estevão Lucchesi de Carvalho</t>
+          <t>Rogério Medeiros Garcia de Lima.</t>
         </is>
       </c>
       <c r="AM176" t="inlineStr">
         <is>
-          <t>Mensal</t>
+          <t>Trimestral</t>
         </is>
       </c>
       <c r="AN176" t="inlineStr">
@@ -40080,17 +39912,17 @@
       </c>
       <c r="AS176" t="inlineStr">
         <is>
-          <t>ASPLAGMETA-2707</t>
+          <t>ASPLAGMETA-2143</t>
         </is>
       </c>
       <c r="AT176" t="inlineStr">
         <is>
-          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2707 Janeiro Apuração Aberto ASPLAGMETA-2708 Fevereiro Apuração Aberto ASPLAGMETA-2709 Março Apuração Aberto ASPLAGMETA-2710 Abril Apuração Aberto ASPLAGMETA-2711 Maio Apuração Aberto ASPLAGMETA-2712 Junho Apuração Aberto ASPLAGMETA-2713 Julho Apuração Aberto ASPLAGMETA-2714 Agosto Apuração Aberto ASPLAGMETA-2715 Setembro Apuração Aberto ASPLAGMETA-2716 Outubro Apuração Aberto ASPLAGMETA-2717 Novembro Apuração Aberto ASPLAGMETA-2718 Dezembro Apuração Aberto ASPLAGMETA-2719 Apurado no período Apuração Aberto</t>
+          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2143 Janeiro Apuração Aberto ASPLAGMETA-2144 Fevereiro Apuração Aberto ASPLAGMETA-2145 Março Apuração Aberto ASPLAGMETA-2146 Abril Apuração Aberto ASPLAGMETA-2147 Maio Apuração Aberto ASPLAGMETA-2148 Junho Apuração Aberto ASPLAGMETA-2149 Julho Apuração Aberto ASPLAGMETA-2150 Agosto Apuração Aberto ASPLAGMETA-2151 Setembro Apuração Aberto ASPLAGMETA-2152 Outubro Apuração Aberto ASPLAGMETA-2153 Novembro Apuração Aberto ASPLAGMETA-2154 Dezembro Apuração Aberto ASPLAGMETA-2155 Apurado no período Apuração Aberto</t>
         </is>
       </c>
       <c r="AU176" t="inlineStr">
         <is>
-          <t>(31) 3237-8229</t>
+          <t>(31) 3232-2615</t>
         </is>
       </c>
       <c r="AV176" t="inlineStr">
@@ -40105,7 +39937,7 @@
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>SEPLAN</t>
+          <t>Superintendência da Gestão de Inovação</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr">
@@ -40116,7 +39948,7 @@
       <c r="AZ176" t="inlineStr"/>
       <c r="BA176" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="BB176" t="inlineStr">
@@ -40145,7 +39977,7 @@
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
-          <t>[ASPLAGMETA-2116] TJMG 141 - Virtualizar, em 2025, o acervo físico de inquéritos policiais em 100% (cem por cento) das comarcas do Estado de Minas Gerais.</t>
+          <t>[ASPLAGMETA-2121] TJMG 149 - Reduzir, até 31/12/2025, 50% (cinquenta por cento) dos feitos em que possuam réus falecidos.</t>
         </is>
       </c>
       <c r="F177" t="inlineStr"/>
@@ -40161,7 +39993,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>Diretor de Secretaria</t>
+          <t>Diretor Executivo</t>
         </is>
       </c>
       <c r="J177" t="inlineStr"/>
@@ -40175,7 +40007,11 @@
           <t>ASPLAG/TJMG</t>
         </is>
       </c>
-      <c r="M177" t="inlineStr"/>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
       <c r="N177" t="inlineStr"/>
       <c r="O177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
@@ -40185,7 +40021,7 @@
       </c>
       <c r="Q177" t="inlineStr">
         <is>
-          <t>bruna.sousa@tjmg.jus.br</t>
+          <t>dircor@tjmg.jus.br</t>
         </is>
       </c>
       <c r="R177" t="inlineStr">
@@ -40207,7 +40043,7 @@
       <c r="V177" t="inlineStr"/>
       <c r="W177" t="inlineStr">
         <is>
-          <t>Núcleo de Virtualização do TJMG, por meio da alimentação do Painel Inquéritos Virtualizados (Qlik Sense).</t>
+          <t>Centro de Estatística Aplicada à Justiça de Primeira Instância (CEJUR) com informações extraídas de sistemas judiciais e paineis do TJMG.</t>
         </is>
       </c>
       <c r="X177" t="inlineStr">
@@ -40217,24 +40053,24 @@
       </c>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>Total de inquéritos policiais físicos virtualizados/ total de inquéritos policiais físicos previstos para serem virtualizados.</t>
+          <t>[(Quantidade de feitos em que tenha cadastrado réu falecido na data de apuração (RFf)) dividida Quantidade de feitos em que tenha cadastrado réu falecido em 31/12/2024 (RFi)) - 1] x 100</t>
         </is>
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>Sra. Bruna Eduarda Medeiros de Sousa</t>
+          <t>Sr. Ricardo de Freitas Reis</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
           <t>2025
-             - 3.61 - Taxa de virtualização do acervo físico de inquéritos policiais nas comarcas do Estado.</t>
+             - 3.66 - Taxa de redução de feitos com indicação de réu falecido.</t>
         </is>
       </c>
       <c r="AB177" t="inlineStr"/>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>92 - Implementação da tramitação eletrônica de inquéritos policiais na Primeira Instância do TJMG.</t>
+          <t>05 - Programa de Melhoria de Indicadores do IPC-Jus TJMG.</t>
         </is>
       </c>
       <c r="AD177" t="inlineStr">
@@ -40266,17 +40102,17 @@
       </c>
       <c r="AK177" t="inlineStr">
         <is>
-          <t>COAPE , DIRCOR , DIRFOR , GESIS</t>
+          <t>CEJUR , COAPE , COSIS , GEFIS , GEINF , GESIS , SEPLAN</t>
         </is>
       </c>
       <c r="AL177" t="inlineStr">
         <is>
-          <t>Des. Estevão Lucchesi de Carvalho</t>
+          <t>Dr. Guilherme Lima Nogueira da Silva</t>
         </is>
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>Mensal</t>
+          <t>Trimestral</t>
         </is>
       </c>
       <c r="AN177" t="inlineStr">
@@ -40306,17 +40142,17 @@
       </c>
       <c r="AS177" t="inlineStr">
         <is>
-          <t>ASPLAGMETA-2720</t>
+          <t>ASPLAGMETA-2654</t>
         </is>
       </c>
       <c r="AT177" t="inlineStr">
         <is>
-          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2720 Janeiro Apuração Aberto ASPLAGMETA-2721 Fevereiro Apuração Aberto ASPLAGMETA-2722 Março Apuração Aberto ASPLAGMETA-2723 Abril Apuração Aberto ASPLAGMETA-2724 Maio Apuração Aberto ASPLAGMETA-2725 Junho Apuração Aberto ASPLAGMETA-2726 Julho Apuração Aberto ASPLAGMETA-2727 Agosto Apuração Aberto ASPLAGMETA-2728 Setembro Apuração Aberto ASPLAGMETA-2729 Outubro Apuração Aberto ASPLAGMETA-2730 Novembro Apuração Aberto ASPLAGMETA-2731 Dezembro Apuração Aberto ASPLAGMETA-2732 Apurado no período Apuração Aberto</t>
+          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2654 Janeiro Apuração Aberto ASPLAGMETA-2655 Fevereiro Apuração Aberto ASPLAGMETA-2656 Março Apuração Aberto ASPLAGMETA-2657 Abril Apuração Aberto ASPLAGMETA-2658 Maio Apuração Aberto ASPLAGMETA-2659 Junho Apuração Aberto ASPLAGMETA-2660 Julho Apuração Aberto ASPLAGMETA-2661 Agosto Apuração Aberto ASPLAGMETA-2662 Setembro Apuração Aberto ASPLAGMETA-2663 Outubro Apuração Aberto ASPLAGMETA-2664 Novembro Apuração Aberto ASPLAGMETA-2665 Dezembro Apuração Aberto ASPLAGMETA-2666 Apurado no período Apuração Aberto</t>
         </is>
       </c>
       <c r="AU177" t="inlineStr">
         <is>
-          <t>(31) 3237-8229</t>
+          <t>(31) 3237-8259</t>
         </is>
       </c>
       <c r="AV177" t="inlineStr">
@@ -40331,7 +40167,7 @@
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>SEPLAN</t>
+          <t>DIRCOR</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
@@ -40342,7 +40178,7 @@
       <c r="AZ177" t="inlineStr"/>
       <c r="BA177" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="BB177" t="inlineStr">
@@ -40371,7 +40207,7 @@
       <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr">
         <is>
-          <t>[ASPLAGMETA-2115] TJMG 133 - Instalar, em 2025, o eproc nas unidades da justiça comum e especial com competência cível de Belo Horizonte, e nas Câmaras do Tribunal de Justiça com competências originárias da segunda instância, Mandado de Segurança, Rescisória e Reclamação.</t>
+          <t>[ASPLAGMETA-2120] TJMG 148 - Reduzir, até 31/12/2025, em 4% (quatro por cento), o tempo médio de tramitação, em dias, dos feitos do acervo gerenciável, a partir da data de distribuição até a data da baixa, na Justiça Comum e no JESP</t>
         </is>
       </c>
       <c r="F178" t="inlineStr"/>
@@ -40385,7 +40221,11 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="I178" t="inlineStr"/>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Diretor Executivo</t>
+        </is>
+      </c>
       <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr">
         <is>
@@ -40406,11 +40246,19 @@
       <c r="O178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Presidência</t>
-        </is>
-      </c>
-      <c r="Q178" t="inlineStr"/>
-      <c r="R178" t="inlineStr"/>
+          <t>Corregedoria</t>
+        </is>
+      </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>dircor@tjmg.jus.br</t>
+        </is>
+      </c>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>asplag@tjmg.jus.br</t>
+        </is>
+      </c>
       <c r="S178" t="inlineStr">
         <is>
           <t>Responsável</t>
@@ -40423,24 +40271,36 @@
       </c>
       <c r="U178" t="inlineStr"/>
       <c r="V178" t="inlineStr"/>
-      <c r="W178" t="inlineStr"/>
+      <c r="W178" t="inlineStr">
+        <is>
+          <t>Centro de Estatística Aplicada à Justiça de Primeira Instância (CEJUR) com informações extraídas de sistemas judiciais e paineis do TJMG.</t>
+        </is>
+      </c>
       <c r="X178" t="inlineStr">
         <is>
-          <t>Soma</t>
-        </is>
-      </c>
-      <c r="Y178" t="inlineStr"/>
-      <c r="Z178" t="inlineStr"/>
+          <t>Último Valor</t>
+        </is>
+      </c>
+      <c r="Y178" t="inlineStr">
+        <is>
+          <t>[(Tempo médio de tramitação dos feitos, da distribuição até a 1ª baixa, considerando os feitos que foram baixados até a data de apuração (TMTf) dividido pelo Tempo médio de tramitação dos feitos, da distribuição até a 1ª baixa, considerando os feitos que foram baixados até 31/12/2024 (TMTi)) -1] x 100 Consideram-se, no cômputo da meta, todos os feitos que tramitaram na Unidade Judiciária e não só os casos novos, o que justifica a expressão “acervo gerenciável” no texto da meta. Nesse sentido, são considerados, por exemplo, precatório e inquéritos.</t>
+        </is>
+      </c>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t>Sr. Ricardo de Freitas Reis</t>
+        </is>
+      </c>
       <c r="AA178" t="inlineStr">
         <is>
           <t>2025
-             - 3.60 - Número de unidades judiciárias previstos para o ano vigente implantados.</t>
+             - 3.65 - Taxa de redução do tempo médio de tramitação até a baixa do processo.</t>
         </is>
       </c>
       <c r="AB178" t="inlineStr"/>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>87 - Programa Estadual de Governança Estratégica de Unidades Judiciárias - Implantação do Sistema Eletrônico para Tramitação de Processos Judiciais Eproc.</t>
+          <t>05 - Programa de Melhoria de Indicadores do IPC-Jus TJMG.</t>
         </is>
       </c>
       <c r="AD178" t="inlineStr">
@@ -40460,14 +40320,26 @@
         </is>
       </c>
       <c r="AH178" t="inlineStr"/>
-      <c r="AI178" t="inlineStr"/>
+      <c r="AI178" t="inlineStr">
+        <is>
+          <t>ASPLAG</t>
+        </is>
+      </c>
       <c r="AJ178" t="inlineStr">
         <is>
           <t>16 - Paz, Justiça e Instituições Eficazes</t>
         </is>
       </c>
-      <c r="AK178" t="inlineStr"/>
-      <c r="AL178" t="inlineStr"/>
+      <c r="AK178" t="inlineStr">
+        <is>
+          <t>CEJUR , COAPE , COSIS , GEFIS , GEINF , GESIS , SEPLAN</t>
+        </is>
+      </c>
+      <c r="AL178" t="inlineStr">
+        <is>
+          <t>Dr. Guilherme Lima Nogueira da Silva</t>
+        </is>
+      </c>
       <c r="AM178" t="inlineStr">
         <is>
           <t>Trimestral</t>
@@ -40500,15 +40372,19 @@
       </c>
       <c r="AS178" t="inlineStr">
         <is>
-          <t>ASPLAGMETA-2733</t>
+          <t>ASPLAGMETA-2667</t>
         </is>
       </c>
       <c r="AT178" t="inlineStr">
         <is>
-          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2733 Janeiro Apuração Aberto ASPLAGMETA-2734 Fevereiro Apuração Aberto ASPLAGMETA-2735 Março Apuração Aberto ASPLAGMETA-2736 Abril Apuração Aberto ASPLAGMETA-2737 Maio Apuração Aberto ASPLAGMETA-2738 Junho Apuração Aberto ASPLAGMETA-2739 Julho Apuração Aberto ASPLAGMETA-2740 Agosto Apuração Aberto ASPLAGMETA-2741 Setembro Apuração Aberto ASPLAGMETA-2742 Outubro Apuração Aberto ASPLAGMETA-2743 Novembro Apuração Aberto ASPLAGMETA-2744 Dezembro Apuração Aberto ASPLAGMETA-2745 Apurado no período Apuração Aberto</t>
-        </is>
-      </c>
-      <c r="AU178" t="inlineStr"/>
+          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2667 Janeiro Apuração Aberto ASPLAGMETA-2668 Fevereiro Apuração Aberto ASPLAGMETA-2669 Março Apuração Aberto ASPLAGMETA-2670 Abril Apuração Aberto ASPLAGMETA-2671 Maio Apuração Aberto ASPLAGMETA-2672 Junho Apuração Aberto ASPLAGMETA-2673 Julho Apuração Aberto ASPLAGMETA-2674 Agosto Apuração Aberto ASPLAGMETA-2675 Setembro Apuração Aberto ASPLAGMETA-2676 Outubro Apuração Aberto ASPLAGMETA-2677 Novembro Apuração Aberto ASPLAGMETA-2678 Dezembro Apuração Aberto ASPLAGMETA-2679 Apurado no período Apuração Aberto</t>
+        </is>
+      </c>
+      <c r="AU178" t="inlineStr">
+        <is>
+          <t>(31) 3237-8259</t>
+        </is>
+      </c>
       <c r="AV178" t="inlineStr">
         <is>
           <t>Estado</t>
@@ -40521,7 +40397,7 @@
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>DIRTEC</t>
+          <t>DIRCOR</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr">
@@ -40532,7 +40408,7 @@
       <c r="AZ178" t="inlineStr"/>
       <c r="BA178" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BB178" t="inlineStr">
@@ -40561,7 +40437,7 @@
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
-          <t>[ASPLAGMETA-2114] TJMG 132 - Executar, em 2025, 100% (cem por cento) das atividades previstas no Programa 1ª Vice SOMA - Suporte à organização, cumprimento de metas e aperfeiçoamento gerencial.</t>
+          <t>[ASPLAGMETA-2119] TJMG 147 - Reduzir, até 31/12/2025, em 30% (dez por cento) o estoque dos processos paralisados sem motivo legal, há mais de 120 (cento e vinte) dias, em secretaria na Justiça Comum e no JESP (excluídos os feitos do SEEU).</t>
         </is>
       </c>
       <c r="F179" t="inlineStr"/>
@@ -40575,7 +40451,11 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="I179" t="inlineStr"/>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Diretor Executivo</t>
+        </is>
+      </c>
       <c r="J179" t="inlineStr"/>
       <c r="K179" t="inlineStr">
         <is>
@@ -40587,16 +40467,28 @@
           <t>ASPLAG/TJMG</t>
         </is>
       </c>
-      <c r="M179" t="inlineStr"/>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
       <c r="N179" t="inlineStr"/>
       <c r="O179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>1ª Vice Presidência</t>
-        </is>
-      </c>
-      <c r="Q179" t="inlineStr"/>
-      <c r="R179" t="inlineStr"/>
+          <t>Corregedoria</t>
+        </is>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>dircor@tjmg.jus.br</t>
+        </is>
+      </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>asplag@tjmg.jus.br</t>
+        </is>
+      </c>
       <c r="S179" t="inlineStr">
         <is>
           <t>Responsável</t>
@@ -40609,24 +40501,36 @@
       </c>
       <c r="U179" t="inlineStr"/>
       <c r="V179" t="inlineStr"/>
-      <c r="W179" t="inlineStr"/>
+      <c r="W179" t="inlineStr">
+        <is>
+          <t>Centro de Estatística Aplicada à Justiça de Primeira Instância (CEJUR) com informações extraídas de sistemas judiciais e paineis do TJMG.</t>
+        </is>
+      </c>
       <c r="X179" t="inlineStr">
         <is>
           <t>Último Valor</t>
         </is>
       </c>
-      <c r="Y179" t="inlineStr"/>
-      <c r="Z179" t="inlineStr"/>
+      <c r="Y179" t="inlineStr">
+        <is>
+          <t>[(Quantidade de processos paralisados sem motivo legal há mais de 100 dias em secretaria na data de apuração (PSML120f) dividida pela Quantidade de processos paralisados sem motivo legal há mais de 100 dias em secretaria em 31/12/2024 (PSML120i)) -1] x 100</t>
+        </is>
+      </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>Sr. Ricardo de Freitas Reis</t>
+        </is>
+      </c>
       <c r="AA179" t="inlineStr">
         <is>
           <t>2025
-             - 3.59 - Taxa de cumprimento das atividades previstas no Programa 1ª Vice-Soma - Suporte à organização, cumprimento de metas e aperfeiçoamento gerencial.</t>
+             - 3.64 - Taxa de redução de processos paralisados em secretaria sem motivo legal há mais de 120 (cento e vinte) dias.</t>
         </is>
       </c>
       <c r="AB179" t="inlineStr"/>
       <c r="AC179" t="inlineStr">
         <is>
-          <t>94 - Programa 1ª Vice SOMA - Suporte à organização, cumprimento de metas e aperfeiçoamento gerencial.</t>
+          <t>05 - Programa de Melhoria de Indicadores do IPC-Jus TJMG.</t>
         </is>
       </c>
       <c r="AD179" t="inlineStr">
@@ -40646,14 +40550,26 @@
         </is>
       </c>
       <c r="AH179" t="inlineStr"/>
-      <c r="AI179" t="inlineStr"/>
+      <c r="AI179" t="inlineStr">
+        <is>
+          <t>ASPLAG</t>
+        </is>
+      </c>
       <c r="AJ179" t="inlineStr">
         <is>
           <t>16 - Paz, Justiça e Instituições Eficazes</t>
         </is>
       </c>
-      <c r="AK179" t="inlineStr"/>
-      <c r="AL179" t="inlineStr"/>
+      <c r="AK179" t="inlineStr">
+        <is>
+          <t>CEJUR , COAPE , COSIS , GEFIS , GEINF , GESIS , SEPLAN</t>
+        </is>
+      </c>
+      <c r="AL179" t="inlineStr">
+        <is>
+          <t>Dr. Guilherme Lima Nogueira da Silva</t>
+        </is>
+      </c>
       <c r="AM179" t="inlineStr">
         <is>
           <t>Trimestral</t>
@@ -40686,15 +40602,19 @@
       </c>
       <c r="AS179" t="inlineStr">
         <is>
-          <t>ASPLAGMETA-2746</t>
+          <t>ASPLAGMETA-2680</t>
         </is>
       </c>
       <c r="AT179" t="inlineStr">
         <is>
-          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2746 Janeiro Apuração Aberto ASPLAGMETA-2747 Fevereiro Apuração Aberto ASPLAGMETA-2748 Março Apuração Aberto ASPLAGMETA-2749 Abril Apuração Aberto ASPLAGMETA-2750 Maio Apuração Aberto ASPLAGMETA-2751 Junho Apuração Aberto ASPLAGMETA-2752 Julho Apuração Aberto ASPLAGMETA-2753 Agosto Apuração Aberto ASPLAGMETA-2754 Setembro Apuração Aberto ASPLAGMETA-2755 Outubro Apuração Aberto ASPLAGMETA-2756 Novembro Apuração Aberto ASPLAGMETA-2757 Dezembro Apuração Aberto ASPLAGMETA-2758 Apurado no período Apuração Aberto</t>
-        </is>
-      </c>
-      <c r="AU179" t="inlineStr"/>
+          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2680 Janeiro Apuração Aberto ASPLAGMETA-2681 Fevereiro Apuração Aberto ASPLAGMETA-2682 Março Apuração Aberto ASPLAGMETA-2683 Abril Apuração Aberto ASPLAGMETA-2684 Maio Apuração Aberto ASPLAGMETA-2685 Junho Apuração Aberto ASPLAGMETA-2686 Julho Apuração Aberto ASPLAGMETA-2687 Agosto Apuração Aberto ASPLAGMETA-2688 Setembro Apuração Aberto ASPLAGMETA-2689 Outubro Apuração Aberto ASPLAGMETA-2690 Novembro Apuração Aberto ASPLAGMETA-2691 Novembro Apuração Aberto ASPLAGMETA-2692 Dezembro Apuração Aberto ASPLAGMETA-2693 Apurado no período Apuração Aberto</t>
+        </is>
+      </c>
+      <c r="AU179" t="inlineStr">
+        <is>
+          <t>(31) 3237-8259</t>
+        </is>
+      </c>
       <c r="AV179" t="inlineStr">
         <is>
           <t>Estado</t>
@@ -40707,7 +40627,7 @@
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>SEPAD</t>
+          <t>DIRCOR</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr">
@@ -40718,7 +40638,7 @@
       <c r="AZ179" t="inlineStr"/>
       <c r="BA179" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BB179" t="inlineStr">
@@ -40747,7 +40667,7 @@
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
-          <t>[ASPLAGMETA-2113] TJMG 130 - Implantar a Central de Processos Eletrônicos (CPE) em 13 (treze) Grupos Jurisdicionais das Turmas Recursais do Tribunal de Justiça de Minas Gerais, no ano de 2025.</t>
+          <t>[ASPLAGMETA-2118] TJMG 146 - Reduzir, até 31/12/2025, em 10% (dez por cento) o estoque dos processos conclusos para Sentença, Decisão e Despacho há mais de 120 (cento e vinte) dias na Justiça Comum e no JESP.</t>
         </is>
       </c>
       <c r="F180" t="inlineStr"/>
@@ -40763,7 +40683,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>Secretário Geral da Presidência</t>
+          <t>Diretor Executivo</t>
         </is>
       </c>
       <c r="J180" t="inlineStr"/>
@@ -40786,12 +40706,12 @@
       <c r="O180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Presidência</t>
+          <t>Corregedoria</t>
         </is>
       </c>
       <c r="Q180" t="inlineStr">
         <is>
-          <t>segove@tjmg.jus.br</t>
+          <t>dircor@tjmg.jus.br</t>
         </is>
       </c>
       <c r="R180" t="inlineStr">
@@ -40813,34 +40733,34 @@
       <c r="V180" t="inlineStr"/>
       <c r="W180" t="inlineStr">
         <is>
-          <t>Cronograma de acompanhamento da Iniciativa 85. Central de Processo Eletrônico - CPE de Turmas Recursais</t>
+          <t>Centro de Estatística Aplicada à Justiça de Primeira Instância (CEJUR) com informações extraídas de sistemas judiciais e paineis do TJMG.</t>
         </is>
       </c>
       <c r="X180" t="inlineStr">
         <is>
-          <t>Soma</t>
+          <t>Último Valor</t>
         </is>
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>Somatório de Turmas Recursais que passaram a integrar a CPE-TR em 2025, nos termos da Portaria Conjunta 1545/PR/2024.</t>
+          <t>[(Estoque de processos conclusos para Sentença, Decisão e Despacho há mais de 100 dias na data de apuração (C120f) dividido pelo Estoque de processos conclusos para Sentença, Decisão e Despacho há mais de 100 dias em 31/12/2024 (C120i)) -1] x 100.</t>
         </is>
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>Sr. Guilherme Augusto Mendes do Valle</t>
+          <t>Sr. Ricardo de Freitas Reis</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
           <t>2025
-             - 3.58 - Número de Grupos Jurisdicionais das Turmas Recursais do TJMG com Central de Processos Eletrônicos - CPE de Turmas Recursais implantada.</t>
+             - 3.63 - Taxa de redução de processos conclusos para Sentença, Decisão e Despacho há mais de 120 (cento e vinte) dias.</t>
         </is>
       </c>
       <c r="AB180" t="inlineStr"/>
       <c r="AC180" t="inlineStr">
         <is>
-          <t>85 - Central de Processos Eletrônicos (CPE) de Turmas Recursais.</t>
+          <t>05 - Programa de Melhoria de Indicadores do IPC-Jus TJMG.</t>
         </is>
       </c>
       <c r="AD180" t="inlineStr">
@@ -40872,17 +40792,17 @@
       </c>
       <c r="AK180" t="inlineStr">
         <is>
-          <t>CEGOP , CEMJUR , COAPE , DENGEP , DIRCOM , DIRFOR , GEJESP , SEPLAN</t>
+          <t>CEJUR , COAPE , COSIS , GEFIS , GEINF , GESIS , SEPLAN</t>
         </is>
       </c>
       <c r="AL180" t="inlineStr">
         <is>
-          <t>Des. Luiz Carlos de Azevedo Corrêa Junior</t>
+          <t>Dr. Guilherme Lima Nogueira da Silva</t>
         </is>
       </c>
       <c r="AM180" t="inlineStr">
         <is>
-          <t>Mensal</t>
+          <t>Trimestral</t>
         </is>
       </c>
       <c r="AN180" t="inlineStr">
@@ -40912,17 +40832,17 @@
       </c>
       <c r="AS180" t="inlineStr">
         <is>
-          <t>ASPLAGMETA-2759</t>
+          <t>ASPLAGMETA-2694</t>
         </is>
       </c>
       <c r="AT180" t="inlineStr">
         <is>
-          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2759 Janeiro Apuração Aberto ASPLAGMETA-2760 Fevereiro Apuração Aberto ASPLAGMETA-2761 Março Apuração Aberto ASPLAGMETA-2762 Abril Apuração Aberto ASPLAGMETA-2763 Maio Apuração Aberto ASPLAGMETA-2764 Junho Apuração Aberto ASPLAGMETA-2765 Julho Apuração Aberto ASPLAGMETA-2766 Agosto Apuração Aberto ASPLAGMETA-2767 Setembro Apuração Aberto ASPLAGMETA-2768 Outubro Apuração Aberto ASPLAGMETA-2769 Novembro Apuração Aberto ASPLAGMETA-2770 Dezembro Apuração Aberto ASPLAGMETA-2771 Apurado no período Apuração Aberto</t>
+          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2694 Janeiro Apuração Aberto ASPLAGMETA-2695 Fevereiro Apuração Aberto ASPLAGMETA-2696 Março Apuração Aberto ASPLAGMETA-2697 Abril Apuração Aberto ASPLAGMETA-2698 Maio Apuração Aberto ASPLAGMETA-2699 Junho Apuração Aberto ASPLAGMETA-2700 Julho Apuração Aberto ASPLAGMETA-2701 Agosto Apuração Aberto ASPLAGMETA-2702 Setembro Apuração Aberto ASPLAGMETA-2703 Outubro Apuração Aberto ASPLAGMETA-2704 Novembro Apuração Aberto ASPLAGMETA-2705 Dezembro Apuração Aberto ASPLAGMETA-2706 Apurado no período Apuração Aberto</t>
         </is>
       </c>
       <c r="AU180" t="inlineStr">
         <is>
-          <t>31 3306-2567</t>
+          <t>(31) 3237-8259</t>
         </is>
       </c>
       <c r="AV180" t="inlineStr">
@@ -40937,18 +40857,18 @@
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>SEGOVE</t>
+          <t>DIRCOR</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">
         <is>
-          <t>Unidade</t>
+          <t>Percentual</t>
         </is>
       </c>
       <c r="AZ180" t="inlineStr"/>
       <c r="BA180" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BB180" t="inlineStr">
@@ -40977,7 +40897,7 @@
       <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
-          <t>[ASPLAGMETA-2112] TJMG 128 - Cessar a competência delegada nas ações previdenciárias e execuções fiscais em pelo menos 40 (quarenta) comarcas até dezembro de 2025.</t>
+          <t>[ASPLAGMETA-2117] TJMG 142 - Expandir o PJE para a classe inquéritos policiais em 100% (cem por cento) das comarcas em 2025.</t>
         </is>
       </c>
       <c r="F181" t="inlineStr"/>
@@ -40993,7 +40913,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>Juíza Auxiliar da Presidência</t>
+          <t>Diretor de Secretaria</t>
         </is>
       </c>
       <c r="J181" t="inlineStr"/>
@@ -41009,19 +40929,19 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="N181" t="inlineStr"/>
       <c r="O181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Presidência</t>
+          <t>Corregedoria</t>
         </is>
       </c>
       <c r="Q181" t="inlineStr">
         <is>
-          <t>juizauxpres.marcela@tjmg.jus.br</t>
+          <t>bruna.sousa@tjmg.jus.br</t>
         </is>
       </c>
       <c r="R181" t="inlineStr">
@@ -41043,7 +40963,7 @@
       <c r="V181" t="inlineStr"/>
       <c r="W181" t="inlineStr">
         <is>
-          <t>Cronograma de acompanhamento da iniciativa 91 - Cessação da competência delegada nas ações previdenciárias e de execuções fiscais distribuídas em unidades judiciárias do TJMG.</t>
+          <t>Cronograma de acompanhamento da Iniciativa 92 - Implementação da tramitação eletrônica de inquéritos policiais na Primeira Instância do TJMG</t>
         </is>
       </c>
       <c r="X181" t="inlineStr">
@@ -41053,24 +40973,24 @@
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>Somatório das comarcas com competência delegada cessada nas ações previdenciárias e execuções fiscais até 2025, em decorrência da implantação de Unidade de Atendimento Avançado (UAA).</t>
+          <t>Total de comarcas com o Pje implantado na classe inquérito policial / total de comarcas do Estado (298)</t>
         </is>
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>Dra. Marcela Maria Pereira Amaral Novais</t>
+          <t>Sra. Bruna Eduarda Medeiros de Sousa</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
           <t>2025
-             - 3.57 - Número de comarcas com a competência delegada nas ações previdenciárias e execuções fiscais cessada.</t>
+             - 3.62 - Taxa de expansão do Pje para a classe inquérito policial nas comarcas do Estado.</t>
         </is>
       </c>
       <c r="AB181" t="inlineStr"/>
       <c r="AC181" t="inlineStr">
         <is>
-          <t>91 - Cessação da competência delegada nas ações previdenciárias e de execuções fiscais distribuídas em unidades judiciárias do TJMG.</t>
+          <t>92 - Implementação da tramitação eletrônica de inquéritos policiais na Primeira Instância do TJMG.</t>
         </is>
       </c>
       <c r="AD181" t="inlineStr">
@@ -41102,17 +41022,17 @@
       </c>
       <c r="AK181" t="inlineStr">
         <is>
-          <t>DENGEP , DIRFOR , DIRSEP , SEGOVE , CORREGEDORIA</t>
+          <t>COAPE , DIRCOR , DIRFOR , GESIS</t>
         </is>
       </c>
       <c r="AL181" t="inlineStr">
         <is>
-          <t>Des. Luiz Carlos de Azevedo Corrêa Junior</t>
+          <t>Des. Estevão Lucchesi de Carvalho</t>
         </is>
       </c>
       <c r="AM181" t="inlineStr">
         <is>
-          <t>Trimestral</t>
+          <t>Mensal</t>
         </is>
       </c>
       <c r="AN181" t="inlineStr">
@@ -41142,17 +41062,17 @@
       </c>
       <c r="AS181" t="inlineStr">
         <is>
-          <t>ASPLAGMETA-2585</t>
+          <t>ASPLAGMETA-2707</t>
         </is>
       </c>
       <c r="AT181" t="inlineStr">
         <is>
-          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2585 Janeiro Apuração Aberto ASPLAGMETA-2588 Fevereiro Apuração Aberto ASPLAGMETA-2589 Março Apuração Aberto ASPLAGMETA-2590 Abril Apuração Aberto ASPLAGMETA-2592 Maio Apuração Aberto ASPLAGMETA-2594 Junho Apuração Aberto ASPLAGMETA-2595 Julho Apuração Aberto ASPLAGMETA-2596 Agosto Apuração Aberto ASPLAGMETA-2597 Setembro Apuração Aberto ASPLAGMETA-2598 Outubro Apuração Aberto ASPLAGMETA-2599 Novembro Apuração Aberto ASPLAGMETA-2600 Dezembro Apuração Aberto ASPLAGMETA-2601 Apurado no período Apuração Aberto</t>
+          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2707 Janeiro Apuração Aberto ASPLAGMETA-2708 Fevereiro Apuração Aberto ASPLAGMETA-2709 Março Apuração Aberto ASPLAGMETA-2710 Abril Apuração Aberto ASPLAGMETA-2711 Maio Apuração Aberto ASPLAGMETA-2712 Junho Apuração Aberto ASPLAGMETA-2713 Julho Apuração Aberto ASPLAGMETA-2714 Agosto Apuração Aberto ASPLAGMETA-2715 Setembro Apuração Aberto ASPLAGMETA-2716 Outubro Apuração Aberto ASPLAGMETA-2717 Novembro Apuração Aberto ASPLAGMETA-2718 Dezembro Apuração Aberto ASPLAGMETA-2719 Apurado no período Apuração Aberto</t>
         </is>
       </c>
       <c r="AU181" t="inlineStr">
         <is>
-          <t>3133063042</t>
+          <t>(31) 3237-8229</t>
         </is>
       </c>
       <c r="AV181" t="inlineStr">
@@ -41167,18 +41087,18 @@
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Presidência</t>
+          <t>SEPLAN</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr">
         <is>
-          <t>Unidade</t>
+          <t>Percentual</t>
         </is>
       </c>
       <c r="AZ181" t="inlineStr"/>
       <c r="BA181" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>100</t>
         </is>
       </c>
       <c r="BB181" t="inlineStr">
@@ -41207,7 +41127,7 @@
       <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr">
         <is>
-          <t>[ASPLAGMETA-2111] TJMG 115 - Devolver para o respectivo Cartório 95% (noventa e cinco por cento) dos processos conclusos no prazo de até 90 (noventa) dias, contado da data da conclusão.</t>
+          <t>[ASPLAGMETA-2116] TJMG 141 - Virtualizar, em 2025, o acervo físico de inquéritos policiais em 100% (cem por cento) das comarcas do Estado de Minas Gerais.</t>
         </is>
       </c>
       <c r="F182" t="inlineStr"/>
@@ -41223,7 +41143,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>Diretora de Secretaria</t>
+          <t>Diretor de Secretaria</t>
         </is>
       </c>
       <c r="J182" t="inlineStr"/>
@@ -41237,21 +41157,17 @@
           <t>ASPLAG/TJMG</t>
         </is>
       </c>
-      <c r="M182" t="inlineStr">
-        <is>
-          <t>2025-05-15</t>
-        </is>
-      </c>
+      <c r="M182" t="inlineStr"/>
       <c r="N182" t="inlineStr"/>
       <c r="O182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>1ª Vice Presidência</t>
+          <t>Corregedoria</t>
         </is>
       </c>
       <c r="Q182" t="inlineStr">
         <is>
-          <t>sepad@tjmg.jus.br</t>
+          <t>bruna.sousa@tjmg.jus.br</t>
         </is>
       </c>
       <c r="R182" t="inlineStr">
@@ -41273,34 +41189,34 @@
       <c r="V182" t="inlineStr"/>
       <c r="W182" t="inlineStr">
         <is>
-          <t>CEINJUR</t>
+          <t>Núcleo de Virtualização do TJMG, por meio da alimentação do Painel Inquéritos Virtualizados (Qlik Sense).</t>
         </is>
       </c>
       <c r="X182" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Último Valor</t>
         </is>
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>Total de processos devolvidos ao cartório em até 90 dias /Total de processos conclusos ao gabinete X 100</t>
+          <t>Total de inquéritos policiais físicos virtualizados/ total de inquéritos policiais físicos previstos para serem virtualizados.</t>
         </is>
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>Sra. Elaine Batista Costa Souza</t>
+          <t>Sra. Bruna Eduarda Medeiros de Sousa</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
           <t>2025
-             - 3.52 - Índice de processos conclusos aos relatores, em até 90 dias.</t>
+             - 3.61 - Taxa de virtualização do acervo físico de inquéritos policiais nas comarcas do Estado.</t>
         </is>
       </c>
       <c r="AB182" t="inlineStr"/>
       <c r="AC182" t="inlineStr">
         <is>
-          <t>04 - Programa Agiliza-Jus. , 94 - Programa 1ª Vice SOMA - Suporte à organização, cumprimento de metas e aperfeiçoamento gerencial.</t>
+          <t>92 - Implementação da tramitação eletrônica de inquéritos policiais na Primeira Instância do TJMG.</t>
         </is>
       </c>
       <c r="AD182" t="inlineStr">
@@ -41330,15 +41246,19 @@
           <t>16 - Paz, Justiça e Instituições Eficazes</t>
         </is>
       </c>
-      <c r="AK182" t="inlineStr"/>
+      <c r="AK182" t="inlineStr">
+        <is>
+          <t>COAPE , DIRCOR , DIRFOR , GESIS</t>
+        </is>
+      </c>
       <c r="AL182" t="inlineStr">
         <is>
-          <t>Dr. Marcelo Paulo Salgado</t>
+          <t>Des. Estevão Lucchesi de Carvalho</t>
         </is>
       </c>
       <c r="AM182" t="inlineStr">
         <is>
-          <t>Trimestral</t>
+          <t>Mensal</t>
         </is>
       </c>
       <c r="AN182" t="inlineStr">
@@ -41368,17 +41288,17 @@
       </c>
       <c r="AS182" t="inlineStr">
         <is>
-          <t>ASPLAGMETA-2496</t>
+          <t>ASPLAGMETA-2720</t>
         </is>
       </c>
       <c r="AT182" t="inlineStr">
         <is>
-          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2496 Janeiro Apuração Aberto ASPLAGMETA-2497 Fevereiro Apuração Aberto ASPLAGMETA-2498 Março Apuração Aberto ASPLAGMETA-2499 Abril Apuração Aberto ASPLAGMETA-2500 Maio Apuração Aberto ASPLAGMETA-2501 Junho Apuração Aberto ASPLAGMETA-2502 Julho Apuração Aberto ASPLAGMETA-2504 Agosto Apuração Aberto ASPLAGMETA-2505 Setembro Apuração Aberto ASPLAGMETA-2507 Outubro Apuração Aberto ASPLAGMETA-2509 Novembro Apuração Aberto ASPLAGMETA-2515 Dezembro Apuração Aberto ASPLAGMETA-2519 Apurado no período Apuração Aberto</t>
+          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2720 Janeiro Apuração Aberto ASPLAGMETA-2721 Fevereiro Apuração Aberto ASPLAGMETA-2722 Março Apuração Aberto ASPLAGMETA-2723 Abril Apuração Aberto ASPLAGMETA-2724 Maio Apuração Aberto ASPLAGMETA-2725 Junho Apuração Aberto ASPLAGMETA-2726 Julho Apuração Aberto ASPLAGMETA-2727 Agosto Apuração Aberto ASPLAGMETA-2728 Setembro Apuração Aberto ASPLAGMETA-2729 Outubro Apuração Aberto ASPLAGMETA-2730 Novembro Apuração Aberto ASPLAGMETA-2731 Dezembro Apuração Aberto ASPLAGMETA-2732 Apurado no período Apuração Aberto</t>
         </is>
       </c>
       <c r="AU182" t="inlineStr">
         <is>
-          <t>(31) 3232 - 2687</t>
+          <t>(31) 3237-8229</t>
         </is>
       </c>
       <c r="AV182" t="inlineStr">
@@ -41393,7 +41313,7 @@
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>SEPAD</t>
+          <t>SEPLAN</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
@@ -41404,7 +41324,7 @@
       <c r="AZ182" t="inlineStr"/>
       <c r="BA182" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>100</t>
         </is>
       </c>
       <c r="BB182" t="inlineStr">
@@ -41433,7 +41353,7 @@
       <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr">
         <is>
-          <t>[ASPLAGMETA-2110] TJMG 91 - Movimentar 95% (noventa e cinco por cento) do acervo processual em prazo inferior a 60 (sessenta) dias.</t>
+          <t>[ASPLAGMETA-2115] TJMG 133 - Instalar, em 2025, o eproc nas unidades da justiça comum e especial com competência cível de Belo Horizonte, e nas Câmaras do Tribunal de Justiça com competências originárias da segunda instância, Mandado de Segurança, Rescisória e Reclamação.</t>
         </is>
       </c>
       <c r="F183" t="inlineStr"/>
@@ -41447,11 +41367,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>Diretora de Secretaria</t>
-        </is>
-      </c>
+      <c r="I183" t="inlineStr"/>
       <c r="J183" t="inlineStr"/>
       <c r="K183" t="inlineStr">
         <is>
@@ -41472,14 +41388,10 @@
       <c r="O183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>1ª Vice Presidência</t>
-        </is>
-      </c>
-      <c r="Q183" t="inlineStr">
-        <is>
-          <t>sepad@tjmg.jus.br</t>
-        </is>
-      </c>
+          <t>Presidência</t>
+        </is>
+      </c>
+      <c r="Q183" t="inlineStr"/>
       <c r="R183" t="inlineStr"/>
       <c r="S183" t="inlineStr">
         <is>
@@ -41493,36 +41405,24 @@
       </c>
       <c r="U183" t="inlineStr"/>
       <c r="V183" t="inlineStr"/>
-      <c r="W183" t="inlineStr">
-        <is>
-          <t>CEINJUR</t>
-        </is>
-      </c>
+      <c r="W183" t="inlineStr"/>
       <c r="X183" t="inlineStr">
         <is>
-          <t>Média</t>
-        </is>
-      </c>
-      <c r="Y183" t="inlineStr">
-        <is>
-          <t>Fórmula = (∑PAC&lt;61d / ∑PPAC) X 1000/k, onde: PAC = processos do acervo dos cartórios; PPAC = processos paralisados no acervo; k = 9,5 para o período de referência “Até 31/12/2025”.</t>
-        </is>
-      </c>
-      <c r="Z183" t="inlineStr">
-        <is>
-          <t>Sra. Elaine Batista Costa Souza</t>
-        </is>
-      </c>
+          <t>Soma</t>
+        </is>
+      </c>
+      <c r="Y183" t="inlineStr"/>
+      <c r="Z183" t="inlineStr"/>
       <c r="AA183" t="inlineStr">
         <is>
           <t>2025
-             - 3.51 - Índice de tramitação processual em até 60 (sessenta) dias.</t>
+             - 3.60 - Número de unidades judiciárias previstos para o ano vigente implantados.</t>
         </is>
       </c>
       <c r="AB183" t="inlineStr"/>
       <c r="AC183" t="inlineStr">
         <is>
-          <t>04 - Programa Agiliza-Jus. , 94 - Programa 1ª Vice SOMA - Suporte à organização, cumprimento de metas e aperfeiçoamento gerencial.</t>
+          <t>87 - Programa Estadual de Governança Estratégica de Unidades Judiciárias - Implantação do Sistema Eletrônico para Tramitação de Processos Judiciais Eproc.</t>
         </is>
       </c>
       <c r="AD183" t="inlineStr">
@@ -41549,14 +41449,10 @@
         </is>
       </c>
       <c r="AK183" t="inlineStr"/>
-      <c r="AL183" t="inlineStr">
-        <is>
-          <t>Dr.  Marcelo Paulo Salgado</t>
-        </is>
-      </c>
+      <c r="AL183" t="inlineStr"/>
       <c r="AM183" t="inlineStr">
         <is>
-          <t>Mensal</t>
+          <t>Trimestral</t>
         </is>
       </c>
       <c r="AN183" t="inlineStr">
@@ -41586,19 +41482,15 @@
       </c>
       <c r="AS183" t="inlineStr">
         <is>
-          <t>ASPLAGMETA-2483</t>
+          <t>ASPLAGMETA-2733</t>
         </is>
       </c>
       <c r="AT183" t="inlineStr">
         <is>
-          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2483 Janeiro Apuração Aberto ASPLAGMETA-2484 Fevereiro Apuração Aberto ASPLAGMETA-2485 Março Apuração Aberto ASPLAGMETA-2486 Abril Apuração Aberto ASPLAGMETA-2487 Maio Apuração Aberto ASPLAGMETA-2488 Junho Apuração Aberto ASPLAGMETA-2489 Julho Apuração Aberto ASPLAGMETA-2490 Agosto Apuração Aberto ASPLAGMETA-2491 Setembro Apuração Aberto ASPLAGMETA-2492 Outubro Apuração Aberto ASPLAGMETA-2493 Novembro Apuração Aberto ASPLAGMETA-2494 Dezembro Apuração Aberto ASPLAGMETA-2495 Apurado no período Apuração Aberto</t>
-        </is>
-      </c>
-      <c r="AU183" t="inlineStr">
-        <is>
-          <t>(31) 3232-2687</t>
-        </is>
-      </c>
+          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2733 Janeiro Apuração Aberto ASPLAGMETA-2734 Fevereiro Apuração Aberto ASPLAGMETA-2735 Março Apuração Aberto ASPLAGMETA-2736 Abril Apuração Aberto ASPLAGMETA-2737 Maio Apuração Aberto ASPLAGMETA-2738 Junho Apuração Aberto ASPLAGMETA-2739 Julho Apuração Aberto ASPLAGMETA-2740 Agosto Apuração Aberto ASPLAGMETA-2741 Setembro Apuração Aberto ASPLAGMETA-2742 Outubro Apuração Aberto ASPLAGMETA-2743 Novembro Apuração Aberto ASPLAGMETA-2744 Dezembro Apuração Aberto ASPLAGMETA-2745 Apurado no período Apuração Aberto</t>
+        </is>
+      </c>
+      <c r="AU183" t="inlineStr"/>
       <c r="AV183" t="inlineStr">
         <is>
           <t>Estado</t>
@@ -41611,7 +41503,7 @@
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>SEPAD</t>
+          <t>DIRTEC</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr">
@@ -41622,7 +41514,7 @@
       <c r="AZ183" t="inlineStr"/>
       <c r="BA183" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>100</t>
         </is>
       </c>
       <c r="BB183" t="inlineStr">
@@ -41651,7 +41543,7 @@
       <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
-          <t>[ASPLAGMETA-2109] TJMG 85 - Proferir, em 2025, 60.000 (sessenta mil) atos de cooperação (audiências, júri, sentenças, decisões, despachos), em processos cíveis e criminais, em caráter de cooperação no Programa Pontualidade 5.0.</t>
+          <t>[ASPLAGMETA-2114] TJMG 132 - Executar, em 2025, 100% (cem por cento) das atividades previstas no Programa 1ª Vice SOMA - Suporte à organização, cumprimento de metas e aperfeiçoamento gerencial.</t>
         </is>
       </c>
       <c r="F184" t="inlineStr"/>
@@ -41665,11 +41557,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>Juíza Auxiliar da Presidência</t>
-        </is>
-      </c>
+      <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr">
         <is>
@@ -41681,28 +41569,16 @@
           <t>ASPLAG/TJMG</t>
         </is>
       </c>
-      <c r="M184" t="inlineStr">
-        <is>
-          <t>2025-05-15</t>
-        </is>
-      </c>
+      <c r="M184" t="inlineStr"/>
       <c r="N184" t="inlineStr"/>
       <c r="O184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Presidência</t>
-        </is>
-      </c>
-      <c r="Q184" t="inlineStr">
-        <is>
-          <t>juizauxpres.marcela@tjmg.jus.br</t>
-        </is>
-      </c>
-      <c r="R184" t="inlineStr">
-        <is>
-          <t>asplag@tjmg.jus.br</t>
-        </is>
-      </c>
+          <t>1ª Vice Presidência</t>
+        </is>
+      </c>
+      <c r="Q184" t="inlineStr"/>
+      <c r="R184" t="inlineStr"/>
       <c r="S184" t="inlineStr">
         <is>
           <t>Responsável</t>
@@ -41715,36 +41591,24 @@
       </c>
       <c r="U184" t="inlineStr"/>
       <c r="V184" t="inlineStr"/>
-      <c r="W184" t="inlineStr">
-        <is>
-          <t>Centro de Monitoramento e Suporte à Prestação Jurisdicional, CEMJUR/ SEGOVE, por meio do Sistema Eletrônico de Informações (SEI).</t>
-        </is>
-      </c>
+      <c r="W184" t="inlineStr"/>
       <c r="X184" t="inlineStr">
         <is>
-          <t>Soma</t>
-        </is>
-      </c>
-      <c r="Y184" t="inlineStr">
-        <is>
-          <t>Somatório de audiências, júris, sentenças, decisões e despachos proferidos, em processos cíveis e criminais, em caráter de cooperação no Programa Pontualidade 5.0.</t>
-        </is>
-      </c>
-      <c r="Z184" t="inlineStr">
-        <is>
-          <t>Dra. Marcela Maria Pereira Amaral Novais</t>
-        </is>
-      </c>
+          <t>Último Valor</t>
+        </is>
+      </c>
+      <c r="Y184" t="inlineStr"/>
+      <c r="Z184" t="inlineStr"/>
       <c r="AA184" t="inlineStr">
         <is>
           <t>2025
-             - 3.34 - Número de atos proferidos, em processos cíveis e criminais, em caráter de cooperação no Programa Pontualidade 5.0.</t>
+             - 3.59 - Taxa de cumprimento das atividades previstas no Programa 1ª Vice-Soma - Suporte à organização, cumprimento de metas e aperfeiçoamento gerencial.</t>
         </is>
       </c>
       <c r="AB184" t="inlineStr"/>
       <c r="AC184" t="inlineStr">
         <is>
-          <t>06 - Programa Pontualidade 5.0.</t>
+          <t>94 - Programa 1ª Vice SOMA - Suporte à organização, cumprimento de metas e aperfeiçoamento gerencial.</t>
         </is>
       </c>
       <c r="AD184" t="inlineStr">
@@ -41764,29 +41628,17 @@
         </is>
       </c>
       <c r="AH184" t="inlineStr"/>
-      <c r="AI184" t="inlineStr">
-        <is>
-          <t>ASPLAG</t>
-        </is>
-      </c>
+      <c r="AI184" t="inlineStr"/>
       <c r="AJ184" t="inlineStr">
         <is>
           <t>16 - Paz, Justiça e Instituições Eficazes</t>
         </is>
       </c>
-      <c r="AK184" t="inlineStr">
-        <is>
-          <t>CEINFO , CEMJUR</t>
-        </is>
-      </c>
-      <c r="AL184" t="inlineStr">
-        <is>
-          <t>Des. Luiz Carlos de Azevedo Corrêa Junior</t>
-        </is>
-      </c>
+      <c r="AK184" t="inlineStr"/>
+      <c r="AL184" t="inlineStr"/>
       <c r="AM184" t="inlineStr">
         <is>
-          <t>Mensal</t>
+          <t>Trimestral</t>
         </is>
       </c>
       <c r="AN184" t="inlineStr">
@@ -41816,19 +41668,15 @@
       </c>
       <c r="AS184" t="inlineStr">
         <is>
-          <t>ASPLAGMETA-2470</t>
+          <t>ASPLAGMETA-2746</t>
         </is>
       </c>
       <c r="AT184" t="inlineStr">
         <is>
-          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2470 Janeiro Apuração Aberto ASPLAGMETA-2471 Fevereiro Apuração Aberto ASPLAGMETA-2472 Março Apuração Aberto ASPLAGMETA-2473 Abril Apuração Aberto ASPLAGMETA-2474 Maio Apuração Aberto ASPLAGMETA-2475 Junho Apuração Aberto ASPLAGMETA-2476 Julho Apuração Aberto ASPLAGMETA-2477 Agosto Apuração Aberto ASPLAGMETA-2478 Setembro Apuração Aberto ASPLAGMETA-2479 Outubro Apuração Aberto ASPLAGMETA-2480 Novembro Apuração Aberto ASPLAGMETA-2481 Dezembro Apuração Aberto ASPLAGMETA-2482 Apurado no período Apuração Aberto</t>
-        </is>
-      </c>
-      <c r="AU184" t="inlineStr">
-        <is>
-          <t>3133063042</t>
-        </is>
-      </c>
+          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2746 Janeiro Apuração Aberto ASPLAGMETA-2747 Fevereiro Apuração Aberto ASPLAGMETA-2748 Março Apuração Aberto ASPLAGMETA-2749 Abril Apuração Aberto ASPLAGMETA-2750 Maio Apuração Aberto ASPLAGMETA-2751 Junho Apuração Aberto ASPLAGMETA-2752 Julho Apuração Aberto ASPLAGMETA-2753 Agosto Apuração Aberto ASPLAGMETA-2754 Setembro Apuração Aberto ASPLAGMETA-2755 Outubro Apuração Aberto ASPLAGMETA-2756 Novembro Apuração Aberto ASPLAGMETA-2757 Dezembro Apuração Aberto ASPLAGMETA-2758 Apurado no período Apuração Aberto</t>
+        </is>
+      </c>
+      <c r="AU184" t="inlineStr"/>
       <c r="AV184" t="inlineStr">
         <is>
           <t>Estado</t>
@@ -41841,18 +41689,18 @@
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Presidência</t>
+          <t>SEPAD</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr">
         <is>
-          <t>Unidade</t>
+          <t>Percentual</t>
         </is>
       </c>
       <c r="AZ184" t="inlineStr"/>
       <c r="BA184" t="inlineStr">
         <is>
-          <t>60.000</t>
+          <t>100</t>
         </is>
       </c>
       <c r="BB184" t="inlineStr">
@@ -41881,7 +41729,7 @@
       <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
-          <t>[ASPLAGMETA-2108] TJMG 80 - Concluir, até dezembro de 2025, 100% (cem por cento) das atividades previstas para o ano no Programa de Desenvolvimento da Atuação do Centro de Inteligência da Justiça de Minas Gerais.</t>
+          <t>[ASPLAGMETA-2113] TJMG 130 - Implantar a Central de Processos Eletrônicos (CPE) em 13 (treze) Grupos Jurisdicionais das Turmas Recursais do Tribunal de Justiça de Minas Gerais, no ano de 2025.</t>
         </is>
       </c>
       <c r="F185" t="inlineStr"/>
@@ -41895,7 +41743,11 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="I185" t="inlineStr"/>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Secretário Geral da Presidência</t>
+        </is>
+      </c>
       <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr">
         <is>
@@ -41919,8 +41771,16 @@
           <t>Presidência</t>
         </is>
       </c>
-      <c r="Q185" t="inlineStr"/>
-      <c r="R185" t="inlineStr"/>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>segove@tjmg.jus.br</t>
+        </is>
+      </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>asplag@tjmg.jus.br</t>
+        </is>
+      </c>
       <c r="S185" t="inlineStr">
         <is>
           <t>Responsável</t>
@@ -41933,28 +41793,36 @@
       </c>
       <c r="U185" t="inlineStr"/>
       <c r="V185" t="inlineStr"/>
-      <c r="W185" t="inlineStr"/>
+      <c r="W185" t="inlineStr">
+        <is>
+          <t>Cronograma de acompanhamento da Iniciativa 85. Central de Processo Eletrônico - CPE de Turmas Recursais</t>
+        </is>
+      </c>
       <c r="X185" t="inlineStr">
         <is>
-          <t>Último Valor</t>
+          <t>Soma</t>
         </is>
       </c>
       <c r="Y185" t="inlineStr">
         <is>
-          <t>Quantidade de atividades executadas do Programa de Desenvolvimento da Atuação do Centro de Inteligência da Justiça de Minas Gerais / (sobre) quantidade total de atividades propostas x 100.</t>
-        </is>
-      </c>
-      <c r="Z185" t="inlineStr"/>
+          <t>Somatório de Turmas Recursais que passaram a integrar a CPE-TR em 2025, nos termos da Portaria Conjunta 1545/PR/2024.</t>
+        </is>
+      </c>
+      <c r="Z185" t="inlineStr">
+        <is>
+          <t>Sr. Guilherme Augusto Mendes do Valle</t>
+        </is>
+      </c>
       <c r="AA185" t="inlineStr">
         <is>
           <t>2025
-             - 3.32 - Taxa de execução das atividades do Programa de Desenvolvimento da Atuação do Centro de Inteligência da Justiça de Minas Gerais.</t>
+             - 3.58 - Número de Grupos Jurisdicionais das Turmas Recursais do TJMG com Central de Processos Eletrônicos - CPE de Turmas Recursais implantada.</t>
         </is>
       </c>
       <c r="AB185" t="inlineStr"/>
       <c r="AC185" t="inlineStr">
         <is>
-          <t>68 - Programa de Desenvolvimento da Atuação do Centro de Inteligência.</t>
+          <t>85 - Central de Processos Eletrônicos (CPE) de Turmas Recursais.</t>
         </is>
       </c>
       <c r="AD185" t="inlineStr">
@@ -41974,17 +41842,29 @@
         </is>
       </c>
       <c r="AH185" t="inlineStr"/>
-      <c r="AI185" t="inlineStr"/>
+      <c r="AI185" t="inlineStr">
+        <is>
+          <t>ASPLAG</t>
+        </is>
+      </c>
       <c r="AJ185" t="inlineStr">
         <is>
           <t>16 - Paz, Justiça e Instituições Eficazes</t>
         </is>
       </c>
-      <c r="AK185" t="inlineStr"/>
-      <c r="AL185" t="inlineStr"/>
+      <c r="AK185" t="inlineStr">
+        <is>
+          <t>CEGOP , CEMJUR , COAPE , DENGEP , DIRCOM , DIRFOR , GEJESP , SEPLAN</t>
+        </is>
+      </c>
+      <c r="AL185" t="inlineStr">
+        <is>
+          <t>Des. Luiz Carlos de Azevedo Corrêa Junior</t>
+        </is>
+      </c>
       <c r="AM185" t="inlineStr">
         <is>
-          <t>Trimestral</t>
+          <t>Mensal</t>
         </is>
       </c>
       <c r="AN185" t="inlineStr">
@@ -42014,15 +41894,19 @@
       </c>
       <c r="AS185" t="inlineStr">
         <is>
-          <t>ASPLAGMETA-2457</t>
+          <t>ASPLAGMETA-2759</t>
         </is>
       </c>
       <c r="AT185" t="inlineStr">
         <is>
-          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2457 Janeiro Apuração Aberto ASPLAGMETA-2458 Fevereiro Apuração Aberto ASPLAGMETA-2459 Março Apuração Aberto ASPLAGMETA-2460 Abril Apuração Aberto ASPLAGMETA-2461 Maio Apuração Aberto ASPLAGMETA-2462 Junho Apuração Aberto ASPLAGMETA-2463 Julho Apuração Aberto ASPLAGMETA-2464 Agosto Apuração Aberto ASPLAGMETA-2465 Setembro Apuração Aberto ASPLAGMETA-2466 Outubro Apuração Aberto ASPLAGMETA-2467 Novembro Apuração Aberto ASPLAGMETA-2468 Dezembro Apuração Aberto ASPLAGMETA-2469 Apurado no período Apuração Aberto</t>
-        </is>
-      </c>
-      <c r="AU185" t="inlineStr"/>
+          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2759 Janeiro Apuração Aberto ASPLAGMETA-2760 Fevereiro Apuração Aberto ASPLAGMETA-2761 Março Apuração Aberto ASPLAGMETA-2762 Abril Apuração Aberto ASPLAGMETA-2763 Maio Apuração Aberto ASPLAGMETA-2764 Junho Apuração Aberto ASPLAGMETA-2765 Julho Apuração Aberto ASPLAGMETA-2766 Agosto Apuração Aberto ASPLAGMETA-2767 Setembro Apuração Aberto ASPLAGMETA-2768 Outubro Apuração Aberto ASPLAGMETA-2769 Novembro Apuração Aberto ASPLAGMETA-2770 Dezembro Apuração Aberto ASPLAGMETA-2771 Apurado no período Apuração Aberto</t>
+        </is>
+      </c>
+      <c r="AU185" t="inlineStr">
+        <is>
+          <t>31 3306-2567</t>
+        </is>
+      </c>
       <c r="AV185" t="inlineStr">
         <is>
           <t>Estado</t>
@@ -42040,13 +41924,13 @@
       </c>
       <c r="AY185" t="inlineStr">
         <is>
-          <t>Percentual</t>
+          <t>Unidade</t>
         </is>
       </c>
       <c r="AZ185" t="inlineStr"/>
       <c r="BA185" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>13</t>
         </is>
       </c>
       <c r="BB185" t="inlineStr">
@@ -42075,7 +41959,7 @@
       <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
-          <t>[ASPLAGMETA-2107] TJMG 79 - Executar, até 2025, 100% (cem por cento) das atividades previstas no plano de Integração do Sistema PJe com o e-Carta Correios.</t>
+          <t>[ASPLAGMETA-2112] TJMG 128 - Cessar a competência delegada nas ações previdenciárias e execuções fiscais em pelo menos 40 (quarenta) comarcas até dezembro de 2025.</t>
         </is>
       </c>
       <c r="F186" t="inlineStr"/>
@@ -42091,7 +41975,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Diretor de Secretaria</t>
+          <t>Juíza Auxiliar da Presidência</t>
         </is>
       </c>
       <c r="J186" t="inlineStr"/>
@@ -42107,19 +41991,19 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="N186" t="inlineStr"/>
       <c r="O186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Corregedoria</t>
+          <t>Presidência</t>
         </is>
       </c>
       <c r="Q186" t="inlineStr">
         <is>
-          <t>seplan@tjmg.jus.br</t>
+          <t>juizauxpres.marcela@tjmg.jus.br</t>
         </is>
       </c>
       <c r="R186" t="inlineStr">
@@ -42141,7 +42025,7 @@
       <c r="V186" t="inlineStr"/>
       <c r="W186" t="inlineStr">
         <is>
-          <t>SEPLAN/COAPE. Cronograma de atividades da iniciativa 67 no Jira</t>
+          <t>Cronograma de acompanhamento da iniciativa 91 - Cessação da competência delegada nas ações previdenciárias e de execuções fiscais distribuídas em unidades judiciárias do TJMG.</t>
         </is>
       </c>
       <c r="X186" t="inlineStr">
@@ -42151,24 +42035,24 @@
       </c>
       <c r="Y186" t="inlineStr">
         <is>
-          <t>QR/QP, sendo: QR = Quantidade de atividades realizadas no ano e QP = Quantidade de atividades planejadas para o ano &gt; Considera o "peso" de cada atividade no cronograma.</t>
+          <t>Somatório das comarcas com competência delegada cessada nas ações previdenciárias e execuções fiscais até 2025, em decorrência da implantação de Unidade de Atendimento Avançado (UAA).</t>
         </is>
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>Sra. Bruna Eduarda Medeiros de Sousa</t>
+          <t>Dra. Marcela Maria Pereira Amaral Novais</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
           <t>2025
-             - 3.31 - Taxa de execução do plano de Integração do Sistema PJe com o e-Carta Correios.</t>
+             - 3.57 - Número de comarcas com a competência delegada nas ações previdenciárias e execuções fiscais cessada.</t>
         </is>
       </c>
       <c r="AB186" t="inlineStr"/>
       <c r="AC186" t="inlineStr">
         <is>
-          <t>67 - Integração do Sistema PJe com o e-Carta Correios.</t>
+          <t>91 - Cessação da competência delegada nas ações previdenciárias e de execuções fiscais distribuídas em unidades judiciárias do TJMG.</t>
         </is>
       </c>
       <c r="AD186" t="inlineStr">
@@ -42200,17 +42084,17 @@
       </c>
       <c r="AK186" t="inlineStr">
         <is>
-          <t>COAPE , DIRFOR</t>
+          <t>DENGEP , DIRFOR , DIRSEP , SEGOVE , CORREGEDORIA</t>
         </is>
       </c>
       <c r="AL186" t="inlineStr">
         <is>
-          <t>Des. Estevão Lucchesi de Carvalho.</t>
+          <t>Des. Luiz Carlos de Azevedo Corrêa Junior</t>
         </is>
       </c>
       <c r="AM186" t="inlineStr">
         <is>
-          <t>Mensal</t>
+          <t>Trimestral</t>
         </is>
       </c>
       <c r="AN186" t="inlineStr">
@@ -42240,17 +42124,17 @@
       </c>
       <c r="AS186" t="inlineStr">
         <is>
-          <t>ASPLAGMETA-2379</t>
+          <t>ASPLAGMETA-2585</t>
         </is>
       </c>
       <c r="AT186" t="inlineStr">
         <is>
-          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2379 Janeiro Apuração Aberto ASPLAGMETA-2380 Fevereiro Apuração Aberto ASPLAGMETA-2381 Março Apuração Aberto ASPLAGMETA-2382 Abril Apuração Aberto ASPLAGMETA-2383 Maio Apuração Aberto ASPLAGMETA-2384 Junho Apuração Aberto ASPLAGMETA-2385 Julho Apuração Aberto ASPLAGMETA-2386 Agosto Apuração Aberto ASPLAGMETA-2387 Setembro Apuração Aberto ASPLAGMETA-2388 Outubro Apuração Aberto ASPLAGMETA-2389 Novembro Apuração Aberto ASPLAGMETA-2390 Dezembro Apuração Aberto ASPLAGMETA-2391 Apurado no período Apuração Aberto</t>
+          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2585 Janeiro Apuração Aberto ASPLAGMETA-2588 Fevereiro Apuração Aberto ASPLAGMETA-2589 Março Apuração Aberto ASPLAGMETA-2590 Abril Apuração Aberto ASPLAGMETA-2592 Maio Apuração Aberto ASPLAGMETA-2594 Junho Apuração Aberto ASPLAGMETA-2595 Julho Apuração Aberto ASPLAGMETA-2596 Agosto Apuração Aberto ASPLAGMETA-2597 Setembro Apuração Aberto ASPLAGMETA-2598 Outubro Apuração Aberto ASPLAGMETA-2599 Novembro Apuração Aberto ASPLAGMETA-2600 Dezembro Apuração Aberto ASPLAGMETA-2601 Apurado no período Apuração Aberto</t>
         </is>
       </c>
       <c r="AU186" t="inlineStr">
         <is>
-          <t>(31) 32378261</t>
+          <t>3133063042</t>
         </is>
       </c>
       <c r="AV186" t="inlineStr">
@@ -42265,18 +42149,18 @@
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>SEPLAN</t>
+          <t>Presidência</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr">
         <is>
-          <t>Percentual</t>
+          <t>Unidade</t>
         </is>
       </c>
       <c r="AZ186" t="inlineStr"/>
       <c r="BA186" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>40</t>
         </is>
       </c>
       <c r="BB186" t="inlineStr">
@@ -42305,7 +42189,7 @@
       <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr">
         <is>
-          <t>[ASPLAGMETA-2106] TJMG 17 - Executar, até dezembro de 2025, 70% (setenta por cento) dos marcos previstos para o ano na iniciativa "Plano de estruturação organizacional para a produtividade na prestação jurisdicional".</t>
+          <t>[ASPLAGMETA-2111] TJMG 115 - Devolver para o respectivo Cartório 95% (noventa e cinco por cento) dos processos conclusos no prazo de até 90 (noventa) dias, contado da data da conclusão.</t>
         </is>
       </c>
       <c r="F187" t="inlineStr"/>
@@ -42321,7 +42205,7 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>Secretário Especial da Presidência e CP</t>
+          <t>Diretora de Secretaria</t>
         </is>
       </c>
       <c r="J187" t="inlineStr"/>
@@ -42344,15 +42228,19 @@
       <c r="O187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Presidência</t>
+          <t>1ª Vice Presidência</t>
         </is>
       </c>
       <c r="Q187" t="inlineStr">
         <is>
-          <t>segove@tjmg.jus.br</t>
-        </is>
-      </c>
-      <c r="R187" t="inlineStr"/>
+          <t>sepad@tjmg.jus.br</t>
+        </is>
+      </c>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>asplag@tjmg.jus.br</t>
+        </is>
+      </c>
       <c r="S187" t="inlineStr">
         <is>
           <t>Responsável</t>
@@ -42367,34 +42255,34 @@
       <c r="V187" t="inlineStr"/>
       <c r="W187" t="inlineStr">
         <is>
-          <t>Sra. Moema/ SEGOVE</t>
+          <t>CEINJUR</t>
         </is>
       </c>
       <c r="X187" t="inlineStr">
         <is>
-          <t>Último Valor</t>
+          <t>Média</t>
         </is>
       </c>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>Resultado do indicador = QME/QMP X 100, onde: QME = Quantidade de marcos executados. QMP = Quantidade de marcos previstos.</t>
+          <t>Total de processos devolvidos ao cartório em até 90 dias /Total de processos conclusos ao gabinete X 100</t>
         </is>
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>Sr. Guilherme  Augusto Mendes do Valle</t>
+          <t>Sra. Elaine Batista Costa Souza</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
         <is>
           <t>2025
-             - 3.19 - Taxa de cumprimento das atividades previstas para o ano vigente na iniciativa "Plano de estruturação organizacional para a produtividade na prestação jurisdicional".</t>
+             - 3.52 - Índice de processos conclusos aos relatores, em até 90 dias.</t>
         </is>
       </c>
       <c r="AB187" t="inlineStr"/>
       <c r="AC187" t="inlineStr">
         <is>
-          <t>21 - Plano de Estruturação Organizacional para a Produtividade na Prestação Jurisdicional.</t>
+          <t>04 - Programa Agiliza-Jus. , 94 - Programa 1ª Vice SOMA - Suporte à organização, cumprimento de metas e aperfeiçoamento gerencial.</t>
         </is>
       </c>
       <c r="AD187" t="inlineStr">
@@ -42414,7 +42302,11 @@
         </is>
       </c>
       <c r="AH187" t="inlineStr"/>
-      <c r="AI187" t="inlineStr"/>
+      <c r="AI187" t="inlineStr">
+        <is>
+          <t>ASPLAG</t>
+        </is>
+      </c>
       <c r="AJ187" t="inlineStr">
         <is>
           <t>16 - Paz, Justiça e Instituições Eficazes</t>
@@ -42423,7 +42315,7 @@
       <c r="AK187" t="inlineStr"/>
       <c r="AL187" t="inlineStr">
         <is>
-          <t>Desembargador Luiz Carlos de Azevedo Correa Junior</t>
+          <t>Dr. Marcelo Paulo Salgado</t>
         </is>
       </c>
       <c r="AM187" t="inlineStr">
@@ -42458,17 +42350,17 @@
       </c>
       <c r="AS187" t="inlineStr">
         <is>
-          <t>ASPLAGMETA-2360</t>
+          <t>ASPLAGMETA-2496</t>
         </is>
       </c>
       <c r="AT187" t="inlineStr">
         <is>
-          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2360 Janeiro Apuração Aberto ASPLAGMETA-2362 Fevereiro Apuração Aberto ASPLAGMETA-2364 Março Apuração Aberto ASPLAGMETA-2366 Abril Apuração Aberto ASPLAGMETA-2367 Maio Apuração Aberto ASPLAGMETA-2368 Junho Apuração Aberto ASPLAGMETA-2370 Julho Apuração Aberto ASPLAGMETA-2372 Agosto Apuração Aberto ASPLAGMETA-2374 Setembro Apuração Aberto ASPLAGMETA-2375 Outubro Apuração Aberto ASPLAGMETA-2376 Novembro Apuração Aberto ASPLAGMETA-2377 Dezembro Apuração Aberto ASPLAGMETA-2378 Apurado no período Apuração Aberto</t>
+          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2496 Janeiro Apuração Aberto ASPLAGMETA-2497 Fevereiro Apuração Aberto ASPLAGMETA-2498 Março Apuração Aberto ASPLAGMETA-2499 Abril Apuração Aberto ASPLAGMETA-2500 Maio Apuração Aberto ASPLAGMETA-2501 Junho Apuração Aberto ASPLAGMETA-2502 Julho Apuração Aberto ASPLAGMETA-2504 Agosto Apuração Aberto ASPLAGMETA-2505 Setembro Apuração Aberto ASPLAGMETA-2507 Outubro Apuração Aberto ASPLAGMETA-2509 Novembro Apuração Aberto ASPLAGMETA-2515 Dezembro Apuração Aberto ASPLAGMETA-2519 Apurado no período Apuração Aberto</t>
         </is>
       </c>
       <c r="AU187" t="inlineStr">
         <is>
-          <t>(31) 3306-3166</t>
+          <t>(31) 3232 - 2687</t>
         </is>
       </c>
       <c r="AV187" t="inlineStr">
@@ -42483,7 +42375,7 @@
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>SEGOVE</t>
+          <t>SEPAD</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr">
@@ -42494,7 +42386,7 @@
       <c r="AZ187" t="inlineStr"/>
       <c r="BA187" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>95</t>
         </is>
       </c>
       <c r="BB187" t="inlineStr">
@@ -42523,7 +42415,7 @@
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr">
         <is>
-          <t>[ASPLAGMETA-2105] TJMG 10 - Reduzir, até 31/12/2025, em 30% (trinta por cento) os mandados judiciais em atraso na 1ª instância, há mais de 30 (trinta) dias.</t>
+          <t>[ASPLAGMETA-2110] TJMG 91 - Movimentar 95% (noventa e cinco por cento) do acervo processual em prazo inferior a 60 (sessenta) dias.</t>
         </is>
       </c>
       <c r="F188" t="inlineStr"/>
@@ -42539,7 +42431,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>Diretor Executivo</t>
+          <t>Diretora de Secretaria</t>
         </is>
       </c>
       <c r="J188" t="inlineStr"/>
@@ -42562,19 +42454,15 @@
       <c r="O188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Corregedoria</t>
+          <t>1ª Vice Presidência</t>
         </is>
       </c>
       <c r="Q188" t="inlineStr">
         <is>
-          <t>dircor@tjmg.jus.br</t>
-        </is>
-      </c>
-      <c r="R188" t="inlineStr">
-        <is>
-          <t>asplag@tjmg.jus.br</t>
-        </is>
-      </c>
+          <t>sepad@tjmg.jus.br</t>
+        </is>
+      </c>
+      <c r="R188" t="inlineStr"/>
       <c r="S188" t="inlineStr">
         <is>
           <t>Responsável</t>
@@ -42589,34 +42477,34 @@
       <c r="V188" t="inlineStr"/>
       <c r="W188" t="inlineStr">
         <is>
-          <t>CEJUR/SEPLAN;  SIJUD - Sistema de Informações Estratégicas do Judiciário.</t>
+          <t>CEINJUR</t>
         </is>
       </c>
       <c r="X188" t="inlineStr">
         <is>
-          <t>Último Valor</t>
+          <t>Média</t>
         </is>
       </c>
       <c r="Y188" t="inlineStr">
         <is>
-          <t>[(Quantidade de mandados judiciais em atraso há mais de 30 dias na data de apuração (MJ30f) dividida pela Quantidade de mandados judiciais em atraso há mais de 30 dias em 31/12/2024 (MJ30i)) - 1] x 100</t>
+          <t>Fórmula = (∑PAC&lt;61d / ∑PPAC) X 1000/k, onde: PAC = processos do acervo dos cartórios; PPAC = processos paralisados no acervo; k = 9,5 para o período de referência “Até 31/12/2025”.</t>
         </is>
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>Sr. Ricardo de Freitas Reis</t>
+          <t>Sra. Elaine Batista Costa Souza</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
           <t>2025
-             - 3.12 - Taxa de redução de mandados judiciais em atraso.</t>
+             - 3.51 - Índice de tramitação processual em até 60 (sessenta) dias.</t>
         </is>
       </c>
       <c r="AB188" t="inlineStr"/>
       <c r="AC188" t="inlineStr">
         <is>
-          <t>05 - Programa de Melhoria de Indicadores do IPC-Jus TJMG.</t>
+          <t>04 - Programa Agiliza-Jus. , 94 - Programa 1ª Vice SOMA - Suporte à organização, cumprimento de metas e aperfeiçoamento gerencial.</t>
         </is>
       </c>
       <c r="AD188" t="inlineStr">
@@ -42636,29 +42524,21 @@
         </is>
       </c>
       <c r="AH188" t="inlineStr"/>
-      <c r="AI188" t="inlineStr">
-        <is>
-          <t>ASPLAG</t>
-        </is>
-      </c>
+      <c r="AI188" t="inlineStr"/>
       <c r="AJ188" t="inlineStr">
         <is>
           <t>16 - Paz, Justiça e Instituições Eficazes</t>
         </is>
       </c>
-      <c r="AK188" t="inlineStr">
-        <is>
-          <t>CEJUR , COSIS , GEFIS , GEINF , GESIS , SEPLAN</t>
-        </is>
-      </c>
+      <c r="AK188" t="inlineStr"/>
       <c r="AL188" t="inlineStr">
         <is>
-          <t>Dr. Guilherme Lima Nogueira da Silva</t>
+          <t>Dr.  Marcelo Paulo Salgado</t>
         </is>
       </c>
       <c r="AM188" t="inlineStr">
         <is>
-          <t>Trimestral</t>
+          <t>Mensal</t>
         </is>
       </c>
       <c r="AN188" t="inlineStr">
@@ -42688,17 +42568,17 @@
       </c>
       <c r="AS188" t="inlineStr">
         <is>
-          <t>ASPLAGMETA-2327</t>
+          <t>ASPLAGMETA-2483</t>
         </is>
       </c>
       <c r="AT188" t="inlineStr">
         <is>
-          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2327 Janeiro Apuração Aberto ASPLAGMETA-2341 Fevereiro Apuração Aberto ASPLAGMETA-2342 Março Apuração Aberto ASPLAGMETA-2343 Abril Apuração Aberto ASPLAGMETA-2344 Maio Apuração Aberto ASPLAGMETA-2345 Junho Apuração Aberto ASPLAGMETA-2346 Julho Apuração Aberto ASPLAGMETA-2348 Agosto Apuração Aberto ASPLAGMETA-2349 Setembro Apuração Aberto ASPLAGMETA-2351 Outubro Apuração Aberto ASPLAGMETA-2352 Novembro Apuração Aberto ASPLAGMETA-2354 Dezembro Apuração Aberto ASPLAGMETA-2357 Apurado no período Apuração Aberto</t>
+          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2483 Janeiro Apuração Aberto ASPLAGMETA-2484 Fevereiro Apuração Aberto ASPLAGMETA-2485 Março Apuração Aberto ASPLAGMETA-2486 Abril Apuração Aberto ASPLAGMETA-2487 Maio Apuração Aberto ASPLAGMETA-2488 Junho Apuração Aberto ASPLAGMETA-2489 Julho Apuração Aberto ASPLAGMETA-2490 Agosto Apuração Aberto ASPLAGMETA-2491 Setembro Apuração Aberto ASPLAGMETA-2492 Outubro Apuração Aberto ASPLAGMETA-2493 Novembro Apuração Aberto ASPLAGMETA-2494 Dezembro Apuração Aberto ASPLAGMETA-2495 Apurado no período Apuração Aberto</t>
         </is>
       </c>
       <c r="AU188" t="inlineStr">
         <is>
-          <t>(31) 3237-8260</t>
+          <t>(31) 3232-2687</t>
         </is>
       </c>
       <c r="AV188" t="inlineStr">
@@ -42713,7 +42593,7 @@
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>DIRCOR</t>
+          <t>SEPAD</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr">
@@ -42724,7 +42604,7 @@
       <c r="AZ188" t="inlineStr"/>
       <c r="BA188" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>95</t>
         </is>
       </c>
       <c r="BB188" t="inlineStr">
@@ -42753,7 +42633,7 @@
       <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr">
         <is>
-          <t>[ASPLAGMETA-2104] TJMG 7 - Publicar, em 2025, 95% (noventa e cinco por cento) dos acórdãos no prazo máximo de 10 (dez) dias após o julgamento dos processos.</t>
+          <t>[ASPLAGMETA-2109] TJMG 85 - Proferir, em 2025, 60.000 (sessenta mil) atos de cooperação (audiências, júri, sentenças, decisões, despachos), em processos cíveis e criminais, em caráter de cooperação no Programa Pontualidade 5.0.</t>
         </is>
       </c>
       <c r="F189" t="inlineStr"/>
@@ -42769,7 +42649,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>Diretor de Secretaria</t>
+          <t>Juíza Auxiliar da Presidência</t>
         </is>
       </c>
       <c r="J189" t="inlineStr"/>
@@ -42792,15 +42672,19 @@
       <c r="O189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>1ª Vice Presidência</t>
+          <t>Presidência</t>
         </is>
       </c>
       <c r="Q189" t="inlineStr">
         <is>
-          <t>sepad@tjmg.jus.br</t>
-        </is>
-      </c>
-      <c r="R189" t="inlineStr"/>
+          <t>juizauxpres.marcela@tjmg.jus.br</t>
+        </is>
+      </c>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t>asplag@tjmg.jus.br</t>
+        </is>
+      </c>
       <c r="S189" t="inlineStr">
         <is>
           <t>Responsável</t>
@@ -42815,34 +42699,34 @@
       <c r="V189" t="inlineStr"/>
       <c r="W189" t="inlineStr">
         <is>
-          <t>CEINJUR</t>
+          <t>Centro de Monitoramento e Suporte à Prestação Jurisdicional, CEMJUR/ SEGOVE, por meio do Sistema Eletrônico de Informações (SEI).</t>
         </is>
       </c>
       <c r="X189" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Soma</t>
         </is>
       </c>
       <c r="Y189" t="inlineStr">
         <is>
-          <t>Resultado do indicador: AP10d/TAP X 100, onde AP10d = Acórdãos publicados em até 10 dias TPA = Total de acórdãos publicados AP10d ∑ dos processos julgados [(data de publicação do acórdão) - (data do julgamento) =&lt; 10dias}</t>
+          <t>Somatório de audiências, júris, sentenças, decisões e despachos proferidos, em processos cíveis e criminais, em caráter de cooperação no Programa Pontualidade 5.0.</t>
         </is>
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>Sra. Elaine Batista Costa Souza</t>
+          <t>Dra. Marcela Maria Pereira Amaral Novais</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
         <is>
           <t>2025
-             - 3.9 - Índice de acórdãos publicados em até 10 (dez) dias.</t>
+             - 3.34 - Número de atos proferidos, em processos cíveis e criminais, em caráter de cooperação no Programa Pontualidade 5.0.</t>
         </is>
       </c>
       <c r="AB189" t="inlineStr"/>
       <c r="AC189" t="inlineStr">
         <is>
-          <t>04 - Programa Agiliza-Jus. , 94 - Programa 1ª Vice SOMA - Suporte à organização, cumprimento de metas e aperfeiçoamento gerencial.</t>
+          <t>06 - Programa Pontualidade 5.0.</t>
         </is>
       </c>
       <c r="AD189" t="inlineStr">
@@ -42862,21 +42746,29 @@
         </is>
       </c>
       <c r="AH189" t="inlineStr"/>
-      <c r="AI189" t="inlineStr"/>
+      <c r="AI189" t="inlineStr">
+        <is>
+          <t>ASPLAG</t>
+        </is>
+      </c>
       <c r="AJ189" t="inlineStr">
         <is>
           <t>16 - Paz, Justiça e Instituições Eficazes</t>
         </is>
       </c>
-      <c r="AK189" t="inlineStr"/>
+      <c r="AK189" t="inlineStr">
+        <is>
+          <t>CEINFO , CEMJUR</t>
+        </is>
+      </c>
       <c r="AL189" t="inlineStr">
         <is>
-          <t>Dr. Marcelo Paulo Salgado</t>
+          <t>Des. Luiz Carlos de Azevedo Corrêa Junior</t>
         </is>
       </c>
       <c r="AM189" t="inlineStr">
         <is>
-          <t>Trimestral</t>
+          <t>Mensal</t>
         </is>
       </c>
       <c r="AN189" t="inlineStr">
@@ -42906,17 +42798,17 @@
       </c>
       <c r="AS189" t="inlineStr">
         <is>
-          <t>ASPLAGMETA-2328</t>
+          <t>ASPLAGMETA-2470</t>
         </is>
       </c>
       <c r="AT189" t="inlineStr">
         <is>
-          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2328 Janeiro Apuração Aberto ASPLAGMETA-2329 Fevereiro Apuração Aberto ASPLAGMETA-2330 Março Apuração Aberto ASPLAGMETA-2331 Abril Apuração Aberto ASPLAGMETA-2332 Maio Apuração Aberto ASPLAGMETA-2333 Junho Apuração Aberto ASPLAGMETA-2334 Julho Apuração Aberto ASPLAGMETA-2335 Agosto Apuração Aberto ASPLAGMETA-2336 Setembro Apuração Aberto ASPLAGMETA-2337 Outubro Apuração Aberto ASPLAGMETA-2338 Novembro Apuração Aberto ASPLAGMETA-2339 Dezembro Apuração Aberto ASPLAGMETA-2340 Apurado no período Apuração Aberto</t>
+          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2470 Janeiro Apuração Aberto ASPLAGMETA-2471 Fevereiro Apuração Aberto ASPLAGMETA-2472 Março Apuração Aberto ASPLAGMETA-2473 Abril Apuração Aberto ASPLAGMETA-2474 Maio Apuração Aberto ASPLAGMETA-2475 Junho Apuração Aberto ASPLAGMETA-2476 Julho Apuração Aberto ASPLAGMETA-2477 Agosto Apuração Aberto ASPLAGMETA-2478 Setembro Apuração Aberto ASPLAGMETA-2479 Outubro Apuração Aberto ASPLAGMETA-2480 Novembro Apuração Aberto ASPLAGMETA-2481 Dezembro Apuração Aberto ASPLAGMETA-2482 Apurado no período Apuração Aberto</t>
         </is>
       </c>
       <c r="AU189" t="inlineStr">
         <is>
-          <t>(31) 3232-2687</t>
+          <t>3133063042</t>
         </is>
       </c>
       <c r="AV189" t="inlineStr">
@@ -42931,18 +42823,18 @@
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>SEPAD</t>
+          <t>Presidência</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr">
         <is>
-          <t>Percentual</t>
+          <t>Unidade</t>
         </is>
       </c>
       <c r="AZ189" t="inlineStr"/>
       <c r="BA189" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>60.000</t>
         </is>
       </c>
       <c r="BB189" t="inlineStr">
@@ -42971,7 +42863,7 @@
       <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr">
         <is>
-          <t>[ASPLAGMETA-2103] TJMG 6 - Realizar, em 2025, 70% (setenta por cento) dos julgamentos colegiados em até 100 dias. (desconsiderado o tempo de permanência em carga aos Advogados e aos Órgãos Externos, 25 (vinte e cinco) dias).</t>
+          <t>[ASPLAGMETA-2108] TJMG 80 - Concluir, até dezembro de 2025, 100% (cem por cento) das atividades previstas para o ano no Programa de Desenvolvimento da Atuação do Centro de Inteligência da Justiça de Minas Gerais.</t>
         </is>
       </c>
       <c r="F190" t="inlineStr"/>
@@ -42985,11 +42877,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>Diretora de Secretaria</t>
-        </is>
-      </c>
+      <c r="I190" t="inlineStr"/>
       <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr">
         <is>
@@ -43010,14 +42898,10 @@
       <c r="O190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>1ª Vice Presidência</t>
-        </is>
-      </c>
-      <c r="Q190" t="inlineStr">
-        <is>
-          <t>sepad@tjmg.jus.br</t>
-        </is>
-      </c>
+          <t>Presidência</t>
+        </is>
+      </c>
+      <c r="Q190" t="inlineStr"/>
       <c r="R190" t="inlineStr"/>
       <c r="S190" t="inlineStr">
         <is>
@@ -43031,36 +42915,28 @@
       </c>
       <c r="U190" t="inlineStr"/>
       <c r="V190" t="inlineStr"/>
-      <c r="W190" t="inlineStr">
-        <is>
-          <t>CEINJUR</t>
-        </is>
-      </c>
+      <c r="W190" t="inlineStr"/>
       <c r="X190" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Último Valor</t>
         </is>
       </c>
       <c r="Y190" t="inlineStr">
         <is>
-          <t>Resultado do indicador: JC100d/ TJC, onde: JC100d = Número de julgamentos colegiados realizados em até 100 dias TJC = Total de julgamentos colegiados realizados no período JC100d  ∑ dos processos decididos pelo colegiado [(data de distribuição do processo) - (data do julgamento colegiado) =&lt; 100dias}</t>
-        </is>
-      </c>
-      <c r="Z190" t="inlineStr">
-        <is>
-          <t>Sra. Elaine Batista Costa Souza</t>
-        </is>
-      </c>
+          <t>Quantidade de atividades executadas do Programa de Desenvolvimento da Atuação do Centro de Inteligência da Justiça de Minas Gerais / (sobre) quantidade total de atividades propostas x 100.</t>
+        </is>
+      </c>
+      <c r="Z190" t="inlineStr"/>
       <c r="AA190" t="inlineStr">
         <is>
           <t>2025
-             - 3.8 - Taxa de julgamentos colegiados em até 100 (cem) dias - 2º Grau.</t>
+             - 3.32 - Taxa de execução das atividades do Programa de Desenvolvimento da Atuação do Centro de Inteligência da Justiça de Minas Gerais.</t>
         </is>
       </c>
       <c r="AB190" t="inlineStr"/>
       <c r="AC190" t="inlineStr">
         <is>
-          <t>04 - Programa Agiliza-Jus. , 94 - Programa 1ª Vice SOMA - Suporte à organização, cumprimento de metas e aperfeiçoamento gerencial.</t>
+          <t>68 - Programa de Desenvolvimento da Atuação do Centro de Inteligência.</t>
         </is>
       </c>
       <c r="AD190" t="inlineStr">
@@ -43087,14 +42963,10 @@
         </is>
       </c>
       <c r="AK190" t="inlineStr"/>
-      <c r="AL190" t="inlineStr">
-        <is>
-          <t>Dr.  Marcelo Paulo Salgado</t>
-        </is>
-      </c>
+      <c r="AL190" t="inlineStr"/>
       <c r="AM190" t="inlineStr">
         <is>
-          <t>Mensal</t>
+          <t>Trimestral</t>
         </is>
       </c>
       <c r="AN190" t="inlineStr">
@@ -43124,19 +42996,15 @@
       </c>
       <c r="AS190" t="inlineStr">
         <is>
-          <t>ASPLAGMETA-2314</t>
+          <t>ASPLAGMETA-2457</t>
         </is>
       </c>
       <c r="AT190" t="inlineStr">
         <is>
-          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2314 Janeiro Apuração Aberto ASPLAGMETA-2315 Fevereiro Apuração Aberto ASPLAGMETA-2316 Março Apuração Aberto ASPLAGMETA-2317 Abril Apuração Aberto ASPLAGMETA-2318 Maio Apuração Aberto ASPLAGMETA-2319 Junho Apuração Aberto ASPLAGMETA-2320 Julho Apuração Aberto ASPLAGMETA-2321 Agosto Apuração Aberto ASPLAGMETA-2322 Setembro Apuração Aberto ASPLAGMETA-2323 Outubro Apuração Aberto ASPLAGMETA-2324 Novembro Apuração Aberto ASPLAGMETA-2325 Dezembro Apuração Aberto ASPLAGMETA-2326 Apurado no período Apuração Aberto</t>
-        </is>
-      </c>
-      <c r="AU190" t="inlineStr">
-        <is>
-          <t>(31) 3232-2687</t>
-        </is>
-      </c>
+          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2457 Janeiro Apuração Aberto ASPLAGMETA-2458 Fevereiro Apuração Aberto ASPLAGMETA-2459 Março Apuração Aberto ASPLAGMETA-2460 Abril Apuração Aberto ASPLAGMETA-2461 Maio Apuração Aberto ASPLAGMETA-2462 Junho Apuração Aberto ASPLAGMETA-2463 Julho Apuração Aberto ASPLAGMETA-2464 Agosto Apuração Aberto ASPLAGMETA-2465 Setembro Apuração Aberto ASPLAGMETA-2466 Outubro Apuração Aberto ASPLAGMETA-2467 Novembro Apuração Aberto ASPLAGMETA-2468 Dezembro Apuração Aberto ASPLAGMETA-2469 Apurado no período Apuração Aberto</t>
+        </is>
+      </c>
+      <c r="AU190" t="inlineStr"/>
       <c r="AV190" t="inlineStr">
         <is>
           <t>Estado</t>
@@ -43149,7 +43017,7 @@
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>SEPAD</t>
+          <t>SEGOVE</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
@@ -43160,7 +43028,7 @@
       <c r="AZ190" t="inlineStr"/>
       <c r="BA190" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>100</t>
         </is>
       </c>
       <c r="BB190" t="inlineStr">
@@ -43189,7 +43057,7 @@
       <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr">
         <is>
-          <t>[ASPLAGMETA-2102] TJMG 5 - Realizar, em 2025, 70% (setenta por cento) dos julgamentos monocráticos, pelo relator, em 60 (sessenta) dias (desconsiderado o tempo de permanência em carga aos Advogados e aos Órgãos Externos, 25 (vinte e cinco) dias).</t>
+          <t>[ASPLAGMETA-2107] TJMG 79 - Executar, até 2025, 100% (cem por cento) das atividades previstas no plano de Integração do Sistema PJe com o e-Carta Correios.</t>
         </is>
       </c>
       <c r="F191" t="inlineStr"/>
@@ -43205,7 +43073,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>Diretora de Secretaria</t>
+          <t>Diretor de Secretaria</t>
         </is>
       </c>
       <c r="J191" t="inlineStr"/>
@@ -43228,12 +43096,12 @@
       <c r="O191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>1ª Vice Presidência</t>
+          <t>Corregedoria</t>
         </is>
       </c>
       <c r="Q191" t="inlineStr">
         <is>
-          <t>sepad@tjmg.jus.br</t>
+          <t>seplan@tjmg.jus.br</t>
         </is>
       </c>
       <c r="R191" t="inlineStr">
@@ -43255,34 +43123,34 @@
       <c r="V191" t="inlineStr"/>
       <c r="W191" t="inlineStr">
         <is>
-          <t>CEINJUR</t>
+          <t>SEPLAN/COAPE. Cronograma de atividades da iniciativa 67 no Jira</t>
         </is>
       </c>
       <c r="X191" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Último Valor</t>
         </is>
       </c>
       <c r="Y191" t="inlineStr">
         <is>
-          <t>Resultado do indicador = JM60d/TJM X 100, onde: JM60d = Número de julgamentos monocráticos realizados em até 60 dias. TJM = Total de julgamentos monocráticos realizados no período. JM60d  ∑ dos processos decididos monocraticamente [(data de distribuição do processo) - (data da decisão monocrática) =&lt; 60dias.</t>
+          <t>QR/QP, sendo: QR = Quantidade de atividades realizadas no ano e QP = Quantidade de atividades planejadas para o ano &gt; Considera o "peso" de cada atividade no cronograma.</t>
         </is>
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>Sra. Elaine Batista Costa Souza</t>
+          <t>Sra. Bruna Eduarda Medeiros de Sousa</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
           <t>2025
-             - 3.7 - Taxa de julgamentos monocráticos em até 60 (sessenta) dias - 2º Grau.</t>
+             - 3.31 - Taxa de execução do plano de Integração do Sistema PJe com o e-Carta Correios.</t>
         </is>
       </c>
       <c r="AB191" t="inlineStr"/>
       <c r="AC191" t="inlineStr">
         <is>
-          <t>04 - Programa Agiliza-Jus. , 94 - Programa 1ª Vice SOMA - Suporte à organização, cumprimento de metas e aperfeiçoamento gerencial.</t>
+          <t>67 - Integração do Sistema PJe com o e-Carta Correios.</t>
         </is>
       </c>
       <c r="AD191" t="inlineStr">
@@ -43312,10 +43180,14 @@
           <t>16 - Paz, Justiça e Instituições Eficazes</t>
         </is>
       </c>
-      <c r="AK191" t="inlineStr"/>
+      <c r="AK191" t="inlineStr">
+        <is>
+          <t>COAPE , DIRFOR</t>
+        </is>
+      </c>
       <c r="AL191" t="inlineStr">
         <is>
-          <t>Dr. Marcelo Paulo Salgado</t>
+          <t>Des. Estevão Lucchesi de Carvalho.</t>
         </is>
       </c>
       <c r="AM191" t="inlineStr">
@@ -43350,17 +43222,17 @@
       </c>
       <c r="AS191" t="inlineStr">
         <is>
-          <t>ASPLAGMETA-2301</t>
+          <t>ASPLAGMETA-2379</t>
         </is>
       </c>
       <c r="AT191" t="inlineStr">
         <is>
-          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2301 Janeiro Apuração Aberto ASPLAGMETA-2302 Fevereiro Apuração Aberto ASPLAGMETA-2303 Março Apuração Aberto ASPLAGMETA-2304 Abril Apuração Aberto ASPLAGMETA-2305 Maio Apuração Aberto ASPLAGMETA-2306 Junho Apuração Aberto ASPLAGMETA-2307 Julho Apuração Aberto ASPLAGMETA-2308 Agosto Apuração Aberto ASPLAGMETA-2309 Setembro Apuração Aberto ASPLAGMETA-2310 Outubro Apuração Aberto ASPLAGMETA-2311 Novembro Apuração Aberto ASPLAGMETA-2312 Dezembro Apuração Aberto ASPLAGMETA-2313 Apurado no período Apuração Aberto</t>
+          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2379 Janeiro Apuração Aberto ASPLAGMETA-2380 Fevereiro Apuração Aberto ASPLAGMETA-2381 Março Apuração Aberto ASPLAGMETA-2382 Abril Apuração Aberto ASPLAGMETA-2383 Maio Apuração Aberto ASPLAGMETA-2384 Junho Apuração Aberto ASPLAGMETA-2385 Julho Apuração Aberto ASPLAGMETA-2386 Agosto Apuração Aberto ASPLAGMETA-2387 Setembro Apuração Aberto ASPLAGMETA-2388 Outubro Apuração Aberto ASPLAGMETA-2389 Novembro Apuração Aberto ASPLAGMETA-2390 Dezembro Apuração Aberto ASPLAGMETA-2391 Apurado no período Apuração Aberto</t>
         </is>
       </c>
       <c r="AU191" t="inlineStr">
         <is>
-          <t>(31) 3232-2687</t>
+          <t>(31) 32378261</t>
         </is>
       </c>
       <c r="AV191" t="inlineStr">
@@ -43375,7 +43247,7 @@
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>SEPAD</t>
+          <t>SEPLAN</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr">
@@ -43386,7 +43258,7 @@
       <c r="AZ191" t="inlineStr"/>
       <c r="BA191" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>100</t>
         </is>
       </c>
       <c r="BB191" t="inlineStr">
@@ -43415,7 +43287,7 @@
       <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr">
         <is>
-          <t>[ASPLAGMETA-2101] TJMG 100 - Promover, por ação própria ou mediante parceria com outros órgãos internos e externos ao TJMG, o oferecimento de serviços de itinerância em pelo menos 50 (cinquenta) ações, até dezembro de 2025.</t>
+          <t>[ASPLAGMETA-2106] TJMG 17 - Executar, até dezembro de 2025, 70% (setenta por cento) dos marcos previstos para o ano na iniciativa "Plano de estruturação organizacional para a produtividade na prestação jurisdicional".</t>
         </is>
       </c>
       <c r="F192" t="inlineStr"/>
@@ -43431,7 +43303,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>Gerente</t>
+          <t>Secretário Especial da Presidência e CP</t>
         </is>
       </c>
       <c r="J192" t="inlineStr"/>
@@ -43454,19 +43326,15 @@
       <c r="O192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>3ª Vice Presidência</t>
+          <t>Presidência</t>
         </is>
       </c>
       <c r="Q192" t="inlineStr">
         <is>
-          <t>agin@tjmg.jus.br</t>
-        </is>
-      </c>
-      <c r="R192" t="inlineStr">
-        <is>
-          <t>asplag@tjmg.jus.br</t>
-        </is>
-      </c>
+          <t>segove@tjmg.jus.br</t>
+        </is>
+      </c>
+      <c r="R192" t="inlineStr"/>
       <c r="S192" t="inlineStr">
         <is>
           <t>Responsável</t>
@@ -43479,28 +43347,36 @@
       </c>
       <c r="U192" t="inlineStr"/>
       <c r="V192" t="inlineStr"/>
-      <c r="W192" t="inlineStr"/>
+      <c r="W192" t="inlineStr">
+        <is>
+          <t>Sra. Moema/ SEGOVE</t>
+        </is>
+      </c>
       <c r="X192" t="inlineStr">
         <is>
-          <t>Soma</t>
+          <t>Último Valor</t>
         </is>
       </c>
       <c r="Y192" t="inlineStr">
         <is>
-          <t>Somatório do número de ações realizadas no âmbito da descrição da meta no ano de 2025</t>
-        </is>
-      </c>
-      <c r="Z192" t="inlineStr"/>
+          <t>Resultado do indicador = QME/QMP X 100, onde: QME = Quantidade de marcos executados. QMP = Quantidade de marcos previstos.</t>
+        </is>
+      </c>
+      <c r="Z192" t="inlineStr">
+        <is>
+          <t>Sr. Guilherme  Augusto Mendes do Valle</t>
+        </is>
+      </c>
       <c r="AA192" t="inlineStr">
         <is>
           <t>2025
-             - 2.4 - Número de ações de itinerância efetivamente realizadas.</t>
+             - 3.19 - Taxa de cumprimento das atividades previstas para o ano vigente na iniciativa "Plano de estruturação organizacional para a produtividade na prestação jurisdicional".</t>
         </is>
       </c>
       <c r="AB192" t="inlineStr"/>
       <c r="AC192" t="inlineStr">
         <is>
-          <t>07 - Programa de estruturação de políticas públicas autocompositivas de solução de conflitos. , 47 - Programa de otimização do funcionamento dos CEJUSCs - Centros Judiciários de Solução de Conflitos e Cidadania.</t>
+          <t>21 - Plano de Estruturação Organizacional para a Produtividade na Prestação Jurisdicional.</t>
         </is>
       </c>
       <c r="AD192" t="inlineStr">
@@ -43516,28 +43392,20 @@
       <c r="AF192" t="inlineStr"/>
       <c r="AG192" t="inlineStr">
         <is>
-          <t>2 - Ampliação da Relação Institucional do Judiciário com a Sociedade</t>
+          <t>3 - Agilidade e Produtividade na Prestação Jurisdicional</t>
         </is>
       </c>
       <c r="AH192" t="inlineStr"/>
-      <c r="AI192" t="inlineStr">
-        <is>
-          <t>ASPLAG</t>
-        </is>
-      </c>
+      <c r="AI192" t="inlineStr"/>
       <c r="AJ192" t="inlineStr">
         <is>
           <t>16 - Paz, Justiça e Instituições Eficazes</t>
         </is>
       </c>
-      <c r="AK192" t="inlineStr">
-        <is>
-          <t>AGIN</t>
-        </is>
-      </c>
+      <c r="AK192" t="inlineStr"/>
       <c r="AL192" t="inlineStr">
         <is>
-          <t>Rogério Medeiros Garcia de Lima</t>
+          <t>Desembargador Luiz Carlos de Azevedo Correa Junior</t>
         </is>
       </c>
       <c r="AM192" t="inlineStr">
@@ -43572,17 +43440,17 @@
       </c>
       <c r="AS192" t="inlineStr">
         <is>
-          <t>ASPLAGMETA-2156</t>
+          <t>ASPLAGMETA-2360</t>
         </is>
       </c>
       <c r="AT192" t="inlineStr">
         <is>
-          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2156 Janeiro Apuração Aberto ASPLAGMETA-2157 Fevereiro Apuração Aberto ASPLAGMETA-2158 Março Apuração Aberto ASPLAGMETA-2159 Abril Apuração Aberto ASPLAGMETA-2160 Maio Apuração Aberto ASPLAGMETA-2161 Junho Apuração Aberto ASPLAGMETA-2162 Julho Apuração Aberto ASPLAGMETA-2163 Agosto Apuração Aberto ASPLAGMETA-2164 Setembro Apuração Aberto ASPLAGMETA-2165 Outubro Apuração Aberto ASPLAGMETA-2166 Novembro Apuração Aberto ASPLAGMETA-2167 Dezembro Apuração Aberto ASPLAGMETA-2168 Apurado no período Apuração Aberto</t>
+          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2360 Janeiro Apuração Aberto ASPLAGMETA-2362 Fevereiro Apuração Aberto ASPLAGMETA-2364 Março Apuração Aberto ASPLAGMETA-2366 Abril Apuração Aberto ASPLAGMETA-2367 Maio Apuração Aberto ASPLAGMETA-2368 Junho Apuração Aberto ASPLAGMETA-2370 Julho Apuração Aberto ASPLAGMETA-2372 Agosto Apuração Aberto ASPLAGMETA-2374 Setembro Apuração Aberto ASPLAGMETA-2375 Outubro Apuração Aberto ASPLAGMETA-2376 Novembro Apuração Aberto ASPLAGMETA-2377 Dezembro Apuração Aberto ASPLAGMETA-2378 Apurado no período Apuração Aberto</t>
         </is>
       </c>
       <c r="AU192" t="inlineStr">
         <is>
-          <t>(31) 3232-2615</t>
+          <t>(31) 3306-3166</t>
         </is>
       </c>
       <c r="AV192" t="inlineStr">
@@ -43597,18 +43465,18 @@
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Superintendência da Gestão de Inovação</t>
+          <t>SEGOVE</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr">
         <is>
-          <t>Unidade</t>
+          <t>Percentual</t>
         </is>
       </c>
       <c r="AZ192" t="inlineStr"/>
       <c r="BA192" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BB192" t="inlineStr">
@@ -43637,7 +43505,7 @@
       <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr">
         <is>
-          <t>[ASPLAGMETA-2100] TJMG 131 - Executar 100% (cem por cento) das entregas relativas à validação do fluxo de implantação dos Fóruns Digitais e à alteração da Resolução 1.061/2023.</t>
+          <t>[ASPLAGMETA-2105] TJMG 10 - Reduzir, até 31/12/2025, em 12% (trinta por cento) os mandados judiciais em atraso na 1ª instância, há mais de 30 (trinta) dias.</t>
         </is>
       </c>
       <c r="F193" t="inlineStr"/>
@@ -43653,7 +43521,7 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>Secretário Geral da Presidência, acompanhado por Juiz e Juíza auxiliar da Presidência, Juiz auxiliar da Corregedoria Geral de Justiça, Juiz da 3 Vice Presidência.</t>
+          <t>Diretor Executivo</t>
         </is>
       </c>
       <c r="J193" t="inlineStr"/>
@@ -43676,10 +43544,14 @@
       <c r="O193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Presidência</t>
-        </is>
-      </c>
-      <c r="Q193" t="inlineStr"/>
+          <t>Corregedoria</t>
+        </is>
+      </c>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>dircor@tjmg.jus.br</t>
+        </is>
+      </c>
       <c r="R193" t="inlineStr">
         <is>
           <t>asplag@tjmg.jus.br</t>
@@ -43699,7 +43571,7 @@
       <c r="V193" t="inlineStr"/>
       <c r="W193" t="inlineStr">
         <is>
-          <t>Cronograma de acompanhamento da iniciativa 86 - Fóruns Digitais.</t>
+          <t>CEJUR/SEPLAN;  SIJUD - Sistema de Informações Estratégicas do Judiciário.</t>
         </is>
       </c>
       <c r="X193" t="inlineStr">
@@ -43709,24 +43581,24 @@
       </c>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>Entregas concluídas até o período/ Entregas previstas no cômputo da meta. Obs.: À época da pactuação da meta, apenas 2 entregas eram conhecidas, motivo pelo qual foram nominadas na meta.</t>
+          <t>[(Quantidade de mandados judiciais em atraso há mais de 30 dias na data de apuração (MJ30f) dividida pela Quantidade de mandados judiciais em atraso há mais de 30 dias em 31/12/2024 (MJ30i)) - 1] x 100</t>
         </is>
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>Sr. Guilherme Augusto Mendes do Valle, acompanhado por: Dra. Marcela Maria Pereira Novais; Dr. Guilherme Lima Nogueira da Silva; Dr. José Ricardo dos Santos de Freitas Véras; Dr. Luís Fernando Benfatti.</t>
+          <t>Sr. Ricardo de Freitas Reis</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
           <t>2025
-             - 1.20 - Taxa de execução das entregas previstas na iniciativa Fóruns Dgitais.</t>
+             - 3.12 - Taxa de redução de mandados judiciais em atraso.</t>
         </is>
       </c>
       <c r="AB193" t="inlineStr"/>
       <c r="AC193" t="inlineStr">
         <is>
-          <t>86 - Fóruns Digitais.</t>
+          <t>05 - Programa de Melhoria de Indicadores do IPC-Jus TJMG.</t>
         </is>
       </c>
       <c r="AD193" t="inlineStr">
@@ -43742,7 +43614,7 @@
       <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="inlineStr">
         <is>
-          <t>1 - Garantia dos Direitos Fundamentais e do Estado Democrático de Direito</t>
+          <t>3 - Agilidade e Produtividade na Prestação Jurisdicional</t>
         </is>
       </c>
       <c r="AH193" t="inlineStr"/>
@@ -43758,17 +43630,17 @@
       </c>
       <c r="AK193" t="inlineStr">
         <is>
-          <t>DENGEP , DIRCOM , DIRCOR , DIRFOR , DIRSEP , GAPRE , SEOESP , SUP.3ª VICE , CORREGEDORIA</t>
+          <t>CEJUR , COSIS , GEFIS , GEINF , GESIS , SEPLAN</t>
         </is>
       </c>
       <c r="AL193" t="inlineStr">
         <is>
-          <t>Des. Luiz Carlos de Azevedo Corrêa Junior</t>
+          <t>Dr. Guilherme Lima Nogueira da Silva</t>
         </is>
       </c>
       <c r="AM193" t="inlineStr">
         <is>
-          <t>Mensal</t>
+          <t>Trimestral</t>
         </is>
       </c>
       <c r="AN193" t="inlineStr">
@@ -43798,15 +43670,19 @@
       </c>
       <c r="AS193" t="inlineStr">
         <is>
-          <t>ASPLAGMETA-2288</t>
+          <t>ASPLAGMETA-2327</t>
         </is>
       </c>
       <c r="AT193" t="inlineStr">
         <is>
-          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2288 Janeiro Apuração Aberto ASPLAGMETA-2289 Fevereiro Apuração Aberto ASPLAGMETA-2290 Março Apuração Aberto ASPLAGMETA-2291 Abril Apuração Aberto ASPLAGMETA-2292 Maio Apuração Aberto ASPLAGMETA-2293 Junho Apuração Aberto ASPLAGMETA-2294 Julho Apuração Aberto ASPLAGMETA-2295 Agosto Apuração Aberto ASPLAGMETA-2296 Setembro Apuração Aberto ASPLAGMETA-2297 Outubro Apuração Aberto ASPLAGMETA-2298 Novembro Apuração Aberto ASPLAGMETA-2299 Dezembro Apuração Aberto ASPLAGMETA-2300 Apurado no período Apuração Aberto</t>
-        </is>
-      </c>
-      <c r="AU193" t="inlineStr"/>
+          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2327 Janeiro Apuração Aberto ASPLAGMETA-2341 Fevereiro Apuração Aberto ASPLAGMETA-2342 Março Apuração Aberto ASPLAGMETA-2343 Abril Apuração Aberto ASPLAGMETA-2344 Maio Apuração Aberto ASPLAGMETA-2345 Junho Apuração Aberto ASPLAGMETA-2346 Julho Apuração Aberto ASPLAGMETA-2348 Agosto Apuração Aberto ASPLAGMETA-2349 Setembro Apuração Aberto ASPLAGMETA-2351 Outubro Apuração Aberto ASPLAGMETA-2352 Novembro Apuração Aberto ASPLAGMETA-2354 Dezembro Apuração Aberto ASPLAGMETA-2357 Apurado no período Apuração Aberto</t>
+        </is>
+      </c>
+      <c r="AU193" t="inlineStr">
+        <is>
+          <t>(31) 3237-8260</t>
+        </is>
+      </c>
       <c r="AV193" t="inlineStr">
         <is>
           <t>Estado</t>
@@ -43819,7 +43695,7 @@
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>SEGOVE</t>
+          <t>DIRCOR</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr">
@@ -43830,7 +43706,7 @@
       <c r="AZ193" t="inlineStr"/>
       <c r="BA193" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>30</t>
         </is>
       </c>
       <c r="BB193" t="inlineStr">
@@ -43859,7 +43735,7 @@
       <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr">
         <is>
-          <t>[ASPLAGMETA-2099] TJMG 145 - Beneficiar, até 18/12/2025, pelo menos 250.000 (duzentas e cinquenta mil) pessoas com as ações de impacto social fomentadas pela COINJ.</t>
+          <t>[ASPLAGMETA-2104] TJMG 7 - Publicar, em 2025, 95% (noventa e cinco por cento) dos acórdãos no prazo máximo de 10 (dez) dias após o julgamento dos processos.</t>
         </is>
       </c>
       <c r="F194" t="inlineStr"/>
@@ -43875,7 +43751,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>Coordenador</t>
+          <t>Diretor de Secretaria</t>
         </is>
       </c>
       <c r="J194" t="inlineStr"/>
@@ -43898,12 +43774,12 @@
       <c r="O194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Presidência</t>
+          <t>1ª Vice Presidência</t>
         </is>
       </c>
       <c r="Q194" t="inlineStr">
         <is>
-          <t>sandra.nunes@tjmg.jus.br</t>
+          <t>sepad@tjmg.jus.br</t>
         </is>
       </c>
       <c r="R194" t="inlineStr"/>
@@ -43921,34 +43797,34 @@
       <c r="V194" t="inlineStr"/>
       <c r="W194" t="inlineStr">
         <is>
-          <t>COINJ.</t>
+          <t>CEINJUR</t>
         </is>
       </c>
       <c r="X194" t="inlineStr">
         <is>
-          <t>Soma</t>
+          <t>Média</t>
         </is>
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>Somatório de pessoas diretamente beneficiadas com as ações de impacto social fomentadas pela COINJ no ano de 2025.</t>
+          <t>Resultado do indicador: AP10d/TAP X 100, onde AP10d = Acórdãos publicados em até 10 dias TPA = Total de acórdãos publicados AP10d ∑ dos processos julgados [(data de publicação do acórdão) - (data do julgamento) =&lt; 10dias}</t>
         </is>
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>Sandra Ferreira Nunes</t>
+          <t>Sra. Elaine Batista Costa Souza</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
           <t>2025
-             - 1.19 - Número de pessoas beneficiadas com as ações de impacto sociail fomentadas pela COINJ.</t>
+             - 3.9 - Índice de acórdãos publicados em até 10 (dez) dias.</t>
         </is>
       </c>
       <c r="AB194" t="inlineStr"/>
       <c r="AC194" t="inlineStr">
         <is>
-          <t>90 - Travessias da Infância e Juventude.</t>
+          <t>04 - Programa Agiliza-Jus. , 94 - Programa 1ª Vice SOMA - Suporte à organização, cumprimento de metas e aperfeiçoamento gerencial.</t>
         </is>
       </c>
       <c r="AD194" t="inlineStr">
@@ -43964,7 +43840,7 @@
       <c r="AF194" t="inlineStr"/>
       <c r="AG194" t="inlineStr">
         <is>
-          <t>1 - Garantia dos Direitos Fundamentais e do Estado Democrático de Direito</t>
+          <t>3 - Agilidade e Produtividade na Prestação Jurisdicional</t>
         </is>
       </c>
       <c r="AH194" t="inlineStr"/>
@@ -43977,7 +43853,7 @@
       <c r="AK194" t="inlineStr"/>
       <c r="AL194" t="inlineStr">
         <is>
-          <t>Alice de Souza Birchal</t>
+          <t>Dr. Marcelo Paulo Salgado</t>
         </is>
       </c>
       <c r="AM194" t="inlineStr">
@@ -44012,17 +43888,17 @@
       </c>
       <c r="AS194" t="inlineStr">
         <is>
-          <t>ASPLAGMETA-2275</t>
+          <t>ASPLAGMETA-2328</t>
         </is>
       </c>
       <c r="AT194" t="inlineStr">
         <is>
-          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2275 Janeiro Apuração Aberto ASPLAGMETA-2276 Fevereiro Apuração Aberto ASPLAGMETA-2277 Março Apuração Aberto ASPLAGMETA-2278 Abril Apuração Aberto ASPLAGMETA-2279 Maio Apuração Aberto ASPLAGMETA-2280 Junho Apuração Aberto ASPLAGMETA-2281 Julho Apuração Aberto ASPLAGMETA-2282 Agosto Apuração Aberto ASPLAGMETA-2283 Setembro Apuração Aberto ASPLAGMETA-2284 Outubro Apuração Aberto ASPLAGMETA-2285 Novembro Apuração Aberto ASPLAGMETA-2286 Dezembro Apuração Aberto ASPLAGMETA-2287 Apurado no período Apuração Aberto</t>
+          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2328 Janeiro Apuração Aberto ASPLAGMETA-2329 Fevereiro Apuração Aberto ASPLAGMETA-2330 Março Apuração Aberto ASPLAGMETA-2331 Abril Apuração Aberto ASPLAGMETA-2332 Maio Apuração Aberto ASPLAGMETA-2333 Junho Apuração Aberto ASPLAGMETA-2334 Julho Apuração Aberto ASPLAGMETA-2335 Agosto Apuração Aberto ASPLAGMETA-2336 Setembro Apuração Aberto ASPLAGMETA-2337 Outubro Apuração Aberto ASPLAGMETA-2338 Novembro Apuração Aberto ASPLAGMETA-2339 Dezembro Apuração Aberto ASPLAGMETA-2340 Apurado no período Apuração Aberto</t>
         </is>
       </c>
       <c r="AU194" t="inlineStr">
         <is>
-          <t>(31)3247- 8411</t>
+          <t>(31) 3232-2687</t>
         </is>
       </c>
       <c r="AV194" t="inlineStr">
@@ -44037,18 +43913,18 @@
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>COINJ</t>
+          <t>SEPAD</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr">
         <is>
-          <t>Pessoa</t>
+          <t>Percentual</t>
         </is>
       </c>
       <c r="AZ194" t="inlineStr"/>
       <c r="BA194" t="inlineStr">
         <is>
-          <t>250.000</t>
+          <t>95</t>
         </is>
       </c>
       <c r="BB194" t="inlineStr">
@@ -44077,7 +43953,7 @@
       <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr">
         <is>
-          <t>[ASPLAGMETA-2098] TJMG 144 - Obter, até 18/12/2025, pelo menos 10 (dez) parceiros cadastrados no Programa Descubra.</t>
+          <t>[ASPLAGMETA-2103] TJMG 6 - Realizar, em 2025, 70% (setenta por cento) dos julgamentos colegiados em até 100 dias. (desconsiderado o tempo de permanência em carga aos Advogados e aos Órgãos Externos, 25 (vinte e cinco) dias).</t>
         </is>
       </c>
       <c r="F195" t="inlineStr"/>
@@ -44093,7 +43969,7 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>Coordenador</t>
+          <t>Diretora de Secretaria</t>
         </is>
       </c>
       <c r="J195" t="inlineStr"/>
@@ -44107,17 +43983,21 @@
           <t>ASPLAG/TJMG</t>
         </is>
       </c>
-      <c r="M195" t="inlineStr"/>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
       <c r="N195" t="inlineStr"/>
       <c r="O195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Presidência</t>
+          <t>1ª Vice Presidência</t>
         </is>
       </c>
       <c r="Q195" t="inlineStr">
         <is>
-          <t>sandra.nunes@tjmg.jus.br</t>
+          <t>sepad@tjmg.jus.br</t>
         </is>
       </c>
       <c r="R195" t="inlineStr"/>
@@ -44135,30 +44015,34 @@
       <c r="V195" t="inlineStr"/>
       <c r="W195" t="inlineStr">
         <is>
-          <t>COINJ.</t>
-        </is>
-      </c>
-      <c r="X195" t="inlineStr"/>
+          <t>CEINJUR</t>
+        </is>
+      </c>
+      <c r="X195" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>Somatório de parceiros do Programa Descubra cadastrados.</t>
+          <t>Resultado do indicador: JC100d/ TJC, onde: JC100d = Número de julgamentos colegiados realizados em até 100 dias TJC = Total de julgamentos colegiados realizados no período JC100d  ∑ dos processos decididos pelo colegiado [(data de distribuição do processo) - (data do julgamento colegiado) =&lt; 100dias}</t>
         </is>
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>Sandra Ferreira Nunes</t>
+          <t>Sra. Elaine Batista Costa Souza</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
           <t>2025
-             - 1.18 -  Número de parceiros cadastrados no Programa Descubra.</t>
+             - 3.8 - Taxa de julgamentos colegiados em até 100 (cem) dias - 2º Grau.</t>
         </is>
       </c>
       <c r="AB195" t="inlineStr"/>
       <c r="AC195" t="inlineStr">
         <is>
-          <t>90 - Travessias da Infância e Juventude.</t>
+          <t>04 - Programa Agiliza-Jus. , 94 - Programa 1ª Vice SOMA - Suporte à organização, cumprimento de metas e aperfeiçoamento gerencial.</t>
         </is>
       </c>
       <c r="AD195" t="inlineStr">
@@ -44174,7 +44058,7 @@
       <c r="AF195" t="inlineStr"/>
       <c r="AG195" t="inlineStr">
         <is>
-          <t>1 - Garantia dos Direitos Fundamentais e do Estado Democrático de Direito</t>
+          <t>3 - Agilidade e Produtividade na Prestação Jurisdicional</t>
         </is>
       </c>
       <c r="AH195" t="inlineStr"/>
@@ -44184,19 +44068,15 @@
           <t>16 - Paz, Justiça e Instituições Eficazes</t>
         </is>
       </c>
-      <c r="AK195" t="inlineStr">
-        <is>
-          <t>DIRCOM , DIRDEP</t>
-        </is>
-      </c>
+      <c r="AK195" t="inlineStr"/>
       <c r="AL195" t="inlineStr">
         <is>
-          <t>Alice de Souza Birchal</t>
+          <t>Dr.  Marcelo Paulo Salgado</t>
         </is>
       </c>
       <c r="AM195" t="inlineStr">
         <is>
-          <t>Trimestral</t>
+          <t>Mensal</t>
         </is>
       </c>
       <c r="AN195" t="inlineStr">
@@ -44226,17 +44106,17 @@
       </c>
       <c r="AS195" t="inlineStr">
         <is>
-          <t>ASPLAGMETA-2263</t>
+          <t>ASPLAGMETA-2314</t>
         </is>
       </c>
       <c r="AT195" t="inlineStr">
         <is>
-          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2263 Janeiro Apuração Aberto ASPLAGMETA-2264 Fevereiro Apuração Aberto ASPLAGMETA-2265 Março Apuração Aberto ASPLAGMETA-2266 Abril Apuração Aberto ASPLAGMETA-2267 Maio Apuração Aberto ASPLAGMETA-2268 Junho Apuração Aberto ASPLAGMETA-2269 Julho Apuração Aberto ASPLAGMETA-2270 Agosto Apuração Aberto ASPLAGMETA-2271 Setembro Apuração Aberto ASPLAGMETA-2272 Outubro Apuração Aberto ASPLAGMETA-2273 Novembro Apuração Aberto ASPLAGMETA-2274 Dezembro Apuração Aberto ASPLAGMETA-2185 Apurado no período Apuração Aberto</t>
+          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2314 Janeiro Apuração Aberto ASPLAGMETA-2315 Fevereiro Apuração Aberto ASPLAGMETA-2316 Março Apuração Aberto ASPLAGMETA-2317 Abril Apuração Aberto ASPLAGMETA-2318 Maio Apuração Aberto ASPLAGMETA-2319 Junho Apuração Aberto ASPLAGMETA-2320 Julho Apuração Aberto ASPLAGMETA-2321 Agosto Apuração Aberto ASPLAGMETA-2322 Setembro Apuração Aberto ASPLAGMETA-2323 Outubro Apuração Aberto ASPLAGMETA-2324 Novembro Apuração Aberto ASPLAGMETA-2325 Dezembro Apuração Aberto ASPLAGMETA-2326 Apurado no período Apuração Aberto</t>
         </is>
       </c>
       <c r="AU195" t="inlineStr">
         <is>
-          <t>(31)3247- 8411</t>
+          <t>(31) 3232-2687</t>
         </is>
       </c>
       <c r="AV195" t="inlineStr">
@@ -44251,18 +44131,18 @@
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>COINJ</t>
+          <t>SEPAD</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr">
         <is>
-          <t>Unidade</t>
+          <t>Percentual</t>
         </is>
       </c>
       <c r="AZ195" t="inlineStr"/>
       <c r="BA195" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BB195" t="inlineStr">
@@ -44291,7 +44171,7 @@
       <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr">
         <is>
-          <t>[ASPLAGMETA-2097] TJMG 143 - Aumentar, até 18/12/2025, em pelo menos 10% (dez por cento) o número de municípios que promovem o Programa Descubra (referência março/2025: 21 municípios).</t>
+          <t>[ASPLAGMETA-2102] TJMG 5 - Realizar, em 2025, 70% (setenta por cento) dos julgamentos monocráticos, pelo relator, em 60 (sessenta) dias (desconsiderado o tempo de permanência em carga aos Advogados e aos Órgãos Externos, 25 (vinte e cinco) dias).</t>
         </is>
       </c>
       <c r="F196" t="inlineStr"/>
@@ -44307,7 +44187,7 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>Coordenador</t>
+          <t>Diretora de Secretaria</t>
         </is>
       </c>
       <c r="J196" t="inlineStr"/>
@@ -44330,15 +44210,19 @@
       <c r="O196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Presidência</t>
+          <t>1ª Vice Presidência</t>
         </is>
       </c>
       <c r="Q196" t="inlineStr">
         <is>
-          <t>sandra.nunes@tjmg.jus.br</t>
-        </is>
-      </c>
-      <c r="R196" t="inlineStr"/>
+          <t>sepad@tjmg.jus.br</t>
+        </is>
+      </c>
+      <c r="R196" t="inlineStr">
+        <is>
+          <t>asplag@tjmg.jus.br</t>
+        </is>
+      </c>
       <c r="S196" t="inlineStr">
         <is>
           <t>Responsável</t>
@@ -44353,34 +44237,34 @@
       <c r="V196" t="inlineStr"/>
       <c r="W196" t="inlineStr">
         <is>
-          <t>COINJ.</t>
+          <t>CEINJUR</t>
         </is>
       </c>
       <c r="X196" t="inlineStr">
         <is>
-          <t>Último Valor</t>
+          <t>Média</t>
         </is>
       </c>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>(Total de municípios que promoveram o Programa Descubra em 2025/Total de municípios que promoveram o Programa Descubra em 2024)*100.</t>
+          <t>Resultado do indicador = JM60d/TJM X 100, onde: JM60d = Número de julgamentos monocráticos realizados em até 60 dias. TJM = Total de julgamentos monocráticos realizados no período. JM60d  ∑ dos processos decididos monocraticamente [(data de distribuição do processo) - (data da decisão monocrática) =&lt; 60dias.</t>
         </is>
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>Sandra Ferreira Nunes</t>
+          <t>Sra. Elaine Batista Costa Souza</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
           <t>2025
-             - 1.17 - Taxa de aumento no número de municípios que promovem o Programa Descubra.</t>
+             - 3.7 - Taxa de julgamentos monocráticos em até 60 (sessenta) dias - 2º Grau.</t>
         </is>
       </c>
       <c r="AB196" t="inlineStr"/>
       <c r="AC196" t="inlineStr">
         <is>
-          <t>90 - Travessias da Infância e Juventude.</t>
+          <t>04 - Programa Agiliza-Jus. , 94 - Programa 1ª Vice SOMA - Suporte à organização, cumprimento de metas e aperfeiçoamento gerencial.</t>
         </is>
       </c>
       <c r="AD196" t="inlineStr">
@@ -44396,29 +44280,29 @@
       <c r="AF196" t="inlineStr"/>
       <c r="AG196" t="inlineStr">
         <is>
-          <t>1 - Garantia dos Direitos Fundamentais e do Estado Democrático de Direito</t>
+          <t>3 - Agilidade e Produtividade na Prestação Jurisdicional</t>
         </is>
       </c>
       <c r="AH196" t="inlineStr"/>
-      <c r="AI196" t="inlineStr"/>
+      <c r="AI196" t="inlineStr">
+        <is>
+          <t>ASPLAG</t>
+        </is>
+      </c>
       <c r="AJ196" t="inlineStr">
         <is>
           <t>16 - Paz, Justiça e Instituições Eficazes</t>
         </is>
       </c>
-      <c r="AK196" t="inlineStr">
-        <is>
-          <t>DIRCOM , DIRDEP</t>
-        </is>
-      </c>
+      <c r="AK196" t="inlineStr"/>
       <c r="AL196" t="inlineStr">
         <is>
-          <t>Alice de Souza Birchal</t>
+          <t>Dr. Marcelo Paulo Salgado</t>
         </is>
       </c>
       <c r="AM196" t="inlineStr">
         <is>
-          <t>Trimestral</t>
+          <t>Mensal</t>
         </is>
       </c>
       <c r="AN196" t="inlineStr">
@@ -44448,17 +44332,17 @@
       </c>
       <c r="AS196" t="inlineStr">
         <is>
-          <t>ASPLAGMETA-2241</t>
+          <t>ASPLAGMETA-2301</t>
         </is>
       </c>
       <c r="AT196" t="inlineStr">
         <is>
-          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2241 Janeiro Apuração Aberto ASPLAGMETA-2243 Fevereiro Apuração Aberto ASPLAGMETA-2246 Março Apuração Aberto ASPLAGMETA-2248 Abril Apuração Aberto ASPLAGMETA-2250 Maio Apuração Aberto ASPLAGMETA-2252 Junho Apuração Aberto ASPLAGMETA-2254 Julho Apuração Aberto ASPLAGMETA-2256 Agosto Apuração Aberto ASPLAGMETA-2258 Setembro Apuração Aberto ASPLAGMETA-2260 Outubro Apuração Aberto ASPLAGMETA-2261 Novembro Apuração Aberto ASPLAGMETA-2262 Dezembro Apuração Aberto ASPLAGMETA-2184 Apurado no período Apuração Aberto</t>
+          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2301 Janeiro Apuração Aberto ASPLAGMETA-2302 Fevereiro Apuração Aberto ASPLAGMETA-2303 Março Apuração Aberto ASPLAGMETA-2304 Abril Apuração Aberto ASPLAGMETA-2305 Maio Apuração Aberto ASPLAGMETA-2306 Junho Apuração Aberto ASPLAGMETA-2307 Julho Apuração Aberto ASPLAGMETA-2308 Agosto Apuração Aberto ASPLAGMETA-2309 Setembro Apuração Aberto ASPLAGMETA-2310 Outubro Apuração Aberto ASPLAGMETA-2311 Novembro Apuração Aberto ASPLAGMETA-2312 Dezembro Apuração Aberto ASPLAGMETA-2313 Apurado no período Apuração Aberto</t>
         </is>
       </c>
       <c r="AU196" t="inlineStr">
         <is>
-          <t>(31)3247- 8411</t>
+          <t>(31) 3232-2687</t>
         </is>
       </c>
       <c r="AV196" t="inlineStr">
@@ -44473,7 +44357,7 @@
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>COINJ</t>
+          <t>SEPAD</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr">
@@ -44484,7 +44368,7 @@
       <c r="AZ196" t="inlineStr"/>
       <c r="BA196" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BB196" t="inlineStr">
@@ -44513,7 +44397,7 @@
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
-          <t>[ASPLAGMETA-2096] TJMG 124 - Alcançar 20.000 (vinte mil) pessoas com ações relacionadas à prevenção e combate à violência doméstica e familiar, com a participação direta da população até dezembro de 2025.</t>
+          <t>[ASPLAGMETA-2101] TJMG 100 - Promover, por ação própria ou mediante parceria com outros órgãos internos e externos ao TJMG, o oferecimento de serviços de itinerância em pelo menos 50 (cinquenta) ações, até dezembro de 2025.</t>
         </is>
       </c>
       <c r="F197" t="inlineStr"/>
@@ -44527,7 +44411,11 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="I197" t="inlineStr"/>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Gerente</t>
+        </is>
+      </c>
       <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr">
         <is>
@@ -44548,12 +44436,12 @@
       <c r="O197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Presidência</t>
+          <t>3ª Vice Presidência</t>
         </is>
       </c>
       <c r="Q197" t="inlineStr">
         <is>
-          <t>comsiv@tjmg.jus.br</t>
+          <t>agin@tjmg.jus.br</t>
         </is>
       </c>
       <c r="R197" t="inlineStr">
@@ -44581,20 +44469,20 @@
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>Somatório de pessoas beneficiadas com ações relacionadas à prevenção e combate à violência doméstica e familiar.</t>
+          <t>Somatório do número de ações realizadas no âmbito da descrição da meta no ano de 2025</t>
         </is>
       </c>
       <c r="Z197" t="inlineStr"/>
       <c r="AA197" t="inlineStr">
         <is>
           <t>2025
-             - 1.16 - Número de pessoas beneficiadas com ações relacionadas à prevenção e combate à violência doméstica e familiar.</t>
+             - 2.4 - Número de ações de itinerância efetivamente realizadas.</t>
         </is>
       </c>
       <c r="AB197" t="inlineStr"/>
       <c r="AC197" t="inlineStr">
         <is>
-          <t>13 - Fortalecimento e implementação de políticas públicas de enfrentamento à violência doméstica e familiar</t>
+          <t>07 - Programa de estruturação de políticas públicas autocompositivas de solução de conflitos. , 47 - Programa de otimização do funcionamento dos CEJUSCs - Centros Judiciários de Solução de Conflitos e Cidadania.</t>
         </is>
       </c>
       <c r="AD197" t="inlineStr">
@@ -44610,7 +44498,7 @@
       <c r="AF197" t="inlineStr"/>
       <c r="AG197" t="inlineStr">
         <is>
-          <t>1 - Garantia dos Direitos Fundamentais e do Estado Democrático de Direito</t>
+          <t>2 - Ampliação da Relação Institucional do Judiciário com a Sociedade</t>
         </is>
       </c>
       <c r="AH197" t="inlineStr"/>
@@ -44624,10 +44512,14 @@
           <t>16 - Paz, Justiça e Instituições Eficazes</t>
         </is>
       </c>
-      <c r="AK197" t="inlineStr"/>
+      <c r="AK197" t="inlineStr">
+        <is>
+          <t>AGIN</t>
+        </is>
+      </c>
       <c r="AL197" t="inlineStr">
         <is>
-          <t>Evangelina Castilho Duarte</t>
+          <t>Rogério Medeiros Garcia de Lima</t>
         </is>
       </c>
       <c r="AM197" t="inlineStr">
@@ -44662,17 +44554,17 @@
       </c>
       <c r="AS197" t="inlineStr">
         <is>
-          <t>ASPLAGMETA-2209</t>
+          <t>ASPLAGMETA-2156</t>
         </is>
       </c>
       <c r="AT197" t="inlineStr">
         <is>
-          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2209 Janeiro Apuração Aberto ASPLAGMETA-2212 Fevereiro Apuração Aberto ASPLAGMETA-2213 Março Apuração Aberto ASPLAGMETA-2215 Abril Apuração Aberto ASPLAGMETA-2216 Maio Apuração Aberto ASPLAGMETA-2218 Junho Apuração Aberto ASPLAGMETA-2220 Julho Apuração Aberto ASPLAGMETA-2222 Agosto Apuração Aberto ASPLAGMETA-2224 Setembro Apuração Aberto ASPLAGMETA-2226 Outubro Apuração Aberto ASPLAGMETA-2229 Novembro Apuração Aberto ASPLAGMETA-2230 Dezembro Apuração Aberto ASPLAGMETA-2183 Apurado no período Apuração Aberto</t>
+          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2156 Janeiro Apuração Aberto ASPLAGMETA-2157 Fevereiro Apuração Aberto ASPLAGMETA-2158 Março Apuração Aberto ASPLAGMETA-2159 Abril Apuração Aberto ASPLAGMETA-2160 Maio Apuração Aberto ASPLAGMETA-2161 Junho Apuração Aberto ASPLAGMETA-2162 Julho Apuração Aberto ASPLAGMETA-2163 Agosto Apuração Aberto ASPLAGMETA-2164 Setembro Apuração Aberto ASPLAGMETA-2165 Outubro Apuração Aberto ASPLAGMETA-2166 Novembro Apuração Aberto ASPLAGMETA-2167 Dezembro Apuração Aberto ASPLAGMETA-2168 Apurado no período Apuração Aberto</t>
         </is>
       </c>
       <c r="AU197" t="inlineStr">
         <is>
-          <t>(31) 3306-3587</t>
+          <t>(31) 3232-2615</t>
         </is>
       </c>
       <c r="AV197" t="inlineStr">
@@ -44687,7 +44579,7 @@
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>COMSIV</t>
+          <t>Superintendência da Gestão de Inovação</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
@@ -44698,7 +44590,7 @@
       <c r="AZ197" t="inlineStr"/>
       <c r="BA197" t="inlineStr">
         <is>
-          <t>20.000</t>
+          <t>50</t>
         </is>
       </c>
       <c r="BB197" t="inlineStr">
@@ -44727,7 +44619,7 @@
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr">
         <is>
-          <t>[ASPLAGMETA-2095] TJMG 111 - Executar, até dezembro de 2025, 80% (oitenta por cento) das ações previstas para o ano vigente no programa D.I.A (Programa de Desenvolvimento, Inclusão e Acessibilidade).</t>
+          <t>[ASPLAGMETA-2100] TJMG 131 - Executar 100% (cem por cento) das entregas relativas à validação do fluxo de implantação dos Fóruns Digitais e à alteração da Resolução 1.061/2023.</t>
         </is>
       </c>
       <c r="F198" t="inlineStr"/>
@@ -44743,7 +44635,7 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>(31) 3306-3028</t>
+          <t>Secretário Geral da Presidência, acompanhado por Juiz e Juíza auxiliar da Presidência, Juiz auxiliar da Corregedoria Geral de Justiça, Juiz da 3 Vice Presidência.</t>
         </is>
       </c>
       <c r="J198" t="inlineStr"/>
@@ -44769,12 +44661,12 @@
           <t>Presidência</t>
         </is>
       </c>
-      <c r="Q198" t="inlineStr">
-        <is>
-          <t>ASPLAG</t>
-        </is>
-      </c>
-      <c r="R198" t="inlineStr"/>
+      <c r="Q198" t="inlineStr"/>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>asplag@tjmg.jus.br</t>
+        </is>
+      </c>
       <c r="S198" t="inlineStr">
         <is>
           <t>Responsável</t>
@@ -44787,7 +44679,11 @@
       </c>
       <c r="U198" t="inlineStr"/>
       <c r="V198" t="inlineStr"/>
-      <c r="W198" t="inlineStr"/>
+      <c r="W198" t="inlineStr">
+        <is>
+          <t>Cronograma de acompanhamento da iniciativa 86 - Fóruns Digitais.</t>
+        </is>
+      </c>
       <c r="X198" t="inlineStr">
         <is>
           <t>Último Valor</t>
@@ -44795,140 +44691,1226 @@
       </c>
       <c r="Y198" t="inlineStr">
         <is>
+          <t>Entregas concluídas até o período/ Entregas previstas no cômputo da meta. Obs.: À época da pactuação da meta, apenas 2 entregas eram conhecidas, motivo pelo qual foram nominadas na meta.</t>
+        </is>
+      </c>
+      <c r="Z198" t="inlineStr">
+        <is>
+          <t>Sr. Guilherme Augusto Mendes do Valle, acompanhado por: Dra. Marcela Maria Pereira Novais; Dr. Guilherme Lima Nogueira da Silva; Dr. José Ricardo dos Santos de Freitas Véras; Dr. Luís Fernando Benfatti.</t>
+        </is>
+      </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>2025
+             - 1.20 - Taxa de execução das entregas previstas na iniciativa Fóruns Dgitais.</t>
+        </is>
+      </c>
+      <c r="AB198" t="inlineStr"/>
+      <c r="AC198" t="inlineStr">
+        <is>
+          <t>86 - Fóruns Digitais.</t>
+        </is>
+      </c>
+      <c r="AD198" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AE198" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AF198" t="inlineStr"/>
+      <c r="AG198" t="inlineStr">
+        <is>
+          <t>1 - Garantia dos Direitos Fundamentais e do Estado Democrático de Direito</t>
+        </is>
+      </c>
+      <c r="AH198" t="inlineStr"/>
+      <c r="AI198" t="inlineStr">
+        <is>
+          <t>ASPLAG</t>
+        </is>
+      </c>
+      <c r="AJ198" t="inlineStr">
+        <is>
+          <t>16 - Paz, Justiça e Instituições Eficazes</t>
+        </is>
+      </c>
+      <c r="AK198" t="inlineStr">
+        <is>
+          <t>DENGEP , DIRCOM , DIRCOR , DIRFOR , DIRSEP , GAPRE , SEOESP , SUP.3ª VICE , CORREGEDORIA</t>
+        </is>
+      </c>
+      <c r="AL198" t="inlineStr">
+        <is>
+          <t>Des. Luiz Carlos de Azevedo Corrêa Junior</t>
+        </is>
+      </c>
+      <c r="AM198" t="inlineStr">
+        <is>
+          <t>Mensal</t>
+        </is>
+      </c>
+      <c r="AN198" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="AO198" t="inlineStr">
+        <is>
+          <t>Maior – melhor</t>
+        </is>
+      </c>
+      <c r="AP198" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="AQ198" t="inlineStr">
+        <is>
+          <t>ASPLAG - Metas Estratégicas</t>
+        </is>
+      </c>
+      <c r="AR198" t="inlineStr">
+        <is>
+          <t>Não Resolvido</t>
+        </is>
+      </c>
+      <c r="AS198" t="inlineStr">
+        <is>
+          <t>ASPLAGMETA-2288</t>
+        </is>
+      </c>
+      <c r="AT198" t="inlineStr">
+        <is>
+          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2288 Janeiro Apuração Aberto ASPLAGMETA-2289 Fevereiro Apuração Aberto ASPLAGMETA-2290 Março Apuração Aberto ASPLAGMETA-2291 Abril Apuração Aberto ASPLAGMETA-2292 Maio Apuração Aberto ASPLAGMETA-2293 Junho Apuração Aberto ASPLAGMETA-2294 Julho Apuração Aberto ASPLAGMETA-2295 Agosto Apuração Aberto ASPLAGMETA-2296 Setembro Apuração Aberto ASPLAGMETA-2297 Outubro Apuração Aberto ASPLAGMETA-2298 Novembro Apuração Aberto ASPLAGMETA-2299 Dezembro Apuração Aberto ASPLAGMETA-2300 Apurado no período Apuração Aberto</t>
+        </is>
+      </c>
+      <c r="AU198" t="inlineStr"/>
+      <c r="AV198" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="AW198" t="inlineStr">
+        <is>
+          <t>Institucional</t>
+        </is>
+      </c>
+      <c r="AX198" t="inlineStr">
+        <is>
+          <t>SEGOVE</t>
+        </is>
+      </c>
+      <c r="AY198" t="inlineStr">
+        <is>
+          <t>Percentual</t>
+        </is>
+      </c>
+      <c r="AZ198" t="inlineStr"/>
+      <c r="BA198" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="BB198" t="inlineStr">
+        <is>
+          <t>Nenhum</t>
+        </is>
+      </c>
+      <c r="BC198" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr"/>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Resumo</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>[ASPLAGMETA-2099] TJMG 145 - Beneficiar, até 18/12/2025, pelo menos 250.000 (duzentas e cinquenta mil) pessoas com as ações de impacto social fomentadas pela COINJ.</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Nenhum</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Coordenador</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Plano Estratégico 2025</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>ASPLAG/TJMG</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr"/>
+      <c r="O199" t="inlineStr"/>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>Presidência</t>
+        </is>
+      </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>sandra.nunes@tjmg.jus.br</t>
+        </is>
+      </c>
+      <c r="R199" t="inlineStr"/>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>Responsável</t>
+        </is>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>Nenhum</t>
+        </is>
+      </c>
+      <c r="U199" t="inlineStr"/>
+      <c r="V199" t="inlineStr"/>
+      <c r="W199" t="inlineStr">
+        <is>
+          <t>COINJ.</t>
+        </is>
+      </c>
+      <c r="X199" t="inlineStr">
+        <is>
+          <t>Soma</t>
+        </is>
+      </c>
+      <c r="Y199" t="inlineStr">
+        <is>
+          <t>Somatório de pessoas diretamente beneficiadas com as ações de impacto social fomentadas pela COINJ no ano de 2025.</t>
+        </is>
+      </c>
+      <c r="Z199" t="inlineStr">
+        <is>
+          <t>Sandra Ferreira Nunes</t>
+        </is>
+      </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>2025
+             - 1.19 - Número de pessoas beneficiadas com as ações de impacto sociail fomentadas pela COINJ.</t>
+        </is>
+      </c>
+      <c r="AB199" t="inlineStr"/>
+      <c r="AC199" t="inlineStr">
+        <is>
+          <t>90 - Travessias da Infância e Juventude.</t>
+        </is>
+      </c>
+      <c r="AD199" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AE199" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AF199" t="inlineStr"/>
+      <c r="AG199" t="inlineStr">
+        <is>
+          <t>1 - Garantia dos Direitos Fundamentais e do Estado Democrático de Direito</t>
+        </is>
+      </c>
+      <c r="AH199" t="inlineStr"/>
+      <c r="AI199" t="inlineStr"/>
+      <c r="AJ199" t="inlineStr">
+        <is>
+          <t>16 - Paz, Justiça e Instituições Eficazes</t>
+        </is>
+      </c>
+      <c r="AK199" t="inlineStr"/>
+      <c r="AL199" t="inlineStr">
+        <is>
+          <t>Alice de Souza Birchal</t>
+        </is>
+      </c>
+      <c r="AM199" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="AN199" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="AO199" t="inlineStr">
+        <is>
+          <t>Maior – melhor</t>
+        </is>
+      </c>
+      <c r="AP199" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="AQ199" t="inlineStr">
+        <is>
+          <t>ASPLAG - Metas Estratégicas</t>
+        </is>
+      </c>
+      <c r="AR199" t="inlineStr">
+        <is>
+          <t>Não Resolvido</t>
+        </is>
+      </c>
+      <c r="AS199" t="inlineStr">
+        <is>
+          <t>ASPLAGMETA-2275</t>
+        </is>
+      </c>
+      <c r="AT199" t="inlineStr">
+        <is>
+          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2275 Janeiro Apuração Aberto ASPLAGMETA-2276 Fevereiro Apuração Aberto ASPLAGMETA-2277 Março Apuração Aberto ASPLAGMETA-2278 Abril Apuração Aberto ASPLAGMETA-2279 Maio Apuração Aberto ASPLAGMETA-2280 Junho Apuração Aberto ASPLAGMETA-2281 Julho Apuração Aberto ASPLAGMETA-2282 Agosto Apuração Aberto ASPLAGMETA-2283 Setembro Apuração Aberto ASPLAGMETA-2284 Outubro Apuração Aberto ASPLAGMETA-2285 Novembro Apuração Aberto ASPLAGMETA-2286 Dezembro Apuração Aberto ASPLAGMETA-2287 Apurado no período Apuração Aberto</t>
+        </is>
+      </c>
+      <c r="AU199" t="inlineStr">
+        <is>
+          <t>(31)3247- 8411</t>
+        </is>
+      </c>
+      <c r="AV199" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="AW199" t="inlineStr">
+        <is>
+          <t>Institucional</t>
+        </is>
+      </c>
+      <c r="AX199" t="inlineStr">
+        <is>
+          <t>COINJ</t>
+        </is>
+      </c>
+      <c r="AY199" t="inlineStr">
+        <is>
+          <t>Pessoa</t>
+        </is>
+      </c>
+      <c r="AZ199" t="inlineStr"/>
+      <c r="BA199" t="inlineStr">
+        <is>
+          <t>250.000</t>
+        </is>
+      </c>
+      <c r="BB199" t="inlineStr">
+        <is>
+          <t>Nenhum</t>
+        </is>
+      </c>
+      <c r="BC199" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr"/>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Resumo</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>[ASPLAGMETA-2098] TJMG 144 - Obter, até 18/12/2025, pelo menos 10 (dez) parceiros cadastrados no Programa Descubra.</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Nenhum</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Coordenador</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Plano Estratégico 2025</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>ASPLAG/TJMG</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr"/>
+      <c r="N200" t="inlineStr"/>
+      <c r="O200" t="inlineStr"/>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>Presidência</t>
+        </is>
+      </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>sandra.nunes@tjmg.jus.br</t>
+        </is>
+      </c>
+      <c r="R200" t="inlineStr"/>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>Responsável</t>
+        </is>
+      </c>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>Nenhum</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr"/>
+      <c r="V200" t="inlineStr"/>
+      <c r="W200" t="inlineStr">
+        <is>
+          <t>COINJ.</t>
+        </is>
+      </c>
+      <c r="X200" t="inlineStr"/>
+      <c r="Y200" t="inlineStr">
+        <is>
+          <t>Somatório de parceiros do Programa Descubra cadastrados.</t>
+        </is>
+      </c>
+      <c r="Z200" t="inlineStr">
+        <is>
+          <t>Sandra Ferreira Nunes</t>
+        </is>
+      </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>2025
+             - 1.18 -  Número de parceiros cadastrados no Programa Descubra.</t>
+        </is>
+      </c>
+      <c r="AB200" t="inlineStr"/>
+      <c r="AC200" t="inlineStr">
+        <is>
+          <t>90 - Travessias da Infância e Juventude.</t>
+        </is>
+      </c>
+      <c r="AD200" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AE200" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AF200" t="inlineStr"/>
+      <c r="AG200" t="inlineStr">
+        <is>
+          <t>1 - Garantia dos Direitos Fundamentais e do Estado Democrático de Direito</t>
+        </is>
+      </c>
+      <c r="AH200" t="inlineStr"/>
+      <c r="AI200" t="inlineStr"/>
+      <c r="AJ200" t="inlineStr">
+        <is>
+          <t>16 - Paz, Justiça e Instituições Eficazes</t>
+        </is>
+      </c>
+      <c r="AK200" t="inlineStr">
+        <is>
+          <t>DIRCOM , DIRDEP</t>
+        </is>
+      </c>
+      <c r="AL200" t="inlineStr">
+        <is>
+          <t>Alice de Souza Birchal</t>
+        </is>
+      </c>
+      <c r="AM200" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="AN200" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="AO200" t="inlineStr">
+        <is>
+          <t>Maior – melhor</t>
+        </is>
+      </c>
+      <c r="AP200" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="AQ200" t="inlineStr">
+        <is>
+          <t>ASPLAG - Metas Estratégicas</t>
+        </is>
+      </c>
+      <c r="AR200" t="inlineStr">
+        <is>
+          <t>Não Resolvido</t>
+        </is>
+      </c>
+      <c r="AS200" t="inlineStr">
+        <is>
+          <t>ASPLAGMETA-2263</t>
+        </is>
+      </c>
+      <c r="AT200" t="inlineStr">
+        <is>
+          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2263 Janeiro Apuração Aberto ASPLAGMETA-2264 Fevereiro Apuração Aberto ASPLAGMETA-2265 Março Apuração Aberto ASPLAGMETA-2266 Abril Apuração Aberto ASPLAGMETA-2267 Maio Apuração Aberto ASPLAGMETA-2268 Junho Apuração Aberto ASPLAGMETA-2269 Julho Apuração Aberto ASPLAGMETA-2270 Agosto Apuração Aberto ASPLAGMETA-2271 Setembro Apuração Aberto ASPLAGMETA-2272 Outubro Apuração Aberto ASPLAGMETA-2273 Novembro Apuração Aberto ASPLAGMETA-2274 Dezembro Apuração Aberto ASPLAGMETA-2185 Apurado no período Apuração Aberto</t>
+        </is>
+      </c>
+      <c r="AU200" t="inlineStr">
+        <is>
+          <t>(31)3247- 8411</t>
+        </is>
+      </c>
+      <c r="AV200" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="AW200" t="inlineStr">
+        <is>
+          <t>Institucional</t>
+        </is>
+      </c>
+      <c r="AX200" t="inlineStr">
+        <is>
+          <t>COINJ</t>
+        </is>
+      </c>
+      <c r="AY200" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="AZ200" t="inlineStr"/>
+      <c r="BA200" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BB200" t="inlineStr">
+        <is>
+          <t>Nenhum</t>
+        </is>
+      </c>
+      <c r="BC200" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr"/>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Resumo</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>[ASPLAGMETA-2097] TJMG 143 - Aumentar, até 18/12/2025, em pelo menos 10% (dez por cento) o número de municípios que promovem o Programa Descubra (referência março/2025: 21 municípios).</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Nenhum</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Coordenador</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Plano Estratégico 2025</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>ASPLAG/TJMG</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr"/>
+      <c r="O201" t="inlineStr"/>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>Presidência</t>
+        </is>
+      </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>sandra.nunes@tjmg.jus.br</t>
+        </is>
+      </c>
+      <c r="R201" t="inlineStr"/>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>Responsável</t>
+        </is>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>Nenhum</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr"/>
+      <c r="V201" t="inlineStr"/>
+      <c r="W201" t="inlineStr">
+        <is>
+          <t>COINJ.</t>
+        </is>
+      </c>
+      <c r="X201" t="inlineStr">
+        <is>
+          <t>Último Valor</t>
+        </is>
+      </c>
+      <c r="Y201" t="inlineStr">
+        <is>
+          <t>(Total de municípios que promoveram o Programa Descubra em 2025/Total de municípios que promoveram o Programa Descubra em 2024)*100.</t>
+        </is>
+      </c>
+      <c r="Z201" t="inlineStr">
+        <is>
+          <t>Sandra Ferreira Nunes</t>
+        </is>
+      </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>2025
+             - 1.17 - Taxa de aumento no número de municípios que promovem o Programa Descubra.</t>
+        </is>
+      </c>
+      <c r="AB201" t="inlineStr"/>
+      <c r="AC201" t="inlineStr">
+        <is>
+          <t>90 - Travessias da Infância e Juventude.</t>
+        </is>
+      </c>
+      <c r="AD201" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AE201" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AF201" t="inlineStr"/>
+      <c r="AG201" t="inlineStr">
+        <is>
+          <t>1 - Garantia dos Direitos Fundamentais e do Estado Democrático de Direito</t>
+        </is>
+      </c>
+      <c r="AH201" t="inlineStr"/>
+      <c r="AI201" t="inlineStr"/>
+      <c r="AJ201" t="inlineStr">
+        <is>
+          <t>16 - Paz, Justiça e Instituições Eficazes</t>
+        </is>
+      </c>
+      <c r="AK201" t="inlineStr">
+        <is>
+          <t>DIRCOM , DIRDEP</t>
+        </is>
+      </c>
+      <c r="AL201" t="inlineStr">
+        <is>
+          <t>Alice de Souza Birchal</t>
+        </is>
+      </c>
+      <c r="AM201" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="AN201" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="AO201" t="inlineStr">
+        <is>
+          <t>Maior – melhor</t>
+        </is>
+      </c>
+      <c r="AP201" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="AQ201" t="inlineStr">
+        <is>
+          <t>ASPLAG - Metas Estratégicas</t>
+        </is>
+      </c>
+      <c r="AR201" t="inlineStr">
+        <is>
+          <t>Não Resolvido</t>
+        </is>
+      </c>
+      <c r="AS201" t="inlineStr">
+        <is>
+          <t>ASPLAGMETA-2241</t>
+        </is>
+      </c>
+      <c r="AT201" t="inlineStr">
+        <is>
+          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2241 Janeiro Apuração Aberto ASPLAGMETA-2243 Fevereiro Apuração Aberto ASPLAGMETA-2246 Março Apuração Aberto ASPLAGMETA-2248 Abril Apuração Aberto ASPLAGMETA-2250 Maio Apuração Aberto ASPLAGMETA-2252 Junho Apuração Aberto ASPLAGMETA-2254 Julho Apuração Aberto ASPLAGMETA-2256 Agosto Apuração Aberto ASPLAGMETA-2258 Setembro Apuração Aberto ASPLAGMETA-2260 Outubro Apuração Aberto ASPLAGMETA-2261 Novembro Apuração Aberto ASPLAGMETA-2262 Dezembro Apuração Aberto ASPLAGMETA-2184 Apurado no período Apuração Aberto</t>
+        </is>
+      </c>
+      <c r="AU201" t="inlineStr">
+        <is>
+          <t>(31)3247- 8411</t>
+        </is>
+      </c>
+      <c r="AV201" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="AW201" t="inlineStr">
+        <is>
+          <t>Institucional</t>
+        </is>
+      </c>
+      <c r="AX201" t="inlineStr">
+        <is>
+          <t>COINJ</t>
+        </is>
+      </c>
+      <c r="AY201" t="inlineStr">
+        <is>
+          <t>Percentual</t>
+        </is>
+      </c>
+      <c r="AZ201" t="inlineStr"/>
+      <c r="BA201" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BB201" t="inlineStr">
+        <is>
+          <t>Nenhum</t>
+        </is>
+      </c>
+      <c r="BC201" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr"/>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Resumo</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>[ASPLAGMETA-2096] TJMG 124 - Alcançar 20.000 (vinte mil) pessoas com ações relacionadas à prevenção e combate à violência doméstica e familiar, com a participação direta da população até dezembro de 2025.</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Nenhum</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr"/>
+      <c r="J202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Plano Estratégico 2025</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>ASPLAG/TJMG</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr"/>
+      <c r="O202" t="inlineStr"/>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>Presidência</t>
+        </is>
+      </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>comsiv@tjmg.jus.br</t>
+        </is>
+      </c>
+      <c r="R202" t="inlineStr">
+        <is>
+          <t>asplag@tjmg.jus.br</t>
+        </is>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>Responsável</t>
+        </is>
+      </c>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>Nenhum</t>
+        </is>
+      </c>
+      <c r="U202" t="inlineStr"/>
+      <c r="V202" t="inlineStr"/>
+      <c r="W202" t="inlineStr"/>
+      <c r="X202" t="inlineStr">
+        <is>
+          <t>Soma</t>
+        </is>
+      </c>
+      <c r="Y202" t="inlineStr">
+        <is>
+          <t>Somatório de pessoas beneficiadas com ações relacionadas à prevenção e combate à violência doméstica e familiar.</t>
+        </is>
+      </c>
+      <c r="Z202" t="inlineStr"/>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>2025
+             - 1.16 - Número de pessoas beneficiadas com ações relacionadas à prevenção e combate à violência doméstica e familiar.</t>
+        </is>
+      </c>
+      <c r="AB202" t="inlineStr"/>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>13 - Fortalecimento e implementação de políticas públicas de enfrentamento à violência doméstica e familiar</t>
+        </is>
+      </c>
+      <c r="AD202" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AE202" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AF202" t="inlineStr"/>
+      <c r="AG202" t="inlineStr">
+        <is>
+          <t>1 - Garantia dos Direitos Fundamentais e do Estado Democrático de Direito</t>
+        </is>
+      </c>
+      <c r="AH202" t="inlineStr"/>
+      <c r="AI202" t="inlineStr">
+        <is>
+          <t>ASPLAG</t>
+        </is>
+      </c>
+      <c r="AJ202" t="inlineStr">
+        <is>
+          <t>16 - Paz, Justiça e Instituições Eficazes</t>
+        </is>
+      </c>
+      <c r="AK202" t="inlineStr"/>
+      <c r="AL202" t="inlineStr">
+        <is>
+          <t>Evangelina Castilho Duarte</t>
+        </is>
+      </c>
+      <c r="AM202" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="AN202" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="AO202" t="inlineStr">
+        <is>
+          <t>Maior – melhor</t>
+        </is>
+      </c>
+      <c r="AP202" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="AQ202" t="inlineStr">
+        <is>
+          <t>ASPLAG - Metas Estratégicas</t>
+        </is>
+      </c>
+      <c r="AR202" t="inlineStr">
+        <is>
+          <t>Não Resolvido</t>
+        </is>
+      </c>
+      <c r="AS202" t="inlineStr">
+        <is>
+          <t>ASPLAGMETA-2209</t>
+        </is>
+      </c>
+      <c r="AT202" t="inlineStr">
+        <is>
+          <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2209 Janeiro Apuração Aberto ASPLAGMETA-2212 Fevereiro Apuração Aberto ASPLAGMETA-2213 Março Apuração Aberto ASPLAGMETA-2215 Abril Apuração Aberto ASPLAGMETA-2216 Maio Apuração Aberto ASPLAGMETA-2218 Junho Apuração Aberto ASPLAGMETA-2220 Julho Apuração Aberto ASPLAGMETA-2222 Agosto Apuração Aberto ASPLAGMETA-2224 Setembro Apuração Aberto ASPLAGMETA-2226 Outubro Apuração Aberto ASPLAGMETA-2229 Novembro Apuração Aberto ASPLAGMETA-2230 Dezembro Apuração Aberto ASPLAGMETA-2183 Apurado no período Apuração Aberto</t>
+        </is>
+      </c>
+      <c r="AU202" t="inlineStr">
+        <is>
+          <t>(31) 3306-3587</t>
+        </is>
+      </c>
+      <c r="AV202" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="AW202" t="inlineStr">
+        <is>
+          <t>Institucional</t>
+        </is>
+      </c>
+      <c r="AX202" t="inlineStr">
+        <is>
+          <t>COMSIV</t>
+        </is>
+      </c>
+      <c r="AY202" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="AZ202" t="inlineStr"/>
+      <c r="BA202" t="inlineStr">
+        <is>
+          <t>20.000</t>
+        </is>
+      </c>
+      <c r="BB202" t="inlineStr">
+        <is>
+          <t>Nenhum</t>
+        </is>
+      </c>
+      <c r="BC202" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr"/>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Resumo</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>[ASPLAGMETA-2095] TJMG 111 - Executar, até dezembro de 2025, 80% (oitenta por cento) das ações previstas para o ano vigente no programa D.I.A (Programa de Desenvolvimento, Inclusão e Acessibilidade).</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Nenhum</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>(31) 3306-3028</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Plano Estratégico 2025</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>ASPLAG/TJMG</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr"/>
+      <c r="O203" t="inlineStr"/>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>Presidência</t>
+        </is>
+      </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>ASPLAG</t>
+        </is>
+      </c>
+      <c r="R203" t="inlineStr"/>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>Responsável</t>
+        </is>
+      </c>
+      <c r="T203" t="inlineStr">
+        <is>
+          <t>Nenhum</t>
+        </is>
+      </c>
+      <c r="U203" t="inlineStr"/>
+      <c r="V203" t="inlineStr"/>
+      <c r="W203" t="inlineStr"/>
+      <c r="X203" t="inlineStr">
+        <is>
+          <t>Último Valor</t>
+        </is>
+      </c>
+      <c r="Y203" t="inlineStr">
+        <is>
           <t>Resultado do indicador = QME/QMP X 100, onde: QME= Quantidade de ações executadas. QMP = Quantidade total de ações previstas para o ano de 2024.</t>
         </is>
       </c>
-      <c r="Z198" t="inlineStr">
+      <c r="Z203" t="inlineStr">
         <is>
           <t>Selmara Alves Fernandes</t>
         </is>
       </c>
-      <c r="AA198" t="inlineStr">
+      <c r="AA203" t="inlineStr">
         <is>
           <t>2025
              - 1.14 - Taxa de execução das ações previstas no Programa D.I.A (Programa de Desenvolvimento, Inclusão e Acessibilidade).</t>
         </is>
       </c>
-      <c r="AB198" t="inlineStr"/>
-      <c r="AC198" t="inlineStr">
+      <c r="AB203" t="inlineStr"/>
+      <c r="AC203" t="inlineStr">
         <is>
           <t>79 - Programa D.I.A. (Programa de Desenvolvimento, Inclusão e Acessibilidade).</t>
         </is>
       </c>
-      <c r="AD198" t="inlineStr">
+      <c r="AD203" t="inlineStr">
         <is>
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="AE198" t="inlineStr">
+      <c r="AE203" t="inlineStr">
         <is>
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="AF198" t="inlineStr"/>
-      <c r="AG198" t="inlineStr">
+      <c r="AF203" t="inlineStr"/>
+      <c r="AG203" t="inlineStr">
         <is>
           <t>1 - Garantia dos Direitos Fundamentais e do Estado Democrático de Direito</t>
         </is>
       </c>
-      <c r="AH198" t="inlineStr"/>
-      <c r="AI198" t="inlineStr">
+      <c r="AH203" t="inlineStr"/>
+      <c r="AI203" t="inlineStr">
         <is>
           <t>asplag@tjmg.jus.br</t>
         </is>
       </c>
-      <c r="AJ198" t="inlineStr">
+      <c r="AJ203" t="inlineStr">
         <is>
           <t>16 - Paz, Justiça e Instituições Eficazes</t>
         </is>
       </c>
-      <c r="AK198" t="inlineStr">
+      <c r="AK203" t="inlineStr">
         <is>
           <t>DENGEP , DIRCOM , DIRSEP</t>
         </is>
       </c>
-      <c r="AL198" t="inlineStr">
+      <c r="AL203" t="inlineStr">
         <is>
           <t>Luiz Artur Rocha Hilário</t>
         </is>
       </c>
-      <c r="AM198" t="inlineStr">
+      <c r="AM203" t="inlineStr">
         <is>
           <t>Mensal</t>
         </is>
       </c>
-      <c r="AN198" t="inlineStr">
+      <c r="AN203" t="inlineStr">
         <is>
           <t>PE</t>
         </is>
       </c>
-      <c r="AO198" t="inlineStr">
+      <c r="AO203" t="inlineStr">
         <is>
           <t>Maior – melhor</t>
         </is>
       </c>
-      <c r="AP198" t="inlineStr">
+      <c r="AP203" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="AQ198" t="inlineStr">
+      <c r="AQ203" t="inlineStr">
         <is>
           <t>ASPLAG - Metas Estratégicas</t>
         </is>
       </c>
-      <c r="AR198" t="inlineStr">
+      <c r="AR203" t="inlineStr">
         <is>
           <t>Não Resolvido</t>
         </is>
       </c>
-      <c r="AS198" t="inlineStr">
+      <c r="AS203" t="inlineStr">
         <is>
           <t>ASPLAGMETA-2186</t>
         </is>
       </c>
-      <c r="AT198" t="inlineStr">
+      <c r="AT203" t="inlineStr">
         <is>
           <t>Chave Resumo Tipo Estado Responsável ASPLAGMETA-2186 Janeiro Apuração Aberto ASPLAGMETA-2189 Fevereiro Apuração Aberto ASPLAGMETA-2190 Março Apuração Aberto ASPLAGMETA-2191 Abril Apuração Aberto ASPLAGMETA-2192 Maio Apuração Aberto ASPLAGMETA-2194 Junho Apuração Aberto ASPLAGMETA-2196 Julho Apuração Aberto ASPLAGMETA-2197 Agosto Apuração Aberto ASPLAGMETA-2199 Setembro Apuração Aberto ASPLAGMETA-2200 Outubro Apuração Aberto ASPLAGMETA-2202 Novembro Apuração Aberto ASPLAGMETA-2204 Dezembro Apuração Aberto ASPLAGMETA-2182 Apurado no período Apuração Aberto</t>
         </is>
       </c>
-      <c r="AU198" t="inlineStr">
+      <c r="AU203" t="inlineStr">
         <is>
           <t>selmara.fernandes@tjmg.jus.br</t>
         </is>
       </c>
-      <c r="AV198" t="inlineStr">
+      <c r="AV203" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="AW198" t="inlineStr">
+      <c r="AW203" t="inlineStr">
         <is>
           <t>Institucional</t>
         </is>
       </c>
-      <c r="AX198" t="inlineStr">
+      <c r="AX203" t="inlineStr">
         <is>
           <t>SEGOVE</t>
         </is>
       </c>
-      <c r="AY198" t="inlineStr">
+      <c r="AY203" t="inlineStr">
         <is>
           <t>Percentual</t>
         </is>
       </c>
-      <c r="AZ198" t="inlineStr"/>
-      <c r="BA198" t="inlineStr">
+      <c r="AZ203" t="inlineStr"/>
+      <c r="BA203" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="BB198" t="inlineStr">
-        <is>
-          <t>Nenhum</t>
-        </is>
-      </c>
-      <c r="BC198" t="inlineStr">
+      <c r="BB203" t="inlineStr">
+        <is>
+          <t>Nenhum</t>
+        </is>
+      </c>
+      <c r="BC203" t="inlineStr">
         <is>
           <t>0</t>
         </is>
